--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$1593</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$1644</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -310,7 +310,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="275">
   <si>
     <t>id</t>
   </si>
@@ -1081,6 +1081,63 @@
   <si>
     <t>15x</t>
   </si>
+  <si>
+    <t>1_19_30_41_52_63</t>
+  </si>
+  <si>
+    <t>图标10</t>
+  </si>
+  <si>
+    <t>2_20_31_42_53_64</t>
+  </si>
+  <si>
+    <t>图标J</t>
+  </si>
+  <si>
+    <t>3_21_32_43_54_65</t>
+  </si>
+  <si>
+    <t>图标Q</t>
+  </si>
+  <si>
+    <t>4_22_33_44_55_66</t>
+  </si>
+  <si>
+    <t>图标K</t>
+  </si>
+  <si>
+    <t>5_23_34_45_56_67</t>
+  </si>
+  <si>
+    <t>图标A</t>
+  </si>
+  <si>
+    <t>6_24_35_46_57_68</t>
+  </si>
+  <si>
+    <t>7_25_36_47_58_69</t>
+  </si>
+  <si>
+    <t>8_26_37_48_59_70</t>
+  </si>
+  <si>
+    <t>9_27_38_49_60_71</t>
+  </si>
+  <si>
+    <t>10_28_39_50_61_72</t>
+  </si>
+  <si>
+    <t>11_29_40_51_62_73</t>
+  </si>
+  <si>
+    <t>图标6</t>
+  </si>
+  <si>
+    <t>夺宝符号</t>
+  </si>
+  <si>
+    <t>wheel</t>
+  </si>
 </sst>
 </file>
 
@@ -1348,7 +1405,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1359,12 +1416,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2005,7 +2062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2282,6 +2339,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -6600,7 +6658,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:N1593"/>
+  <dimension ref="A1:N1660"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="11"/>
@@ -16931,7 +16989,7 @@
       <c r="I346" s="12">
         <v>0</v>
       </c>
-      <c r="L346" s="98" t="s">
+      <c r="L346" s="99" t="s">
         <v>70</v>
       </c>
     </row>
@@ -50673,8 +50731,1928 @@
       <c r="K1593" s="2"/>
       <c r="L1593" s="14"/>
     </row>
+    <row r="1594" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1594" s="2">
+        <v>1048200101</v>
+      </c>
+      <c r="B1594" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1594" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1594" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1594" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1594" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1594" s="2">
+        <v>1</v>
+      </c>
+      <c r="H1594" s="13"/>
+      <c r="I1594" s="13"/>
+      <c r="J1594" s="13"/>
+      <c r="K1594" s="2"/>
+      <c r="L1594" s="14"/>
+    </row>
+    <row r="1595" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1595" s="2">
+        <v>1048200102</v>
+      </c>
+      <c r="B1595" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1595" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1595" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1595" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1595" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1595" s="2">
+        <v>1</v>
+      </c>
+      <c r="H1595" s="13"/>
+      <c r="I1595" s="13"/>
+      <c r="J1595" s="13"/>
+      <c r="K1595" s="2"/>
+      <c r="L1595" s="14"/>
+    </row>
+    <row r="1596" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1596" s="2">
+        <v>1048200103</v>
+      </c>
+      <c r="B1596" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1596" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1596" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1596" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1596" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1596" s="2">
+        <v>1</v>
+      </c>
+      <c r="H1596" s="13"/>
+      <c r="I1596" s="13"/>
+      <c r="J1596" s="13"/>
+      <c r="K1596" s="2"/>
+      <c r="L1596" s="14"/>
+    </row>
+    <row r="1597" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1597" s="2">
+        <v>1048200104</v>
+      </c>
+      <c r="B1597" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1597" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1597" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1597" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="F1597" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1597" s="2">
+        <v>2</v>
+      </c>
+      <c r="H1597" s="13"/>
+      <c r="I1597" s="13"/>
+      <c r="J1597" s="13"/>
+      <c r="K1597" s="2"/>
+      <c r="L1597" s="14"/>
+    </row>
+    <row r="1598" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1598" s="2">
+        <v>1048200105</v>
+      </c>
+      <c r="B1598" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1598" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1598" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1598" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1598" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1598" s="2">
+        <v>2</v>
+      </c>
+      <c r="H1598" s="13"/>
+      <c r="I1598" s="13"/>
+      <c r="J1598" s="13"/>
+      <c r="K1598" s="2"/>
+      <c r="L1598" s="14"/>
+    </row>
+    <row r="1599" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1599" s="2">
+        <v>1048200106</v>
+      </c>
+      <c r="B1599" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1599" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1599" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1599" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1599" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1599" s="2">
+        <v>5</v>
+      </c>
+      <c r="H1599" s="13"/>
+      <c r="I1599" s="13"/>
+      <c r="J1599" s="13"/>
+      <c r="K1599" s="2"/>
+      <c r="L1599" s="14"/>
+    </row>
+    <row r="1600" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1600" s="2">
+        <v>1048200107</v>
+      </c>
+      <c r="B1600" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1600" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1600" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1600" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1600" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1600" s="2">
+        <v>5</v>
+      </c>
+      <c r="H1600" s="13"/>
+      <c r="I1600" s="13"/>
+      <c r="J1600" s="13"/>
+      <c r="K1600" s="2"/>
+      <c r="L1600" s="14"/>
+    </row>
+    <row r="1601" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1601" s="2">
+        <v>1048200108</v>
+      </c>
+      <c r="B1601" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1601" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1601" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1601" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1601" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1601" s="2">
+        <v>8</v>
+      </c>
+      <c r="H1601" s="13"/>
+      <c r="I1601" s="13"/>
+      <c r="J1601" s="13"/>
+      <c r="K1601" s="2"/>
+      <c r="L1601" s="14"/>
+    </row>
+    <row r="1602" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1602" s="2">
+        <v>1048200109</v>
+      </c>
+      <c r="B1602" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1602" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1602" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1602" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1602" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1602" s="2">
+        <v>10</v>
+      </c>
+      <c r="H1602" s="13"/>
+      <c r="I1602" s="13"/>
+      <c r="J1602" s="13"/>
+      <c r="K1602" s="2"/>
+      <c r="L1602" s="14"/>
+    </row>
+    <row r="1603" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1603" s="2">
+        <v>1048200110</v>
+      </c>
+      <c r="B1603" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1603" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1603" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1603" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1603" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1603" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1603" s="13"/>
+      <c r="I1603" s="13"/>
+      <c r="J1603" s="13"/>
+      <c r="K1603" s="2"/>
+      <c r="L1603" s="14"/>
+    </row>
+    <row r="1604" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1604" s="2">
+        <v>1048200111</v>
+      </c>
+      <c r="B1604" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1604" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1604" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1604" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1604" s="58">
+        <v>3</v>
+      </c>
+      <c r="G1604" s="2">
+        <v>30</v>
+      </c>
+      <c r="H1604" s="13"/>
+      <c r="I1604" s="13"/>
+      <c r="J1604" s="13"/>
+      <c r="K1604" s="2"/>
+      <c r="L1604" s="14"/>
+    </row>
+    <row r="1605" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1605" s="2">
+        <v>1048200201</v>
+      </c>
+      <c r="B1605" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1605" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1605" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1605" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1605" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1605" s="2">
+        <v>2</v>
+      </c>
+      <c r="H1605" s="13"/>
+      <c r="I1605" s="13"/>
+      <c r="J1605" s="13"/>
+      <c r="K1605" s="2"/>
+      <c r="L1605" s="14"/>
+    </row>
+    <row r="1606" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1606" s="2">
+        <v>1048200202</v>
+      </c>
+      <c r="B1606" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1606" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1606" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1606" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1606" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1606" s="2">
+        <v>2</v>
+      </c>
+      <c r="H1606" s="13"/>
+      <c r="I1606" s="13"/>
+      <c r="J1606" s="13"/>
+      <c r="K1606" s="2"/>
+      <c r="L1606" s="14"/>
+    </row>
+    <row r="1607" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1607" s="2">
+        <v>1048200203</v>
+      </c>
+      <c r="B1607" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1607" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1607" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1607" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1607" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1607" s="2">
+        <v>2</v>
+      </c>
+      <c r="H1607" s="13"/>
+      <c r="I1607" s="13"/>
+      <c r="J1607" s="13"/>
+      <c r="K1607" s="2"/>
+      <c r="L1607" s="14"/>
+    </row>
+    <row r="1608" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1608" s="2">
+        <v>1048200204</v>
+      </c>
+      <c r="B1608" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1608" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1608" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1608" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="F1608" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1608" s="2">
+        <v>3</v>
+      </c>
+      <c r="H1608" s="13"/>
+      <c r="I1608" s="13"/>
+      <c r="J1608" s="13"/>
+      <c r="K1608" s="2"/>
+      <c r="L1608" s="14"/>
+    </row>
+    <row r="1609" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1609" s="2">
+        <v>1048200205</v>
+      </c>
+      <c r="B1609" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1609" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1609" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1609" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1609" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1609" s="2">
+        <v>3</v>
+      </c>
+      <c r="H1609" s="13"/>
+      <c r="I1609" s="13"/>
+      <c r="J1609" s="13"/>
+      <c r="K1609" s="2"/>
+      <c r="L1609" s="14"/>
+    </row>
+    <row r="1610" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1610" s="2">
+        <v>1048200206</v>
+      </c>
+      <c r="B1610" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1610" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1610" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1610" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1610" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1610" s="2">
+        <v>8</v>
+      </c>
+      <c r="H1610" s="13"/>
+      <c r="I1610" s="13"/>
+      <c r="J1610" s="13"/>
+      <c r="K1610" s="2"/>
+      <c r="L1610" s="14"/>
+    </row>
+    <row r="1611" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1611" s="2">
+        <v>1048200207</v>
+      </c>
+      <c r="B1611" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1611" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1611" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1611" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1611" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1611" s="12">
+        <v>8</v>
+      </c>
+      <c r="H1611" s="12"/>
+      <c r="I1611" s="12"/>
+      <c r="J1611" s="13"/>
+      <c r="K1611" s="2"/>
+      <c r="L1611" s="14"/>
+    </row>
+    <row r="1612" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1612" s="2">
+        <v>1048200208</v>
+      </c>
+      <c r="B1612" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1612" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1612" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1612" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1612" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1612" s="12">
+        <v>10</v>
+      </c>
+      <c r="H1612" s="12"/>
+      <c r="I1612" s="12"/>
+      <c r="J1612" s="13"/>
+      <c r="K1612" s="2"/>
+      <c r="L1612" s="14"/>
+    </row>
+    <row r="1613" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1613" s="2">
+        <v>1048200209</v>
+      </c>
+      <c r="B1613" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1613" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1613" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1613" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1613" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1613" s="12">
+        <v>15</v>
+      </c>
+      <c r="H1613" s="12"/>
+      <c r="I1613" s="12"/>
+      <c r="J1613" s="13"/>
+      <c r="K1613" s="2"/>
+      <c r="L1613" s="14"/>
+    </row>
+    <row r="1614" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1614" s="2">
+        <v>1048200210</v>
+      </c>
+      <c r="B1614" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1614" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1614" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1614" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1614" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1614" s="12">
+        <v>15</v>
+      </c>
+      <c r="H1614" s="12"/>
+      <c r="I1614" s="12"/>
+      <c r="J1614" s="13"/>
+      <c r="K1614" s="2"/>
+      <c r="L1614" s="14"/>
+    </row>
+    <row r="1615" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1615" s="2">
+        <v>1048200211</v>
+      </c>
+      <c r="B1615" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1615" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1615" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1615" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1615" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1615" s="12">
+        <v>35</v>
+      </c>
+      <c r="H1615" s="12"/>
+      <c r="I1615" s="12"/>
+      <c r="J1615" s="13"/>
+      <c r="K1615" s="2"/>
+      <c r="L1615" s="14"/>
+    </row>
+    <row r="1616" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1616" s="2">
+        <v>1048200301</v>
+      </c>
+      <c r="B1616" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1616" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1616" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1616" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1616" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1616" s="12">
+        <v>3</v>
+      </c>
+      <c r="H1616" s="12"/>
+      <c r="I1616" s="12"/>
+      <c r="J1616" s="13"/>
+      <c r="K1616" s="2"/>
+      <c r="L1616" s="14"/>
+    </row>
+    <row r="1617" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1617" s="2">
+        <v>1048200302</v>
+      </c>
+      <c r="B1617" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1617" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1617" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1617" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1617" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1617" s="12">
+        <v>3</v>
+      </c>
+      <c r="H1617" s="12"/>
+      <c r="I1617" s="12"/>
+      <c r="J1617" s="13"/>
+      <c r="K1617" s="2"/>
+      <c r="L1617" s="14"/>
+    </row>
+    <row r="1618" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1618" s="2">
+        <v>1048200303</v>
+      </c>
+      <c r="B1618" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1618" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1618" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1618" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1618" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1618" s="12">
+        <v>3</v>
+      </c>
+      <c r="H1618" s="12"/>
+      <c r="I1618" s="12"/>
+      <c r="J1618" s="13"/>
+      <c r="K1618" s="2"/>
+      <c r="L1618" s="14"/>
+    </row>
+    <row r="1619" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1619" s="2">
+        <v>1048200304</v>
+      </c>
+      <c r="B1619" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1619" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1619" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1619" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="F1619" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1619" s="12">
+        <v>5</v>
+      </c>
+      <c r="H1619" s="12"/>
+      <c r="I1619" s="12"/>
+      <c r="J1619" s="13"/>
+      <c r="K1619" s="2"/>
+      <c r="L1619" s="14"/>
+    </row>
+    <row r="1620" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1620" s="2">
+        <v>1048200305</v>
+      </c>
+      <c r="B1620" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1620" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1620" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1620" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1620" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1620" s="12">
+        <v>5</v>
+      </c>
+      <c r="H1620" s="12"/>
+      <c r="I1620" s="12"/>
+      <c r="J1620" s="13"/>
+      <c r="K1620" s="2"/>
+      <c r="L1620" s="14"/>
+    </row>
+    <row r="1621" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1621" s="2">
+        <v>1048200306</v>
+      </c>
+      <c r="B1621" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1621" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1621" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1621" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1621" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1621" s="12">
+        <v>10</v>
+      </c>
+      <c r="H1621" s="12"/>
+      <c r="I1621" s="12"/>
+      <c r="J1621" s="13"/>
+      <c r="K1621" s="2"/>
+      <c r="L1621" s="14"/>
+    </row>
+    <row r="1622" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1622" s="2">
+        <v>1048200307</v>
+      </c>
+      <c r="B1622" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1622" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1622" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1622" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1622" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1622" s="12">
+        <v>10</v>
+      </c>
+      <c r="H1622" s="12"/>
+      <c r="I1622" s="12"/>
+      <c r="J1622" s="13"/>
+      <c r="K1622" s="2"/>
+      <c r="L1622" s="14"/>
+    </row>
+    <row r="1623" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1623" s="2">
+        <v>1048200308</v>
+      </c>
+      <c r="B1623" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1623" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1623" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1623" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1623" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1623" s="12">
+        <v>15</v>
+      </c>
+      <c r="H1623" s="12"/>
+      <c r="I1623" s="12"/>
+      <c r="J1623" s="13"/>
+      <c r="K1623" s="2"/>
+      <c r="L1623" s="14"/>
+    </row>
+    <row r="1624" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1624" s="2">
+        <v>1048200309</v>
+      </c>
+      <c r="B1624" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1624" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1624" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1624" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1624" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1624" s="12">
+        <v>20</v>
+      </c>
+      <c r="H1624" s="12"/>
+      <c r="I1624" s="12"/>
+      <c r="J1624" s="13"/>
+      <c r="K1624" s="2"/>
+      <c r="L1624" s="14"/>
+    </row>
+    <row r="1625" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1625" s="2">
+        <v>1048200310</v>
+      </c>
+      <c r="B1625" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1625" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1625" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1625" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1625" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1625" s="12">
+        <v>30</v>
+      </c>
+      <c r="H1625" s="12"/>
+      <c r="I1625" s="12"/>
+      <c r="J1625" s="13"/>
+      <c r="K1625" s="2"/>
+      <c r="L1625" s="14"/>
+    </row>
+    <row r="1626" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1626" s="2">
+        <v>1048200311</v>
+      </c>
+      <c r="B1626" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1626" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1626" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1626" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1626" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1626" s="12">
+        <v>40</v>
+      </c>
+      <c r="H1626" s="12"/>
+      <c r="I1626" s="12"/>
+      <c r="J1626" s="13"/>
+      <c r="K1626" s="2"/>
+      <c r="L1626" s="14"/>
+    </row>
+    <row r="1627" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1627" s="2">
+        <v>1048200401</v>
+      </c>
+      <c r="B1627" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1627" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1627" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1627" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1627" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1627" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1627" s="12"/>
+      <c r="I1627" s="12"/>
+      <c r="J1627" s="13"/>
+      <c r="K1627" s="2"/>
+      <c r="L1627" s="14"/>
+    </row>
+    <row r="1628" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1628" s="2">
+        <v>1048200402</v>
+      </c>
+      <c r="B1628" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1628" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1628" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1628" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1628" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1628" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1628" s="12"/>
+      <c r="I1628" s="12"/>
+      <c r="J1628" s="13"/>
+      <c r="K1628" s="2"/>
+      <c r="L1628" s="14"/>
+    </row>
+    <row r="1629" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1629" s="2">
+        <v>1048200403</v>
+      </c>
+      <c r="B1629" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1629" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1629" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1629" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1629" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1629" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1629" s="12"/>
+      <c r="I1629" s="12"/>
+      <c r="J1629" s="13"/>
+      <c r="K1629" s="2"/>
+      <c r="L1629" s="14"/>
+    </row>
+    <row r="1630" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1630" s="2">
+        <v>1048200404</v>
+      </c>
+      <c r="B1630" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1630" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1630" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1630" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="F1630" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1630" s="12">
+        <v>8</v>
+      </c>
+      <c r="H1630" s="12"/>
+      <c r="I1630" s="12"/>
+      <c r="J1630" s="13"/>
+      <c r="K1630" s="2"/>
+      <c r="L1630" s="14"/>
+    </row>
+    <row r="1631" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1631" s="2">
+        <v>1048200405</v>
+      </c>
+      <c r="B1631" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1631" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1631" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1631" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1631" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1631" s="12">
+        <v>8</v>
+      </c>
+      <c r="H1631" s="12"/>
+      <c r="I1631" s="12"/>
+      <c r="J1631" s="13"/>
+      <c r="K1631" s="2"/>
+      <c r="L1631" s="14"/>
+    </row>
+    <row r="1632" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1632" s="2">
+        <v>1048200406</v>
+      </c>
+      <c r="B1632" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1632" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1632" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1632" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1632" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1632" s="12">
+        <v>15</v>
+      </c>
+      <c r="H1632" s="12"/>
+      <c r="I1632" s="12"/>
+      <c r="J1632" s="13"/>
+      <c r="K1632" s="2"/>
+      <c r="L1632" s="14"/>
+    </row>
+    <row r="1633" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1633" s="2">
+        <v>1048200407</v>
+      </c>
+      <c r="B1633" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1633" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1633" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1633" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1633" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1633" s="12">
+        <v>15</v>
+      </c>
+      <c r="H1633" s="12"/>
+      <c r="I1633" s="12"/>
+      <c r="J1633" s="13"/>
+      <c r="K1633" s="2"/>
+      <c r="L1633" s="14"/>
+    </row>
+    <row r="1634" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1634" s="2">
+        <v>1048200408</v>
+      </c>
+      <c r="B1634" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1634" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1634" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1634" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1634" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1634" s="12">
+        <v>20</v>
+      </c>
+      <c r="H1634" s="12"/>
+      <c r="I1634" s="12"/>
+      <c r="J1634" s="13"/>
+      <c r="K1634" s="2"/>
+      <c r="L1634" s="14"/>
+    </row>
+    <row r="1635" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1635" s="2">
+        <v>1048200409</v>
+      </c>
+      <c r="B1635" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1635" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1635" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1635" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1635" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1635" s="12">
+        <v>30</v>
+      </c>
+      <c r="H1635" s="12"/>
+      <c r="I1635" s="12"/>
+      <c r="J1635" s="13"/>
+      <c r="K1635" s="2"/>
+      <c r="L1635" s="14"/>
+    </row>
+    <row r="1636" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1636" s="2">
+        <v>1048200410</v>
+      </c>
+      <c r="B1636" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1636" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1636" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1636" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1636" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1636" s="12">
+        <v>40</v>
+      </c>
+      <c r="H1636" s="12"/>
+      <c r="I1636" s="12"/>
+      <c r="J1636" s="13"/>
+      <c r="K1636" s="2"/>
+      <c r="L1636" s="14"/>
+    </row>
+    <row r="1637" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1637" s="2">
+        <v>1048200411</v>
+      </c>
+      <c r="B1637" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1637" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1637" s="66">
+        <v>3</v>
+      </c>
+      <c r="E1637" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1637" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1637" s="12">
+        <v>50</v>
+      </c>
+      <c r="H1637" s="12"/>
+      <c r="I1637" s="12"/>
+      <c r="J1637" s="13"/>
+      <c r="K1637" s="2"/>
+      <c r="L1637" s="14"/>
+    </row>
+    <row r="1638" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1638" s="2">
+        <v>1048200501</v>
+      </c>
+      <c r="B1638" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1638" s="2"/>
+      <c r="D1638" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1638" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F1638" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1638" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1638" s="98">
+        <v>30480001</v>
+      </c>
+      <c r="I1638" s="12"/>
+      <c r="J1638" s="13"/>
+      <c r="K1638" s="2"/>
+      <c r="L1638" s="14"/>
+    </row>
+    <row r="1639" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1639" s="2">
+        <v>1048200502</v>
+      </c>
+      <c r="B1639" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1639" s="2"/>
+      <c r="D1639" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1639" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F1639" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1639" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1639" s="98">
+        <v>30480002</v>
+      </c>
+      <c r="I1639" s="12"/>
+      <c r="J1639" s="13"/>
+      <c r="K1639" s="2"/>
+      <c r="L1639" s="14"/>
+    </row>
+    <row r="1640" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1640" s="2">
+        <v>1048200503</v>
+      </c>
+      <c r="B1640" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1640" s="2"/>
+      <c r="D1640" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1640" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F1640" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1640" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1640" s="98">
+        <v>30480003</v>
+      </c>
+      <c r="I1640" s="12"/>
+      <c r="J1640" s="13"/>
+      <c r="K1640" s="2"/>
+      <c r="L1640" s="14"/>
+    </row>
+    <row r="1641" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1641" s="2">
+        <v>1048200601</v>
+      </c>
+      <c r="B1641" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1641" s="2"/>
+      <c r="D1641" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1641" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1641" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1641" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1641" s="12"/>
+      <c r="I1641" s="12"/>
+      <c r="J1641" s="13"/>
+      <c r="K1641" s="92">
+        <v>104800101</v>
+      </c>
+      <c r="L1641" s="91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1642" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1642" s="2">
+        <v>1048200602</v>
+      </c>
+      <c r="B1642" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1642" s="2"/>
+      <c r="D1642" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1642" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1642" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1642" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1642" s="12"/>
+      <c r="I1642" s="12"/>
+      <c r="J1642" s="13"/>
+      <c r="K1642" s="92">
+        <v>104800102</v>
+      </c>
+      <c r="L1642" s="91" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1643" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1643" s="2">
+        <v>1048200603</v>
+      </c>
+      <c r="B1643" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1643" s="2"/>
+      <c r="D1643" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1643" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1643" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1643" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1643" s="12"/>
+      <c r="I1643" s="12"/>
+      <c r="J1643" s="13"/>
+      <c r="K1643" s="92">
+        <v>104800103</v>
+      </c>
+      <c r="L1643" s="91" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1644" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1644" s="2">
+        <v>1048200604</v>
+      </c>
+      <c r="B1644" s="2">
+        <v>104800</v>
+      </c>
+      <c r="C1644" s="2"/>
+      <c r="D1644" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1644" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1644" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1644" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1644" s="12"/>
+      <c r="I1644" s="12"/>
+      <c r="J1644" s="13"/>
+      <c r="K1644" s="92">
+        <v>104800104</v>
+      </c>
+      <c r="L1644" s="91" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1645" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1645" s="10">
+        <v>1055110301</v>
+      </c>
+      <c r="B1645" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1645" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1645" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1645" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1645" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1645" s="12">
+        <v>2</v>
+      </c>
+      <c r="H1645" s="12"/>
+      <c r="I1645" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1645" s="13"/>
+      <c r="K1645" s="2"/>
+      <c r="L1645" s="14"/>
+    </row>
+    <row r="1646" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1646" s="10">
+        <v>1055110302</v>
+      </c>
+      <c r="B1646" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1646" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1646" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1646" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1646" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1646" s="12">
+        <v>5</v>
+      </c>
+      <c r="H1646" s="12"/>
+      <c r="I1646" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1646" s="13"/>
+      <c r="K1646" s="2"/>
+      <c r="L1646" s="14"/>
+    </row>
+    <row r="1647" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1647" s="10">
+        <v>1055110303</v>
+      </c>
+      <c r="B1647" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1647" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1647" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1647" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1647" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1647" s="12">
+        <v>8</v>
+      </c>
+      <c r="H1647" s="12"/>
+      <c r="I1647" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1647" s="13"/>
+      <c r="K1647" s="2"/>
+      <c r="L1647" s="14"/>
+    </row>
+    <row r="1648" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1648" s="10">
+        <v>1055110304</v>
+      </c>
+      <c r="B1648" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1648" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1648" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1648" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1648" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1648" s="12">
+        <v>10</v>
+      </c>
+      <c r="H1648" s="12"/>
+      <c r="I1648" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1648" s="13"/>
+      <c r="K1648" s="2"/>
+      <c r="L1648" s="14"/>
+    </row>
+    <row r="1649" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1649" s="10">
+        <v>1055110305</v>
+      </c>
+      <c r="B1649" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1649" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1649" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1649" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1649" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1649" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1649" s="12"/>
+      <c r="I1649" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1649" s="13"/>
+      <c r="K1649" s="2"/>
+      <c r="L1649" s="14"/>
+    </row>
+    <row r="1650" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1650" s="10">
+        <v>1055110306</v>
+      </c>
+      <c r="B1650" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1650" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1650" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1650" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F1650" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1650" s="12">
+        <v>15</v>
+      </c>
+      <c r="H1650" s="12"/>
+      <c r="I1650" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1650" s="13"/>
+      <c r="K1650" s="2"/>
+      <c r="L1650" s="14"/>
+    </row>
+    <row r="1651" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1651" s="10">
+        <v>1055110307</v>
+      </c>
+      <c r="B1651" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1651" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1651" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1651" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1651" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1651" s="12">
+        <v>20</v>
+      </c>
+      <c r="H1651" s="12"/>
+      <c r="I1651" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1651" s="13"/>
+      <c r="K1651" s="2"/>
+      <c r="L1651" s="14"/>
+    </row>
+    <row r="1652" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1652" s="10">
+        <v>1055110308</v>
+      </c>
+      <c r="B1652" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1652" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1652" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1652" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1652" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1652" s="12">
+        <v>25</v>
+      </c>
+      <c r="H1652" s="12"/>
+      <c r="I1652" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1652" s="13"/>
+      <c r="K1652" s="2"/>
+      <c r="L1652" s="14"/>
+    </row>
+    <row r="1653" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1653" s="10">
+        <v>1055140101</v>
+      </c>
+      <c r="B1653" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1653" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1653" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1653" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F1653" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1653" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1653" s="12"/>
+      <c r="I1653" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1653" s="13"/>
+      <c r="K1653" s="2">
+        <v>105501101</v>
+      </c>
+      <c r="L1653" s="14"/>
+    </row>
+    <row r="1654" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1654" s="10">
+        <v>1055140102</v>
+      </c>
+      <c r="B1654" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1654" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1654" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1654" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1654" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1654" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1654" s="12"/>
+      <c r="I1654" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1654" s="13"/>
+      <c r="K1654" s="2"/>
+      <c r="L1654" s="14"/>
+    </row>
+    <row r="1655" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1655" s="10">
+        <v>1055140103</v>
+      </c>
+      <c r="B1655" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1655" s="2">
+        <v>11</v>
+      </c>
+      <c r="D1655" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1655" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1655" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1655" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1655" s="12"/>
+      <c r="I1655" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1655" s="13"/>
+      <c r="K1655" s="2"/>
+      <c r="L1655" s="14"/>
+    </row>
+    <row r="1656" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1656" s="10">
+        <v>1055140104</v>
+      </c>
+      <c r="B1656" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1656" s="2">
+        <v>12</v>
+      </c>
+      <c r="D1656" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1656" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F1656" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1656" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1656" s="12"/>
+      <c r="I1656" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1656" s="13"/>
+      <c r="K1656" s="2"/>
+      <c r="L1656" s="14"/>
+    </row>
+    <row r="1657" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1657" s="10">
+        <v>1055140105</v>
+      </c>
+      <c r="B1657" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1657" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1657" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1657" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1657" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1657" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1657" s="12"/>
+      <c r="I1657" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1657" s="13"/>
+      <c r="K1657" s="2"/>
+      <c r="L1657" s="14"/>
+    </row>
+    <row r="1658" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1658" s="10">
+        <v>1055140106</v>
+      </c>
+      <c r="B1658" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1658" s="2">
+        <v>14</v>
+      </c>
+      <c r="D1658" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1658" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1658" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1658" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1658" s="12"/>
+      <c r="I1658" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1658" s="13"/>
+      <c r="K1658" s="2"/>
+      <c r="L1658" s="14"/>
+    </row>
+    <row r="1659" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1659" s="10">
+        <v>1055140107</v>
+      </c>
+      <c r="B1659" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1659" s="2">
+        <v>15</v>
+      </c>
+      <c r="D1659" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1659" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F1659" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1659" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1659" s="12"/>
+      <c r="I1659" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1659" s="13"/>
+      <c r="K1659" s="2"/>
+      <c r="L1659" s="14"/>
+    </row>
+    <row r="1660" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1660" s="10">
+        <v>1055140108</v>
+      </c>
+      <c r="B1660" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C1660" s="2">
+        <v>16</v>
+      </c>
+      <c r="D1660" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1660" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F1660" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1660" s="12">
+        <v>0</v>
+      </c>
+      <c r="H1660" s="12">
+        <v>30550101</v>
+      </c>
+      <c r="I1660" s="12">
+        <v>0</v>
+      </c>
+      <c r="J1660" s="13"/>
+      <c r="K1660" s="2"/>
+      <c r="L1660" s="14"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L1593" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L1644" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$1644</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$1660</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -881,7 +881,7 @@
     <t>免费游戏图标</t>
   </si>
   <si>
-    <t>30500001_30500002_30500003</t>
+    <t>30510001_30510002_30510003</t>
   </si>
   <si>
     <t>彩池图标1</t>
@@ -1405,11 +1405,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1422,6 +1417,11 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -52652,7 +52652,7 @@
       <c r="L1660" s="14"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L1644" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L1660" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8438913E-968D-4AFB-B2C0-54FCE189C565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E719E69D-731B-4494-83ED-86CF67C9D908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
@@ -50,6 +50,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">admin:
@@ -59,6 +60,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏ID，标识码</t>
@@ -72,6 +74,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -81,6 +84,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">该游戏的元素ID：图案1_图案2……
@@ -96,6 +100,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>vidisJW:</t>
@@ -104,6 +109,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -124,6 +130,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -133,6 +140,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>奖项数量</t>
@@ -146,6 +154,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -155,6 +164,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>中奖数量对应的倍数</t>
@@ -168,6 +178,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -177,6 +188,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该行元素的数量触发小游戏的ID，根据小游戏配置填写
@@ -191,6 +203,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -199,6 +212,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -214,6 +228,7 @@
             <b/>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -223,6 +238,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该数量如果其他元素组成时，根据其他元素的数量，倍率增加多少倍，格式为[{元素ID，数量，倍率}]，即该元素ID多少个后，对结果加成多少倍</t>
@@ -236,6 +252,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>大于0表示该中奖线触发对应jp奖池
@@ -250,6 +267,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -258,6 +276,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -273,6 +292,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -281,6 +301,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -295,6 +316,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -303,6 +325,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -316,7 +339,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="275">
   <si>
     <t>id</t>
   </si>
@@ -1161,35 +1184,41 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1197,18 +1226,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1222,12 +1254,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1235,6 +1269,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1242,6 +1277,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1249,6 +1285,7 @@
       <sz val="12"/>
       <color theme="10"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1257,6 +1294,7 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1264,6 +1302,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1271,22 +1310,26 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1772,7 +1815,21 @@
     <cellStyle name="超链接 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
     <cellStyle name="好_Sheet1" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="80">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.7993408001953185"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7076,7 +7133,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:N1660"/>
+  <dimension ref="A1:N1675"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.95" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" style="3"/>
@@ -53059,311 +53116,667 @@
       <c r="K1660" s="2"/>
       <c r="L1660" s="10"/>
     </row>
+    <row r="1661" spans="1:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1661" s="8">
+        <v>1055210301</v>
+      </c>
+      <c r="B1661" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1661" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1661" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1661" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1661" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1661" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1662" s="8">
+        <v>1055210302</v>
+      </c>
+      <c r="B1662" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1662" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1662" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1662" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1662" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1662" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1663" s="8">
+        <v>1055210303</v>
+      </c>
+      <c r="B1663" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1663" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1663" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1663" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1663" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1663" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1664" s="8">
+        <v>1055210304</v>
+      </c>
+      <c r="B1664" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1664" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1664" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1664" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1664" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1665" s="8">
+        <v>1055210305</v>
+      </c>
+      <c r="B1665" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1665" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1665" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1665" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1665" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1665" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1666" s="8">
+        <v>1055210306</v>
+      </c>
+      <c r="B1666" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1666" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1666" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1666" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F1666" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1666" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1667" s="8">
+        <v>1055210307</v>
+      </c>
+      <c r="B1667" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1667" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1667" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1667" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1667" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1667" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1668" s="8">
+        <v>1055210308</v>
+      </c>
+      <c r="B1668" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1668" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1668" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1668" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1668" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1668" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1669" s="8">
+        <v>1055240101</v>
+      </c>
+      <c r="B1669" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1669" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1669" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1669" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F1669" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1669" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1669" s="2">
+        <v>105502101</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1670" s="8">
+        <v>1055240102</v>
+      </c>
+      <c r="B1670" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1670" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1670" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1670" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1670" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1670" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1671" s="8">
+        <v>1055240103</v>
+      </c>
+      <c r="B1671" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1671" s="2">
+        <v>11</v>
+      </c>
+      <c r="D1671" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1671" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1671" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1671" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1672" s="8">
+        <v>1055240104</v>
+      </c>
+      <c r="B1672" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1672" s="2">
+        <v>12</v>
+      </c>
+      <c r="D1672" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1672" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F1672" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1672" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1673" s="8">
+        <v>1055240105</v>
+      </c>
+      <c r="B1673" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1673" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1673" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1673" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1673" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1673" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1674" s="8">
+        <v>1055240106</v>
+      </c>
+      <c r="B1674" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1674" s="2">
+        <v>14</v>
+      </c>
+      <c r="D1674" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1674" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1674" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1674" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1675" s="8">
+        <v>1055240107</v>
+      </c>
+      <c r="B1675" s="2">
+        <v>105502</v>
+      </c>
+      <c r="C1675" s="2">
+        <v>15</v>
+      </c>
+      <c r="D1675" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1675" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F1675" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1675" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:L1660" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="22" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A949:A1048576">
-    <cfRule type="duplicateValues" dxfId="77" priority="478"/>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A949:A1660 A1676:A1048576">
+    <cfRule type="duplicateValues" dxfId="79" priority="480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="76" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="75" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="74" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="73" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="72" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="71" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="70" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="69" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="68" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="67" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="66" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="65" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="64" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="63" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="62" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="61" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="60" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="59" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="58" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="57" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="56" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="55" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="54" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="53" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="52" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A209:A469">
-    <cfRule type="duplicateValues" dxfId="51" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A521:A799">
-    <cfRule type="duplicateValues" dxfId="50" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A800:A851">
-    <cfRule type="duplicateValues" dxfId="49" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A852:A897">
+    <cfRule type="duplicateValues" dxfId="50" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A898:A908">
+    <cfRule type="duplicateValues" dxfId="49" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A909:A919">
     <cfRule type="duplicateValues" dxfId="48" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A898:A908">
+  <conditionalFormatting sqref="A920:A930">
     <cfRule type="duplicateValues" dxfId="47" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A909:A919">
+  <conditionalFormatting sqref="A931:A941">
     <cfRule type="duplicateValues" dxfId="46" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A920:A930">
-    <cfRule type="duplicateValues" dxfId="45" priority="17"/>
+  <conditionalFormatting sqref="A942">
+    <cfRule type="duplicateValues" dxfId="45" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A931:A941">
-    <cfRule type="duplicateValues" dxfId="44" priority="16"/>
+  <conditionalFormatting sqref="A943">
+    <cfRule type="duplicateValues" dxfId="44" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A942">
+  <conditionalFormatting sqref="A944">
     <cfRule type="duplicateValues" dxfId="43" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A943">
+  <conditionalFormatting sqref="A945">
     <cfRule type="duplicateValues" dxfId="42" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A944">
+  <conditionalFormatting sqref="A946">
     <cfRule type="duplicateValues" dxfId="41" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A945">
+  <conditionalFormatting sqref="A947">
     <cfRule type="duplicateValues" dxfId="40" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A946">
+  <conditionalFormatting sqref="A948">
     <cfRule type="duplicateValues" dxfId="39" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A947">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A948">
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B257:B259 B261 B263 B265 B267 B269 B1333:L1048576">
-    <cfRule type="expression" dxfId="36" priority="57">
+  <conditionalFormatting sqref="B257:B259 B261 B263 B265 B267 B269 B1333:L1660 B1676:L1048576">
+    <cfRule type="expression" dxfId="38" priority="59">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209">
-    <cfRule type="expression" dxfId="35" priority="60">
+    <cfRule type="expression" dxfId="37" priority="62">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:G60">
-    <cfRule type="expression" dxfId="34" priority="160">
+    <cfRule type="expression" dxfId="36" priority="162">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:G178">
-    <cfRule type="expression" dxfId="33" priority="62">
+    <cfRule type="expression" dxfId="35" priority="64">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="32" priority="477">
+    <cfRule type="expression" dxfId="34" priority="479">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61:L134">
-    <cfRule type="expression" dxfId="31" priority="75">
+    <cfRule type="expression" dxfId="33" priority="77">
       <formula>MOD($B61,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B269:L307">
-    <cfRule type="expression" dxfId="30" priority="50">
+    <cfRule type="expression" dxfId="32" priority="52">
       <formula>MOD($B269,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B351:L548">
-    <cfRule type="expression" dxfId="29" priority="41">
+    <cfRule type="expression" dxfId="31" priority="43">
       <formula>MOD($B351,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762:L1328">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>MOD($B762,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C592 F592:G592">
-    <cfRule type="expression" dxfId="27" priority="490">
+    <cfRule type="expression" dxfId="29" priority="492">
       <formula>MOD($B605,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C593 F593:G593">
-    <cfRule type="expression" dxfId="26" priority="493">
+    <cfRule type="expression" dxfId="28" priority="495">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C594:C595 F594:G595">
-    <cfRule type="expression" dxfId="25" priority="494">
+    <cfRule type="expression" dxfId="27" priority="496">
       <formula>MOD($B606,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C596:C601 F596:G601">
-    <cfRule type="expression" dxfId="24" priority="491">
+    <cfRule type="expression" dxfId="26" priority="493">
       <formula>MOD($B610,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C602:C605">
-    <cfRule type="expression" dxfId="23" priority="492">
+    <cfRule type="expression" dxfId="25" priority="494">
       <formula>MOD($B618,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C606:C611">
-    <cfRule type="expression" dxfId="22" priority="489">
+    <cfRule type="expression" dxfId="24" priority="491">
       <formula>MOD($B623,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="21" priority="480">
+    <cfRule type="expression" dxfId="23" priority="482">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 F258:L258 D260 I260 D262 I262 D264 I264 D266 I266 D268 I268 I270 I272 I274 I276 I278 I280 I282 I284 I286 I288 I290 I292">
-    <cfRule type="expression" dxfId="20" priority="479">
+    <cfRule type="expression" dxfId="22" priority="481">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="19" priority="56">
+    <cfRule type="expression" dxfId="21" priority="58">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E549">
-    <cfRule type="expression" dxfId="18" priority="33">
+    <cfRule type="expression" dxfId="20" priority="35">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E592:E605">
-    <cfRule type="expression" dxfId="17" priority="34">
+    <cfRule type="expression" dxfId="19" priority="36">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755:G761">
-    <cfRule type="expression" dxfId="16" priority="495">
+    <cfRule type="expression" dxfId="18" priority="497">
       <formula>MOD($B754,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="15" priority="482">
+    <cfRule type="expression" dxfId="17" priority="484">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="14" priority="481">
+    <cfRule type="expression" dxfId="16" priority="483">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H592:H601">
-    <cfRule type="expression" dxfId="13" priority="35">
+    <cfRule type="expression" dxfId="15" priority="37">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H606:H608">
-    <cfRule type="expression" dxfId="12" priority="485">
+    <cfRule type="expression" dxfId="14" priority="487">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I205:L256 B210:H256">
-    <cfRule type="expression" dxfId="11" priority="59">
+    <cfRule type="expression" dxfId="13" priority="61">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J41:J42 L41:L42 B179:L204 B205:G208 B259:D268 F259:L268 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B549:D549 F549:L549 B550:L591 I592:L601 D592:D604 B592:B611 F602:J604 H605:L605 F605:F608 I606:L608 D609:G610 I609:J610 D611:J611 B612:L643 B644:K647 B648:L753 B754:F761 H754:L761 B1329:G1332 I1329:J1332 L1329:L1332">
-    <cfRule type="expression" dxfId="10" priority="476">
+    <cfRule type="expression" dxfId="12" priority="478">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J171:J172 L171:L172">
-    <cfRule type="expression" dxfId="9" priority="73">
+    <cfRule type="expression" dxfId="11" priority="75">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J43:L60">
-    <cfRule type="expression" dxfId="8" priority="162">
+    <cfRule type="expression" dxfId="10" priority="164">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J173:L178">
-    <cfRule type="expression" dxfId="7" priority="63">
+    <cfRule type="expression" dxfId="9" priority="65">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="6" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="5" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K347:L350">
-    <cfRule type="expression" dxfId="4" priority="48">
+    <cfRule type="expression" dxfId="6" priority="50">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K609:L611">
-    <cfRule type="expression" dxfId="3" priority="38">
+    <cfRule type="expression" dxfId="5" priority="40">
       <formula>MOD($B602,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L346">
-    <cfRule type="expression" dxfId="2" priority="483">
+    <cfRule type="expression" dxfId="4" priority="485">
       <formula>MOD($B350,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L644">
-    <cfRule type="expression" dxfId="1" priority="32">
+    <cfRule type="expression" dxfId="3" priority="34">
       <formula>MOD($B644,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L645:L647">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="2" priority="33">
       <formula>MOD($B638,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1661:A1675">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1661:L1675">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B1661,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -310,7 +310,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="281">
   <si>
     <t>id</t>
   </si>
@@ -1138,6 +1138,24 @@
   <si>
     <t>wheel</t>
   </si>
+  <si>
+    <t>蓝发女孩</t>
+  </si>
+  <si>
+    <t>泳圈女孩</t>
+  </si>
+  <si>
+    <t>Wild</t>
+  </si>
+  <si>
+    <t>冰淇淋</t>
+  </si>
+  <si>
+    <t>水枪男孩</t>
+  </si>
+  <si>
+    <t>墨镜男孩</t>
+  </si>
 </sst>
 </file>
 
@@ -1405,12 +1423,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2020,7 +2038,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2261,6 +2279,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top"/>
@@ -6580,7 +6601,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:N1675"/>
+  <dimension ref="A1:N1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="8"/>
@@ -16902,7 +16923,7 @@
       <c r="I346" s="9">
         <v>0</v>
       </c>
-      <c r="L346" s="85" t="s">
+      <c r="L346" s="86" t="s">
         <v>70</v>
       </c>
     </row>
@@ -52664,7 +52685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1665" customHeight="1" spans="1:11">
+    <row r="1665" customHeight="1" spans="1:12">
       <c r="A1665" s="7">
         <v>1055210305</v>
       </c>
@@ -52687,7 +52708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1666" customHeight="1" spans="1:11">
+    <row r="1666" customHeight="1" spans="1:12">
       <c r="A1666" s="7">
         <v>1055210306</v>
       </c>
@@ -52710,7 +52731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1667" customHeight="1" spans="1:11">
+    <row r="1667" customHeight="1" spans="1:12">
       <c r="A1667" s="7">
         <v>1055210307</v>
       </c>
@@ -52733,7 +52754,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1668" customHeight="1" spans="1:11">
+    <row r="1668" customHeight="1" spans="1:12">
       <c r="A1668" s="7">
         <v>1055210308</v>
       </c>
@@ -52756,7 +52777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1669" customHeight="1" spans="1:11">
+    <row r="1669" customHeight="1" spans="1:12">
       <c r="A1669" s="7">
         <v>1055240101</v>
       </c>
@@ -52782,7 +52803,7 @@
         <v>105502101</v>
       </c>
     </row>
-    <row r="1670" customHeight="1" spans="1:11">
+    <row r="1670" customHeight="1" spans="1:12">
       <c r="A1670" s="7">
         <v>1055240102</v>
       </c>
@@ -52805,7 +52826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1671" customHeight="1" spans="1:11">
+    <row r="1671" customHeight="1" spans="1:12">
       <c r="A1671" s="7">
         <v>1055240103</v>
       </c>
@@ -52828,7 +52849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1672" customHeight="1" spans="1:11">
+    <row r="1672" customHeight="1" spans="1:12">
       <c r="A1672" s="7">
         <v>1055240104</v>
       </c>
@@ -52851,7 +52872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1673" customHeight="1" spans="1:11">
+    <row r="1673" customHeight="1" spans="1:12">
       <c r="A1673" s="7">
         <v>1055240105</v>
       </c>
@@ -52874,7 +52895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1674" customHeight="1" spans="1:11">
+    <row r="1674" customHeight="1" spans="1:12">
       <c r="A1674" s="7">
         <v>1055240106</v>
       </c>
@@ -52897,7 +52918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1675" customHeight="1" spans="1:11">
+    <row r="1675" customHeight="1" spans="1:12">
       <c r="A1675" s="7">
         <v>1055240107</v>
       </c>
@@ -52918,6 +52939,2040 @@
       </c>
       <c r="G1675" s="9">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1676" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1676" s="2">
+        <v>1041700601</v>
+      </c>
+      <c r="B1676" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1676" s="2"/>
+      <c r="D1676" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1676" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1676" s="47">
+        <v>3</v>
+      </c>
+      <c r="G1676" s="9">
+        <v>10</v>
+      </c>
+      <c r="H1676" s="9"/>
+      <c r="I1676" s="9"/>
+      <c r="J1676" s="10"/>
+      <c r="K1676" s="2"/>
+      <c r="L1676" s="10"/>
+    </row>
+    <row r="1677" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1677" s="2">
+        <v>1041700602</v>
+      </c>
+      <c r="B1677" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1677" s="2"/>
+      <c r="D1677" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1677" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1677" s="55">
+        <v>3</v>
+      </c>
+      <c r="G1677" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1677" s="9"/>
+      <c r="I1677" s="9"/>
+      <c r="J1677" s="10"/>
+      <c r="K1677" s="2"/>
+      <c r="L1677" s="10"/>
+    </row>
+    <row r="1678" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1678" s="2">
+        <v>1041700603</v>
+      </c>
+      <c r="B1678" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1678" s="2"/>
+      <c r="D1678" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1678" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1678" s="55">
+        <v>3</v>
+      </c>
+      <c r="G1678" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1678" s="9"/>
+      <c r="I1678" s="9"/>
+      <c r="J1678" s="10"/>
+      <c r="K1678" s="2"/>
+      <c r="L1678" s="10"/>
+    </row>
+    <row r="1679" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1679" s="2">
+        <v>1041700604</v>
+      </c>
+      <c r="B1679" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1679" s="2"/>
+      <c r="D1679" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1679" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1679" s="55">
+        <v>3</v>
+      </c>
+      <c r="G1679" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1679" s="9"/>
+      <c r="I1679" s="9"/>
+      <c r="J1679" s="10"/>
+      <c r="K1679" s="2"/>
+      <c r="L1679" s="10"/>
+    </row>
+    <row r="1680" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1680" s="2">
+        <v>1041700605</v>
+      </c>
+      <c r="B1680" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1680" s="2"/>
+      <c r="D1680" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1680" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1680" s="55">
+        <v>3</v>
+      </c>
+      <c r="G1680" s="9">
+        <v>30</v>
+      </c>
+      <c r="H1680" s="9"/>
+      <c r="I1680" s="9"/>
+      <c r="J1680" s="10"/>
+      <c r="K1680" s="2"/>
+      <c r="L1680" s="10"/>
+    </row>
+    <row r="1681" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1681" s="2">
+        <v>1041700606</v>
+      </c>
+      <c r="B1681" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1681" s="2"/>
+      <c r="D1681" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1681" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1681" s="55">
+        <v>3</v>
+      </c>
+      <c r="G1681" s="9">
+        <v>40</v>
+      </c>
+      <c r="H1681" s="9"/>
+      <c r="I1681" s="9"/>
+      <c r="J1681" s="10"/>
+      <c r="K1681" s="2"/>
+      <c r="L1681" s="10"/>
+    </row>
+    <row r="1682" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1682" s="2">
+        <v>1041700607</v>
+      </c>
+      <c r="B1682" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1682" s="2"/>
+      <c r="D1682" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1682" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1682" s="55">
+        <v>3</v>
+      </c>
+      <c r="G1682" s="9">
+        <v>50</v>
+      </c>
+      <c r="H1682" s="9"/>
+      <c r="I1682" s="9"/>
+      <c r="J1682" s="10"/>
+      <c r="K1682" s="2"/>
+      <c r="L1682" s="10"/>
+    </row>
+    <row r="1683" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1683" s="2">
+        <v>1041700608</v>
+      </c>
+      <c r="B1683" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1683" s="2"/>
+      <c r="D1683" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1683" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1683" s="55">
+        <v>3</v>
+      </c>
+      <c r="G1683" s="9">
+        <v>60</v>
+      </c>
+      <c r="H1683" s="9"/>
+      <c r="I1683" s="9"/>
+      <c r="J1683" s="10"/>
+      <c r="K1683" s="2"/>
+      <c r="L1683" s="10"/>
+    </row>
+    <row r="1684" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1684" s="2">
+        <v>1041700701</v>
+      </c>
+      <c r="B1684" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1684" s="2"/>
+      <c r="D1684" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1684" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1684" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1684" s="9">
+        <v>40</v>
+      </c>
+      <c r="H1684" s="9"/>
+      <c r="I1684" s="9"/>
+      <c r="J1684" s="10"/>
+      <c r="K1684" s="2"/>
+      <c r="L1684" s="10"/>
+    </row>
+    <row r="1685" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1685" s="2">
+        <v>1041700702</v>
+      </c>
+      <c r="B1685" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1685" s="2"/>
+      <c r="D1685" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1685" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1685" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1685" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1685" s="9"/>
+      <c r="I1685" s="9"/>
+      <c r="J1685" s="10"/>
+      <c r="K1685" s="2"/>
+      <c r="L1685" s="10"/>
+    </row>
+    <row r="1686" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1686" s="2">
+        <v>1041700703</v>
+      </c>
+      <c r="B1686" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1686" s="2"/>
+      <c r="D1686" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1686" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1686" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1686" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1686" s="9"/>
+      <c r="I1686" s="9"/>
+      <c r="J1686" s="10"/>
+      <c r="K1686" s="2"/>
+      <c r="L1686" s="10"/>
+    </row>
+    <row r="1687" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1687" s="2">
+        <v>1041700704</v>
+      </c>
+      <c r="B1687" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1687" s="2"/>
+      <c r="D1687" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1687" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1687" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1687" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1687" s="9"/>
+      <c r="I1687" s="9"/>
+      <c r="J1687" s="10"/>
+      <c r="K1687" s="2"/>
+      <c r="L1687" s="10"/>
+    </row>
+    <row r="1688" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1688" s="2">
+        <v>1041700705</v>
+      </c>
+      <c r="B1688" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1688" s="2"/>
+      <c r="D1688" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1688" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1688" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1688" s="9">
+        <v>200</v>
+      </c>
+      <c r="H1688" s="9"/>
+      <c r="I1688" s="9"/>
+      <c r="J1688" s="10"/>
+      <c r="K1688" s="2"/>
+      <c r="L1688" s="10"/>
+    </row>
+    <row r="1689" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1689" s="2">
+        <v>1041700706</v>
+      </c>
+      <c r="B1689" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1689" s="2"/>
+      <c r="D1689" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1689" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1689" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1689" s="9">
+        <v>200</v>
+      </c>
+      <c r="H1689" s="9"/>
+      <c r="I1689" s="9"/>
+      <c r="J1689" s="10"/>
+      <c r="K1689" s="2"/>
+      <c r="L1689" s="10"/>
+    </row>
+    <row r="1690" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1690" s="2">
+        <v>1041700707</v>
+      </c>
+      <c r="B1690" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1690" s="2"/>
+      <c r="D1690" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1690" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1690" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1690" s="9">
+        <v>300</v>
+      </c>
+      <c r="H1690" s="9"/>
+      <c r="I1690" s="9"/>
+      <c r="J1690" s="10"/>
+      <c r="K1690" s="2"/>
+      <c r="L1690" s="10"/>
+    </row>
+    <row r="1691" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1691" s="2">
+        <v>1041700708</v>
+      </c>
+      <c r="B1691" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1691" s="2"/>
+      <c r="D1691" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1691" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1691" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1691" s="9">
+        <v>400</v>
+      </c>
+      <c r="H1691" s="9"/>
+      <c r="I1691" s="9"/>
+      <c r="J1691" s="10"/>
+      <c r="K1691" s="2"/>
+      <c r="L1691" s="10"/>
+    </row>
+    <row r="1692" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1692" s="2">
+        <v>1041700801</v>
+      </c>
+      <c r="B1692" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1692" s="2"/>
+      <c r="D1692" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1692" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1692" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1692" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1692" s="9"/>
+      <c r="I1692" s="9"/>
+      <c r="J1692" s="10"/>
+      <c r="K1692" s="2"/>
+      <c r="L1692" s="10"/>
+    </row>
+    <row r="1693" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1693" s="2">
+        <v>1041700802</v>
+      </c>
+      <c r="B1693" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1693" s="2"/>
+      <c r="D1693" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1693" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1693" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1693" s="9">
+        <v>150</v>
+      </c>
+      <c r="H1693" s="9"/>
+      <c r="I1693" s="9"/>
+      <c r="J1693" s="10"/>
+      <c r="K1693" s="2"/>
+      <c r="L1693" s="10"/>
+    </row>
+    <row r="1694" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1694" s="2">
+        <v>1041700803</v>
+      </c>
+      <c r="B1694" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1694" s="2"/>
+      <c r="D1694" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1694" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1694" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1694" s="9">
+        <v>150</v>
+      </c>
+      <c r="H1694" s="9"/>
+      <c r="I1694" s="9"/>
+      <c r="J1694" s="10"/>
+      <c r="K1694" s="2"/>
+      <c r="L1694" s="10"/>
+    </row>
+    <row r="1695" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1695" s="2">
+        <v>1041700804</v>
+      </c>
+      <c r="B1695" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1695" s="2"/>
+      <c r="D1695" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1695" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1695" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1695" s="9">
+        <v>150</v>
+      </c>
+      <c r="H1695" s="9"/>
+      <c r="I1695" s="9"/>
+      <c r="J1695" s="10"/>
+      <c r="K1695" s="2"/>
+      <c r="L1695" s="10"/>
+    </row>
+    <row r="1696" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1696" s="2">
+        <v>1041700805</v>
+      </c>
+      <c r="B1696" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1696" s="2"/>
+      <c r="D1696" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1696" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1696" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1696" s="9">
+        <v>200</v>
+      </c>
+      <c r="H1696" s="9"/>
+      <c r="I1696" s="9"/>
+      <c r="J1696" s="10"/>
+      <c r="K1696" s="2"/>
+      <c r="L1696" s="10"/>
+    </row>
+    <row r="1697" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1697" s="2">
+        <v>1041700806</v>
+      </c>
+      <c r="B1697" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1697" s="2"/>
+      <c r="D1697" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1697" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1697" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1697" s="9">
+        <v>300</v>
+      </c>
+      <c r="H1697" s="9"/>
+      <c r="I1697" s="9"/>
+      <c r="J1697" s="10"/>
+      <c r="K1697" s="2"/>
+      <c r="L1697" s="10"/>
+    </row>
+    <row r="1698" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1698" s="2">
+        <v>1041700807</v>
+      </c>
+      <c r="B1698" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1698" s="2"/>
+      <c r="D1698" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1698" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1698" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1698" s="9">
+        <v>400</v>
+      </c>
+      <c r="H1698" s="9"/>
+      <c r="I1698" s="9"/>
+      <c r="J1698" s="10"/>
+      <c r="K1698" s="2"/>
+      <c r="L1698" s="10"/>
+    </row>
+    <row r="1699" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1699" s="2">
+        <v>1041700808</v>
+      </c>
+      <c r="B1699" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1699" s="2"/>
+      <c r="D1699" s="55">
+        <v>3</v>
+      </c>
+      <c r="E1699" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1699" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1699" s="9">
+        <v>1000</v>
+      </c>
+      <c r="H1699" s="9"/>
+      <c r="I1699" s="9"/>
+      <c r="J1699" s="10"/>
+      <c r="K1699" s="2"/>
+      <c r="L1699" s="10"/>
+    </row>
+    <row r="1700" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1700" s="2">
+        <v>1041700901</v>
+      </c>
+      <c r="B1700" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1700" s="2"/>
+      <c r="D1700" s="55">
+        <v>4</v>
+      </c>
+      <c r="E1700" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1700" s="47">
+        <v>3</v>
+      </c>
+      <c r="G1700" s="9">
+        <v>0</v>
+      </c>
+      <c r="H1700" s="9"/>
+      <c r="I1700" s="9"/>
+      <c r="J1700" s="10"/>
+      <c r="K1700" s="2"/>
+      <c r="L1700" s="10"/>
+    </row>
+    <row r="1701" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1701" s="2">
+        <v>1041700902</v>
+      </c>
+      <c r="B1701" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1701" s="2"/>
+      <c r="D1701" s="55">
+        <v>4</v>
+      </c>
+      <c r="E1701" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1701" s="47">
+        <v>1</v>
+      </c>
+      <c r="G1701" s="9">
+        <v>0</v>
+      </c>
+      <c r="H1701" s="9"/>
+      <c r="I1701" s="9"/>
+      <c r="J1701" s="10"/>
+      <c r="K1701" s="80">
+        <v>104100101</v>
+      </c>
+      <c r="L1701" s="79" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1702" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1702" s="2">
+        <v>1041700903</v>
+      </c>
+      <c r="B1702" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1702" s="2"/>
+      <c r="D1702" s="55">
+        <v>4</v>
+      </c>
+      <c r="E1702" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1702" s="47">
+        <v>1</v>
+      </c>
+      <c r="G1702" s="9">
+        <v>0</v>
+      </c>
+      <c r="H1702" s="9"/>
+      <c r="I1702" s="9"/>
+      <c r="J1702" s="10"/>
+      <c r="K1702" s="80">
+        <v>104100102</v>
+      </c>
+      <c r="L1702" s="79" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1703" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1703" s="2">
+        <v>1041700904</v>
+      </c>
+      <c r="B1703" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1703" s="2"/>
+      <c r="D1703" s="55">
+        <v>4</v>
+      </c>
+      <c r="E1703" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1703" s="47">
+        <v>1</v>
+      </c>
+      <c r="G1703" s="9">
+        <v>0</v>
+      </c>
+      <c r="H1703" s="9"/>
+      <c r="I1703" s="9"/>
+      <c r="J1703" s="10"/>
+      <c r="K1703" s="80">
+        <v>104100103</v>
+      </c>
+      <c r="L1703" s="79" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1704" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1704" s="2">
+        <v>1041700905</v>
+      </c>
+      <c r="B1704" s="2">
+        <v>104100</v>
+      </c>
+      <c r="C1704" s="2"/>
+      <c r="D1704" s="55">
+        <v>4</v>
+      </c>
+      <c r="E1704" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1704" s="47">
+        <v>1</v>
+      </c>
+      <c r="G1704" s="9">
+        <v>0</v>
+      </c>
+      <c r="H1704" s="9"/>
+      <c r="I1704" s="9"/>
+      <c r="J1704" s="10"/>
+      <c r="K1704" s="80">
+        <v>104100104</v>
+      </c>
+      <c r="L1704" s="79" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1705" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1705" s="2">
+        <v>1042500101</v>
+      </c>
+      <c r="B1705" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1705" s="2"/>
+      <c r="D1705" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1705" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1705" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1705" s="9">
+        <v>2</v>
+      </c>
+      <c r="H1705" s="9"/>
+      <c r="I1705" s="9"/>
+      <c r="J1705" s="10"/>
+      <c r="K1705" s="2"/>
+      <c r="L1705" s="10"/>
+    </row>
+    <row r="1706" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1706" s="2">
+        <v>1042500102</v>
+      </c>
+      <c r="B1706" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1706" s="2"/>
+      <c r="D1706" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1706" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1706" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1706" s="9">
+        <v>2</v>
+      </c>
+      <c r="H1706" s="9"/>
+      <c r="I1706" s="9"/>
+      <c r="J1706" s="10"/>
+      <c r="K1706" s="2"/>
+      <c r="L1706" s="10"/>
+    </row>
+    <row r="1707" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1707" s="2">
+        <v>1042500103</v>
+      </c>
+      <c r="B1707" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1707" s="2"/>
+      <c r="D1707" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1707" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1707" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1707" s="9">
+        <v>3</v>
+      </c>
+      <c r="H1707" s="9"/>
+      <c r="I1707" s="9"/>
+      <c r="J1707" s="10"/>
+      <c r="K1707" s="2"/>
+      <c r="L1707" s="10"/>
+    </row>
+    <row r="1708" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1708" s="2">
+        <v>1042500104</v>
+      </c>
+      <c r="B1708" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1708" s="2"/>
+      <c r="D1708" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1708" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F1708" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1708" s="9">
+        <v>1</v>
+      </c>
+      <c r="H1708" s="9"/>
+      <c r="I1708" s="9"/>
+      <c r="J1708" s="10"/>
+      <c r="K1708" s="2"/>
+      <c r="L1708" s="10"/>
+    </row>
+    <row r="1709" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1709" s="2">
+        <v>1042500105</v>
+      </c>
+      <c r="B1709" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1709" s="2"/>
+      <c r="D1709" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1709" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1709" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1709" s="9">
+        <v>1</v>
+      </c>
+      <c r="H1709" s="9"/>
+      <c r="I1709" s="9"/>
+      <c r="J1709" s="10"/>
+      <c r="K1709" s="2"/>
+      <c r="L1709" s="10"/>
+    </row>
+    <row r="1710" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1710" s="2">
+        <v>1042500201</v>
+      </c>
+      <c r="B1710" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1710" s="2"/>
+      <c r="D1710" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1710" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1710" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1710" s="9">
+        <v>5</v>
+      </c>
+      <c r="H1710" s="9"/>
+      <c r="I1710" s="9"/>
+      <c r="J1710" s="10"/>
+      <c r="K1710" s="2"/>
+      <c r="L1710" s="10"/>
+    </row>
+    <row r="1711" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1711" s="2">
+        <v>1042500202</v>
+      </c>
+      <c r="B1711" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1711" s="2"/>
+      <c r="D1711" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1711" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1711" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1711" s="9">
+        <v>5</v>
+      </c>
+      <c r="H1711" s="9"/>
+      <c r="I1711" s="9"/>
+      <c r="J1711" s="10"/>
+      <c r="K1711" s="2"/>
+      <c r="L1711" s="10"/>
+    </row>
+    <row r="1712" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1712" s="2">
+        <v>1042500203</v>
+      </c>
+      <c r="B1712" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1712" s="2"/>
+      <c r="D1712" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1712" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1712" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1712" s="9">
+        <v>5</v>
+      </c>
+      <c r="H1712" s="9"/>
+      <c r="I1712" s="9"/>
+      <c r="J1712" s="10"/>
+      <c r="K1712" s="2"/>
+      <c r="L1712" s="10"/>
+    </row>
+    <row r="1713" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1713" s="2">
+        <v>1042500204</v>
+      </c>
+      <c r="B1713" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1713" s="2"/>
+      <c r="D1713" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1713" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1713" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1713" s="9">
+        <v>5</v>
+      </c>
+      <c r="H1713" s="9"/>
+      <c r="I1713" s="9"/>
+      <c r="J1713" s="10"/>
+      <c r="K1713" s="2"/>
+      <c r="L1713" s="10"/>
+    </row>
+    <row r="1714" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1714" s="2">
+        <v>1042500205</v>
+      </c>
+      <c r="B1714" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1714" s="2"/>
+      <c r="D1714" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1714" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1714" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1714" s="9">
+        <v>10</v>
+      </c>
+      <c r="H1714" s="9"/>
+      <c r="I1714" s="9"/>
+      <c r="J1714" s="10"/>
+      <c r="K1714" s="2"/>
+      <c r="L1714" s="10"/>
+    </row>
+    <row r="1715" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1715" s="2">
+        <v>1042500206</v>
+      </c>
+      <c r="B1715" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1715" s="2"/>
+      <c r="D1715" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1715" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1715" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1715" s="9">
+        <v>10</v>
+      </c>
+      <c r="H1715" s="9"/>
+      <c r="I1715" s="9"/>
+      <c r="J1715" s="10"/>
+      <c r="K1715" s="2"/>
+      <c r="L1715" s="10"/>
+    </row>
+    <row r="1716" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1716" s="2">
+        <v>1042500207</v>
+      </c>
+      <c r="B1716" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1716" s="2"/>
+      <c r="D1716" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1716" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F1716" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1716" s="9">
+        <v>10</v>
+      </c>
+      <c r="H1716" s="9"/>
+      <c r="I1716" s="9"/>
+      <c r="J1716" s="10"/>
+      <c r="K1716" s="2"/>
+      <c r="L1716" s="10"/>
+    </row>
+    <row r="1717" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1717" s="2">
+        <v>1042500208</v>
+      </c>
+      <c r="B1717" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1717" s="2"/>
+      <c r="D1717" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1717" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1717" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1717" s="9">
+        <v>10</v>
+      </c>
+      <c r="H1717" s="9"/>
+      <c r="I1717" s="9"/>
+      <c r="J1717" s="10"/>
+      <c r="K1717" s="2"/>
+      <c r="L1717" s="10"/>
+    </row>
+    <row r="1718" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1718" s="2">
+        <v>1042500209</v>
+      </c>
+      <c r="B1718" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1718" s="2"/>
+      <c r="D1718" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1718" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F1718" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1718" s="9">
+        <v>16</v>
+      </c>
+      <c r="H1718" s="9"/>
+      <c r="I1718" s="9"/>
+      <c r="J1718" s="10"/>
+      <c r="K1718" s="2"/>
+      <c r="L1718" s="10"/>
+    </row>
+    <row r="1719" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1719" s="2">
+        <v>1042500210</v>
+      </c>
+      <c r="B1719" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1719" s="2"/>
+      <c r="D1719" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1719" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1719" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1719" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1719" s="9"/>
+      <c r="I1719" s="9"/>
+      <c r="J1719" s="10"/>
+      <c r="K1719" s="2"/>
+      <c r="L1719" s="10"/>
+    </row>
+    <row r="1720" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1720" s="2">
+        <v>1042500211</v>
+      </c>
+      <c r="B1720" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1720" s="2"/>
+      <c r="D1720" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1720" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1720" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1720" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1720" s="9"/>
+      <c r="I1720" s="9"/>
+      <c r="J1720" s="10"/>
+      <c r="K1720" s="2"/>
+      <c r="L1720" s="10"/>
+    </row>
+    <row r="1721" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1721" s="2">
+        <v>1042500212</v>
+      </c>
+      <c r="B1721" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1721" s="2"/>
+      <c r="D1721" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1721" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F1721" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1721" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1721" s="9"/>
+      <c r="I1721" s="9"/>
+      <c r="J1721" s="10"/>
+      <c r="K1721" s="2"/>
+      <c r="L1721" s="10"/>
+    </row>
+    <row r="1722" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1722" s="2">
+        <v>1042500213</v>
+      </c>
+      <c r="B1722" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1722" s="2"/>
+      <c r="D1722" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1722" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1722" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1722" s="9">
+        <v>2</v>
+      </c>
+      <c r="H1722" s="9"/>
+      <c r="I1722" s="9"/>
+      <c r="J1722" s="10"/>
+      <c r="K1722" s="2"/>
+      <c r="L1722" s="10"/>
+    </row>
+    <row r="1723" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1723" s="2">
+        <v>1042500301</v>
+      </c>
+      <c r="B1723" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1723" s="2"/>
+      <c r="D1723" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1723" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1723" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1723" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1723" s="9"/>
+      <c r="I1723" s="9"/>
+      <c r="J1723" s="10"/>
+      <c r="K1723" s="2"/>
+      <c r="L1723" s="10"/>
+    </row>
+    <row r="1724" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1724" s="2">
+        <v>1042500302</v>
+      </c>
+      <c r="B1724" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1724" s="2"/>
+      <c r="D1724" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1724" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1724" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1724" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1724" s="9"/>
+      <c r="I1724" s="9"/>
+      <c r="J1724" s="10"/>
+      <c r="K1724" s="2"/>
+      <c r="L1724" s="10"/>
+    </row>
+    <row r="1725" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1725" s="2">
+        <v>1042500303</v>
+      </c>
+      <c r="B1725" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1725" s="2"/>
+      <c r="D1725" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1725" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1725" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1725" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1725" s="9"/>
+      <c r="I1725" s="9"/>
+      <c r="J1725" s="10"/>
+      <c r="K1725" s="2"/>
+      <c r="L1725" s="10"/>
+    </row>
+    <row r="1726" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1726" s="2">
+        <v>1042500304</v>
+      </c>
+      <c r="B1726" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1726" s="2"/>
+      <c r="D1726" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1726" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1726" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1726" s="9">
+        <v>20</v>
+      </c>
+      <c r="H1726" s="9"/>
+      <c r="I1726" s="9"/>
+      <c r="J1726" s="10"/>
+      <c r="K1726" s="2"/>
+      <c r="L1726" s="10"/>
+    </row>
+    <row r="1727" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1727" s="2">
+        <v>1042500305</v>
+      </c>
+      <c r="B1727" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1727" s="2"/>
+      <c r="D1727" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1727" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1727" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1727" s="9">
+        <v>50</v>
+      </c>
+      <c r="H1727" s="9"/>
+      <c r="I1727" s="9"/>
+      <c r="J1727" s="10"/>
+      <c r="K1727" s="2"/>
+      <c r="L1727" s="10"/>
+    </row>
+    <row r="1728" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1728" s="2">
+        <v>1042500306</v>
+      </c>
+      <c r="B1728" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1728" s="2"/>
+      <c r="D1728" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1728" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1728" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1728" s="9">
+        <v>50</v>
+      </c>
+      <c r="H1728" s="9"/>
+      <c r="I1728" s="9"/>
+      <c r="J1728" s="10"/>
+      <c r="K1728" s="2"/>
+      <c r="L1728" s="10"/>
+    </row>
+    <row r="1729" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1729" s="2">
+        <v>1042500307</v>
+      </c>
+      <c r="B1729" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1729" s="2"/>
+      <c r="D1729" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1729" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F1729" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1729" s="9">
+        <v>50</v>
+      </c>
+      <c r="H1729" s="9"/>
+      <c r="I1729" s="9"/>
+      <c r="J1729" s="10"/>
+      <c r="K1729" s="2"/>
+      <c r="L1729" s="10"/>
+    </row>
+    <row r="1730" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1730" s="2">
+        <v>1042500308</v>
+      </c>
+      <c r="B1730" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1730" s="2"/>
+      <c r="D1730" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1730" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1730" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1730" s="9">
+        <v>80</v>
+      </c>
+      <c r="H1730" s="9"/>
+      <c r="I1730" s="9"/>
+      <c r="J1730" s="10"/>
+      <c r="K1730" s="2"/>
+      <c r="L1730" s="10"/>
+    </row>
+    <row r="1731" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1731" s="2">
+        <v>1042500309</v>
+      </c>
+      <c r="B1731" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1731" s="2"/>
+      <c r="D1731" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1731" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F1731" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1731" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1731" s="9"/>
+      <c r="I1731" s="9"/>
+      <c r="J1731" s="10"/>
+      <c r="K1731" s="2"/>
+      <c r="L1731" s="10"/>
+    </row>
+    <row r="1732" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1732" s="2">
+        <v>1042500310</v>
+      </c>
+      <c r="B1732" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1732" s="2"/>
+      <c r="D1732" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1732" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1732" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1732" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1732" s="9"/>
+      <c r="I1732" s="9"/>
+      <c r="J1732" s="10"/>
+      <c r="K1732" s="2"/>
+      <c r="L1732" s="10"/>
+    </row>
+    <row r="1733" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1733" s="2">
+        <v>1042500311</v>
+      </c>
+      <c r="B1733" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1733" s="2"/>
+      <c r="D1733" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1733" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1733" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1733" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1733" s="9"/>
+      <c r="I1733" s="9"/>
+      <c r="J1733" s="10"/>
+      <c r="K1733" s="2"/>
+      <c r="L1733" s="10"/>
+    </row>
+    <row r="1734" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1734" s="2">
+        <v>1042500312</v>
+      </c>
+      <c r="B1734" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1734" s="2"/>
+      <c r="D1734" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1734" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F1734" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1734" s="9">
+        <v>222</v>
+      </c>
+      <c r="H1734" s="9"/>
+      <c r="I1734" s="9"/>
+      <c r="J1734" s="10"/>
+      <c r="K1734" s="2"/>
+      <c r="L1734" s="10"/>
+    </row>
+    <row r="1735" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1735" s="2">
+        <v>1042500313</v>
+      </c>
+      <c r="B1735" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1735" s="2"/>
+      <c r="D1735" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1735" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1735" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1735" s="9">
+        <v>30</v>
+      </c>
+      <c r="H1735" s="9"/>
+      <c r="I1735" s="9"/>
+      <c r="J1735" s="10"/>
+      <c r="K1735" s="2"/>
+      <c r="L1735" s="10"/>
+    </row>
+    <row r="1736" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1736" s="2">
+        <v>1042500401</v>
+      </c>
+      <c r="B1736" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1736" s="2"/>
+      <c r="D1736" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1736" s="82">
+        <v>9</v>
+      </c>
+      <c r="F1736" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1736" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1736" s="9"/>
+      <c r="I1736" s="9"/>
+      <c r="J1736" s="10"/>
+      <c r="K1736" s="2"/>
+      <c r="L1736" s="10"/>
+    </row>
+    <row r="1737" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1737" s="2">
+        <v>1042500402</v>
+      </c>
+      <c r="B1737" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1737" s="2"/>
+      <c r="D1737" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1737" s="85">
+        <v>10</v>
+      </c>
+      <c r="F1737" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1737" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1737" s="9"/>
+      <c r="I1737" s="9"/>
+      <c r="J1737" s="10"/>
+      <c r="K1737" s="2"/>
+      <c r="L1737" s="10"/>
+    </row>
+    <row r="1738" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1738" s="2">
+        <v>1042500403</v>
+      </c>
+      <c r="B1738" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1738" s="2"/>
+      <c r="D1738" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1738" s="85" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1738" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1738" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1738" s="9"/>
+      <c r="I1738" s="9"/>
+      <c r="J1738" s="10"/>
+      <c r="K1738" s="2"/>
+      <c r="L1738" s="10"/>
+    </row>
+    <row r="1739" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1739" s="2">
+        <v>1042500404</v>
+      </c>
+      <c r="B1739" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1739" s="2"/>
+      <c r="D1739" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1739" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1739" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1739" s="9">
+        <v>100</v>
+      </c>
+      <c r="H1739" s="9"/>
+      <c r="I1739" s="9"/>
+      <c r="J1739" s="10"/>
+      <c r="K1739" s="2"/>
+      <c r="L1739" s="10"/>
+    </row>
+    <row r="1740" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1740" s="2">
+        <v>1042500405</v>
+      </c>
+      <c r="B1740" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1740" s="2"/>
+      <c r="D1740" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1740" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1740" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1740" s="9">
+        <v>130</v>
+      </c>
+      <c r="H1740" s="9"/>
+      <c r="I1740" s="9"/>
+      <c r="J1740" s="10"/>
+      <c r="K1740" s="2"/>
+      <c r="L1740" s="10"/>
+    </row>
+    <row r="1741" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1741" s="2">
+        <v>1042500406</v>
+      </c>
+      <c r="B1741" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1741" s="2"/>
+      <c r="D1741" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1741" s="85" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1741" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1741" s="9">
+        <v>130</v>
+      </c>
+      <c r="H1741" s="9"/>
+      <c r="I1741" s="9"/>
+      <c r="J1741" s="10"/>
+      <c r="K1741" s="2"/>
+      <c r="L1741" s="10"/>
+    </row>
+    <row r="1742" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1742" s="2">
+        <v>1042500407</v>
+      </c>
+      <c r="B1742" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1742" s="2"/>
+      <c r="D1742" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1742" s="85" t="s">
+        <v>278</v>
+      </c>
+      <c r="F1742" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1742" s="9">
+        <v>200</v>
+      </c>
+      <c r="H1742" s="9"/>
+      <c r="I1742" s="9"/>
+      <c r="J1742" s="10"/>
+      <c r="K1742" s="2"/>
+      <c r="L1742" s="10"/>
+    </row>
+    <row r="1743" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1743" s="2">
+        <v>1042500408</v>
+      </c>
+      <c r="B1743" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1743" s="2"/>
+      <c r="D1743" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1743" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1743" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1743" s="9">
+        <v>300</v>
+      </c>
+      <c r="H1743" s="9"/>
+      <c r="I1743" s="9"/>
+      <c r="J1743" s="10"/>
+      <c r="K1743" s="2"/>
+      <c r="L1743" s="10"/>
+    </row>
+    <row r="1744" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1744" s="2">
+        <v>1042500409</v>
+      </c>
+      <c r="B1744" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1744" s="2"/>
+      <c r="D1744" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1744" s="85" t="s">
+        <v>280</v>
+      </c>
+      <c r="F1744" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1744" s="9">
+        <v>400</v>
+      </c>
+      <c r="H1744" s="9"/>
+      <c r="I1744" s="9"/>
+      <c r="J1744" s="10"/>
+      <c r="K1744" s="2"/>
+      <c r="L1744" s="10"/>
+    </row>
+    <row r="1745" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1745" s="2">
+        <v>1042500410</v>
+      </c>
+      <c r="B1745" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1745" s="2"/>
+      <c r="D1745" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1745" s="85" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1745" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1745" s="9">
+        <v>800</v>
+      </c>
+      <c r="H1745" s="9"/>
+      <c r="I1745" s="9"/>
+      <c r="J1745" s="10"/>
+      <c r="K1745" s="2"/>
+      <c r="L1745" s="10"/>
+    </row>
+    <row r="1746" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1746" s="2">
+        <v>1042500411</v>
+      </c>
+      <c r="B1746" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1746" s="2"/>
+      <c r="D1746" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1746" s="85" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1746" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1746" s="9">
+        <v>800</v>
+      </c>
+      <c r="H1746" s="9"/>
+      <c r="I1746" s="9"/>
+      <c r="J1746" s="10"/>
+      <c r="K1746" s="2"/>
+      <c r="L1746" s="10"/>
+    </row>
+    <row r="1747" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1747" s="2">
+        <v>1042500412</v>
+      </c>
+      <c r="B1747" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1747" s="2"/>
+      <c r="D1747" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1747" s="85" t="s">
+        <v>277</v>
+      </c>
+      <c r="F1747" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1747" s="9">
+        <v>1111</v>
+      </c>
+      <c r="H1747" s="9"/>
+      <c r="I1747" s="9"/>
+      <c r="J1747" s="10"/>
+      <c r="K1747" s="2"/>
+      <c r="L1747" s="10"/>
+    </row>
+    <row r="1748" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1748" s="2">
+        <v>1042500501</v>
+      </c>
+      <c r="B1748" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1748" s="2"/>
+      <c r="D1748" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1748" s="85" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1748" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1748" s="9">
+        <v>200</v>
+      </c>
+      <c r="H1748" s="9"/>
+      <c r="I1748" s="9"/>
+      <c r="J1748" s="10"/>
+      <c r="K1748" s="2"/>
+      <c r="L1748" s="10"/>
+    </row>
+    <row r="1749" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1749" s="2">
+        <v>1042500502</v>
+      </c>
+      <c r="B1749" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1749" s="2"/>
+      <c r="D1749" s="55">
+        <v>4</v>
+      </c>
+      <c r="E1749" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1749" s="47">
+        <v>1</v>
+      </c>
+      <c r="G1749" s="9">
+        <v>0</v>
+      </c>
+      <c r="H1749" s="9"/>
+      <c r="I1749" s="9"/>
+      <c r="J1749" s="10"/>
+      <c r="K1749" s="80">
+        <v>104200101</v>
+      </c>
+      <c r="L1749" s="79" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1750" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1750" s="2">
+        <v>1042500503</v>
+      </c>
+      <c r="B1750" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1750" s="2"/>
+      <c r="D1750" s="55">
+        <v>4</v>
+      </c>
+      <c r="E1750" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1750" s="47">
+        <v>1</v>
+      </c>
+      <c r="G1750" s="9">
+        <v>0</v>
+      </c>
+      <c r="H1750" s="9"/>
+      <c r="I1750" s="9"/>
+      <c r="J1750" s="10"/>
+      <c r="K1750" s="80">
+        <v>104200102</v>
+      </c>
+      <c r="L1750" s="79" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1751" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1751" s="2">
+        <v>1042500504</v>
+      </c>
+      <c r="B1751" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1751" s="2"/>
+      <c r="D1751" s="55">
+        <v>4</v>
+      </c>
+      <c r="E1751" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1751" s="47">
+        <v>1</v>
+      </c>
+      <c r="G1751" s="9">
+        <v>0</v>
+      </c>
+      <c r="H1751" s="9"/>
+      <c r="I1751" s="9"/>
+      <c r="J1751" s="10"/>
+      <c r="K1751" s="80">
+        <v>104200103</v>
+      </c>
+      <c r="L1751" s="79" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1752" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1752" s="2">
+        <v>1042500505</v>
+      </c>
+      <c r="B1752" s="2">
+        <v>104200</v>
+      </c>
+      <c r="C1752" s="2"/>
+      <c r="D1752" s="55">
+        <v>4</v>
+      </c>
+      <c r="E1752" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1752" s="47">
+        <v>1</v>
+      </c>
+      <c r="G1752" s="9">
+        <v>0</v>
+      </c>
+      <c r="H1752" s="9"/>
+      <c r="I1752" s="9"/>
+      <c r="J1752" s="10"/>
+      <c r="K1752" s="80">
+        <v>104200104</v>
+      </c>
+      <c r="L1752" s="79" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$1675</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$1752</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1423,12 +1423,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2397,7 +2397,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="0"/>
+          <a:off x="928370" y="0"/>
           <a:ext cx="9361170" cy="9781540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2443,7 +2443,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2489,7 +2489,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2535,7 +2535,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2581,7 +2581,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2627,7 +2627,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2673,7 +2673,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2719,7 +2719,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2765,7 +2765,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2811,7 +2811,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2857,7 +2857,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2903,7 +2903,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2949,7 +2949,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2995,7 +2995,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3041,7 +3041,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3087,7 +3087,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3133,7 +3133,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3179,7 +3179,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3225,7 +3225,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3271,7 +3271,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3317,7 +3317,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="1203325"/>
+          <a:off x="928370" y="1203325"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3363,7 +3363,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3409,7 +3409,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3455,7 +3455,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3501,7 +3501,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3547,7 +3547,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3593,7 +3593,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3639,7 +3639,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3685,7 +3685,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3731,7 +3731,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3777,7 +3777,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3823,7 +3823,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3869,7 +3869,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3915,7 +3915,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3961,7 +3961,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4007,7 +4007,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4053,7 +4053,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4099,7 +4099,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4145,7 +4145,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4191,7 +4191,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4237,7 +4237,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4283,7 +4283,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4329,7 +4329,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4375,7 +4375,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4421,7 +4421,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4467,7 +4467,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4513,7 +4513,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4559,7 +4559,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4605,7 +4605,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4651,7 +4651,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="10240010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4697,7 +4697,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4743,7 +4743,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9972040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4789,7 +4789,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4835,7 +4835,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4881,7 +4881,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4927,7 +4927,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="10240010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4973,7 +4973,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5019,7 +5019,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5065,7 +5065,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5111,7 +5111,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9781540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5157,7 +5157,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5203,7 +5203,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5249,7 +5249,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5295,7 +5295,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5341,7 +5341,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5387,7 +5387,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="9626600"/>
+          <a:off x="928370" y="9626600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5433,7 +5433,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5479,7 +5479,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5525,7 +5525,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5571,7 +5571,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5617,7 +5617,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5663,7 +5663,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5709,7 +5709,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5755,7 +5755,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5801,7 +5801,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5847,7 +5847,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5893,7 +5893,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5939,7 +5939,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5985,7 +5985,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6031,7 +6031,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6077,7 +6077,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6123,7 +6123,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6169,7 +6169,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6215,7 +6215,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6261,7 +6261,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6307,7 +6307,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="32489775"/>
+          <a:off x="928370" y="32489775"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6602,20 +6602,15 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:N1752"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.95" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.1833333333333" defaultRowHeight="18.95" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="8"/>
-    <col min="2" max="2" width="11" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.875" style="9" customWidth="1"/>
-    <col min="8" max="9" width="19.125" style="9" customWidth="1"/>
-    <col min="10" max="10" width="66.625" style="10" customWidth="1"/>
-    <col min="11" max="11" width="11.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.5" style="10" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="12.1833333333333" style="8" customWidth="1"/>
+    <col min="2" max="6" width="12.1833333333333" style="2" customWidth="1"/>
+    <col min="7" max="9" width="12.1833333333333" style="9" customWidth="1"/>
+    <col min="10" max="10" width="12.1833333333333" style="10" customWidth="1"/>
+    <col min="11" max="11" width="12.1833333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.1833333333333" style="10" customWidth="1"/>
+    <col min="13" max="16384" width="12.1833333333333" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
@@ -23587,7 +23582,6 @@
     </row>
     <row r="612" customHeight="1" spans="1:12">
       <c r="A612" s="2">
-        <f t="shared" ref="A612:A641" si="24">(B612)*10000+C612+F612*100+D612*100000</f>
         <v>1038100301</v>
       </c>
       <c r="B612" s="2">
@@ -23603,7 +23597,7 @@
         <v>3</v>
       </c>
       <c r="G612" s="9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I612" s="7">
         <v>0</v>
@@ -23611,7 +23605,6 @@
     </row>
     <row r="613" customHeight="1" spans="1:12">
       <c r="A613" s="2">
-        <f t="shared" si="24"/>
         <v>1038100302</v>
       </c>
       <c r="B613" s="2">
@@ -23627,7 +23620,7 @@
         <v>3</v>
       </c>
       <c r="G613" s="9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I613" s="9">
         <v>0</v>
@@ -23635,7 +23628,6 @@
     </row>
     <row r="614" customHeight="1" spans="1:12">
       <c r="A614" s="2">
-        <f t="shared" si="24"/>
         <v>1038100303</v>
       </c>
       <c r="B614" s="2">
@@ -23651,7 +23643,7 @@
         <v>3</v>
       </c>
       <c r="G614" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I614" s="7">
         <v>0</v>
@@ -23659,7 +23651,6 @@
     </row>
     <row r="615" customHeight="1" spans="1:12">
       <c r="A615" s="2">
-        <f t="shared" si="24"/>
         <v>1038100304</v>
       </c>
       <c r="B615" s="2">
@@ -23675,7 +23666,7 @@
         <v>3</v>
       </c>
       <c r="G615" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I615" s="9">
         <v>0</v>
@@ -23683,7 +23674,6 @@
     </row>
     <row r="616" customHeight="1" spans="1:12">
       <c r="A616" s="2">
-        <f t="shared" si="24"/>
         <v>1038100305</v>
       </c>
       <c r="B616" s="2">
@@ -23699,7 +23689,7 @@
         <v>3</v>
       </c>
       <c r="G616" s="9">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I616" s="7">
         <v>0</v>
@@ -23707,7 +23697,6 @@
     </row>
     <row r="617" customHeight="1" spans="1:12">
       <c r="A617" s="2">
-        <f t="shared" si="24"/>
         <v>1038100306</v>
       </c>
       <c r="B617" s="2">
@@ -23723,7 +23712,7 @@
         <v>3</v>
       </c>
       <c r="G617" s="9">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I617" s="9">
         <v>0</v>
@@ -23731,7 +23720,6 @@
     </row>
     <row r="618" customHeight="1" spans="1:12">
       <c r="A618" s="2">
-        <f t="shared" si="24"/>
         <v>1038100307</v>
       </c>
       <c r="B618" s="2">
@@ -23747,7 +23735,7 @@
         <v>3</v>
       </c>
       <c r="G618" s="9">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I618" s="7">
         <v>0</v>
@@ -23755,7 +23743,6 @@
     </row>
     <row r="619" customHeight="1" spans="1:12">
       <c r="A619" s="2">
-        <f t="shared" si="24"/>
         <v>1038100308</v>
       </c>
       <c r="B619" s="2">
@@ -23771,7 +23758,7 @@
         <v>3</v>
       </c>
       <c r="G619" s="9">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I619" s="9">
         <v>0</v>
@@ -23779,7 +23766,6 @@
     </row>
     <row r="620" customHeight="1" spans="1:12">
       <c r="A620" s="2">
-        <f t="shared" si="24"/>
         <v>1038100309</v>
       </c>
       <c r="B620" s="2">
@@ -23795,7 +23781,7 @@
         <v>3</v>
       </c>
       <c r="G620" s="9">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I620" s="7">
         <v>0</v>
@@ -23803,7 +23789,6 @@
     </row>
     <row r="621" customHeight="1" spans="1:12">
       <c r="A621" s="2">
-        <f t="shared" si="24"/>
         <v>1038100310</v>
       </c>
       <c r="B621" s="2">
@@ -23819,7 +23804,7 @@
         <v>3</v>
       </c>
       <c r="G621" s="9">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="I621" s="9">
         <v>0</v>
@@ -23827,7 +23812,6 @@
     </row>
     <row r="622" customHeight="1" spans="1:12">
       <c r="A622" s="2">
-        <f t="shared" si="24"/>
         <v>1038100401</v>
       </c>
       <c r="B622" s="2">
@@ -23843,7 +23827,7 @@
         <v>4</v>
       </c>
       <c r="G622" s="9">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="I622" s="7">
         <v>0</v>
@@ -23851,7 +23835,6 @@
     </row>
     <row r="623" customHeight="1" spans="1:12">
       <c r="A623" s="2">
-        <f t="shared" si="24"/>
         <v>1038100402</v>
       </c>
       <c r="B623" s="2">
@@ -23867,7 +23850,7 @@
         <v>4</v>
       </c>
       <c r="G623" s="9">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="I623" s="9">
         <v>0</v>
@@ -23875,7 +23858,6 @@
     </row>
     <row r="624" customHeight="1" spans="1:12">
       <c r="A624" s="2">
-        <f t="shared" si="24"/>
         <v>1038100403</v>
       </c>
       <c r="B624" s="2">
@@ -23891,7 +23873,7 @@
         <v>4</v>
       </c>
       <c r="G624" s="9">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="I624" s="7">
         <v>0</v>
@@ -23899,7 +23881,6 @@
     </row>
     <row r="625" customHeight="1" spans="1:9">
       <c r="A625" s="2">
-        <f t="shared" si="24"/>
         <v>1038100404</v>
       </c>
       <c r="B625" s="2">
@@ -23915,7 +23896,7 @@
         <v>4</v>
       </c>
       <c r="G625" s="9">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="I625" s="9">
         <v>0</v>
@@ -23923,7 +23904,6 @@
     </row>
     <row r="626" customHeight="1" spans="1:9">
       <c r="A626" s="2">
-        <f t="shared" si="24"/>
         <v>1038100405</v>
       </c>
       <c r="B626" s="2">
@@ -23939,7 +23919,7 @@
         <v>4</v>
       </c>
       <c r="G626" s="9">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="I626" s="7">
         <v>0</v>
@@ -23947,7 +23927,6 @@
     </row>
     <row r="627" customHeight="1" spans="1:9">
       <c r="A627" s="2">
-        <f t="shared" si="24"/>
         <v>1038100406</v>
       </c>
       <c r="B627" s="2">
@@ -23963,7 +23942,7 @@
         <v>4</v>
       </c>
       <c r="G627" s="9">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="I627" s="9">
         <v>0</v>
@@ -23971,7 +23950,6 @@
     </row>
     <row r="628" customHeight="1" spans="1:9">
       <c r="A628" s="2">
-        <f t="shared" si="24"/>
         <v>1038100407</v>
       </c>
       <c r="B628" s="2">
@@ -23987,7 +23965,7 @@
         <v>4</v>
       </c>
       <c r="G628" s="9">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="I628" s="7">
         <v>0</v>
@@ -23995,7 +23973,6 @@
     </row>
     <row r="629" customHeight="1" spans="1:9">
       <c r="A629" s="2">
-        <f t="shared" si="24"/>
         <v>1038100408</v>
       </c>
       <c r="B629" s="2">
@@ -24011,7 +23988,7 @@
         <v>4</v>
       </c>
       <c r="G629" s="9">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="I629" s="9">
         <v>0</v>
@@ -24019,7 +23996,6 @@
     </row>
     <row r="630" customHeight="1" spans="1:9">
       <c r="A630" s="2">
-        <f t="shared" si="24"/>
         <v>1038100409</v>
       </c>
       <c r="B630" s="2">
@@ -24035,7 +24011,7 @@
         <v>4</v>
       </c>
       <c r="G630" s="9">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="I630" s="7">
         <v>0</v>
@@ -24043,7 +24019,6 @@
     </row>
     <row r="631" customHeight="1" spans="1:9">
       <c r="A631" s="2">
-        <f t="shared" si="24"/>
         <v>1038100410</v>
       </c>
       <c r="B631" s="2">
@@ -24059,7 +24034,7 @@
         <v>4</v>
       </c>
       <c r="G631" s="9">
-        <v>48</v>
+        <v>400</v>
       </c>
       <c r="I631" s="9">
         <v>0</v>
@@ -24067,7 +24042,6 @@
     </row>
     <row r="632" customHeight="1" spans="1:9">
       <c r="A632" s="2">
-        <f t="shared" si="24"/>
         <v>1038100501</v>
       </c>
       <c r="B632" s="2">
@@ -24083,7 +24057,7 @@
         <v>5</v>
       </c>
       <c r="G632" s="9">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="I632" s="7">
         <v>0</v>
@@ -24091,7 +24065,6 @@
     </row>
     <row r="633" customHeight="1" spans="1:9">
       <c r="A633" s="2">
-        <f t="shared" si="24"/>
         <v>1038100502</v>
       </c>
       <c r="B633" s="2">
@@ -24107,7 +24080,7 @@
         <v>5</v>
       </c>
       <c r="G633" s="9">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="I633" s="9">
         <v>0</v>
@@ -24115,7 +24088,6 @@
     </row>
     <row r="634" customHeight="1" spans="1:9">
       <c r="A634" s="2">
-        <f t="shared" si="24"/>
         <v>1038100503</v>
       </c>
       <c r="B634" s="2">
@@ -24131,7 +24103,7 @@
         <v>5</v>
       </c>
       <c r="G634" s="9">
-        <v>12</v>
+        <v>200</v>
       </c>
       <c r="I634" s="7">
         <v>0</v>
@@ -24139,7 +24111,6 @@
     </row>
     <row r="635" customHeight="1" spans="1:9">
       <c r="A635" s="2">
-        <f t="shared" si="24"/>
         <v>1038100504</v>
       </c>
       <c r="B635" s="2">
@@ -24155,7 +24126,7 @@
         <v>5</v>
       </c>
       <c r="G635" s="9">
-        <v>12</v>
+        <v>200</v>
       </c>
       <c r="I635" s="9">
         <v>0</v>
@@ -24163,7 +24134,6 @@
     </row>
     <row r="636" customHeight="1" spans="1:9">
       <c r="A636" s="2">
-        <f t="shared" si="24"/>
         <v>1038100505</v>
       </c>
       <c r="B636" s="2">
@@ -24179,7 +24149,7 @@
         <v>5</v>
       </c>
       <c r="G636" s="9">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="I636" s="7">
         <v>0</v>
@@ -24187,7 +24157,6 @@
     </row>
     <row r="637" customHeight="1" spans="1:9">
       <c r="A637" s="2">
-        <f t="shared" si="24"/>
         <v>1038100506</v>
       </c>
       <c r="B637" s="2">
@@ -24203,7 +24172,7 @@
         <v>5</v>
       </c>
       <c r="G637" s="9">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="I637" s="9">
         <v>0</v>
@@ -24211,7 +24180,6 @@
     </row>
     <row r="638" customHeight="1" spans="1:9">
       <c r="A638" s="2">
-        <f t="shared" si="24"/>
         <v>1038100507</v>
       </c>
       <c r="B638" s="2">
@@ -24227,7 +24195,7 @@
         <v>5</v>
       </c>
       <c r="G638" s="9">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="I638" s="7">
         <v>0</v>
@@ -24235,7 +24203,6 @@
     </row>
     <row r="639" customHeight="1" spans="1:9">
       <c r="A639" s="2">
-        <f t="shared" si="24"/>
         <v>1038100508</v>
       </c>
       <c r="B639" s="2">
@@ -24251,7 +24218,7 @@
         <v>5</v>
       </c>
       <c r="G639" s="9">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="I639" s="9">
         <v>0</v>
@@ -24259,7 +24226,6 @@
     </row>
     <row r="640" customHeight="1" spans="1:9">
       <c r="A640" s="2">
-        <f t="shared" si="24"/>
         <v>1038100509</v>
       </c>
       <c r="B640" s="2">
@@ -24275,7 +24241,7 @@
         <v>5</v>
       </c>
       <c r="G640" s="9">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="I640" s="7">
         <v>0</v>
@@ -24283,7 +24249,6 @@
     </row>
     <row r="641" customHeight="1" spans="1:12">
       <c r="A641" s="2">
-        <f t="shared" si="24"/>
         <v>1038100510</v>
       </c>
       <c r="B641" s="2">
@@ -24299,7 +24264,7 @@
         <v>5</v>
       </c>
       <c r="G641" s="9">
-        <v>160</v>
+        <v>1600</v>
       </c>
       <c r="I641" s="9">
         <v>0</v>
@@ -24307,7 +24272,7 @@
     </row>
     <row r="642" customHeight="1" spans="1:12">
       <c r="A642" s="2">
-        <f t="shared" ref="A642:A649" si="25">(B642)*10000+C642+F642*100+D642*100000</f>
+        <f t="shared" ref="A642:A649" si="24">(B642)*10000+C642+F642*100+D642*100000</f>
         <v>1038400111</v>
       </c>
       <c r="B642" s="2">
@@ -24331,7 +24296,7 @@
     </row>
     <row r="643" customHeight="1" spans="1:12">
       <c r="A643" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1038400112</v>
       </c>
       <c r="B643" s="2">
@@ -24355,7 +24320,7 @@
     </row>
     <row r="644" customHeight="1" spans="1:12">
       <c r="A644" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1038400113</v>
       </c>
       <c r="B644" s="2">
@@ -24385,7 +24350,7 @@
     </row>
     <row r="645" customHeight="1" spans="1:12">
       <c r="A645" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1038400114</v>
       </c>
       <c r="B645" s="2">
@@ -24415,7 +24380,7 @@
     </row>
     <row r="646" customHeight="1" spans="1:12">
       <c r="A646" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1038400115</v>
       </c>
       <c r="B646" s="2">
@@ -24445,7 +24410,7 @@
     </row>
     <row r="647" customHeight="1" spans="1:12">
       <c r="A647" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1038400116</v>
       </c>
       <c r="B647" s="2">
@@ -24475,7 +24440,7 @@
     </row>
     <row r="648" customHeight="1" spans="1:12">
       <c r="A648" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1038400117</v>
       </c>
       <c r="B648" s="2">
@@ -24505,7 +24470,7 @@
     </row>
     <row r="649" customHeight="1" spans="1:12">
       <c r="A649" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1038400118</v>
       </c>
       <c r="B649" s="2">
@@ -24535,7 +24500,7 @@
     </row>
     <row r="650" customHeight="1" spans="1:12">
       <c r="A650" s="2">
-        <f t="shared" ref="A650:A680" si="26">(B650)*10000+C650+F650*100+D650*100000</f>
+        <f t="shared" ref="A650:A680" si="25">(B650)*10000+C650+F650*100+D650*100000</f>
         <v>1027300301</v>
       </c>
       <c r="B650" s="2">
@@ -24559,7 +24524,7 @@
     </row>
     <row r="651" customHeight="1" spans="1:12">
       <c r="A651" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300302</v>
       </c>
       <c r="B651" s="2">
@@ -24583,7 +24548,7 @@
     </row>
     <row r="652" customHeight="1" spans="1:12">
       <c r="A652" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300303</v>
       </c>
       <c r="B652" s="2">
@@ -24607,7 +24572,7 @@
     </row>
     <row r="653" customHeight="1" spans="1:12">
       <c r="A653" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300304</v>
       </c>
       <c r="B653" s="2">
@@ -24631,7 +24596,7 @@
     </row>
     <row r="654" customHeight="1" spans="1:12">
       <c r="A654" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300305</v>
       </c>
       <c r="B654" s="2">
@@ -24655,7 +24620,7 @@
     </row>
     <row r="655" customHeight="1" spans="1:12">
       <c r="A655" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300306</v>
       </c>
       <c r="B655" s="2">
@@ -24679,7 +24644,7 @@
     </row>
     <row r="656" customHeight="1" spans="1:12">
       <c r="A656" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300307</v>
       </c>
       <c r="B656" s="2">
@@ -24703,7 +24668,7 @@
     </row>
     <row r="657" customHeight="1" spans="1:9">
       <c r="A657" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300308</v>
       </c>
       <c r="B657" s="2">
@@ -24727,7 +24692,7 @@
     </row>
     <row r="658" customHeight="1" spans="1:9">
       <c r="A658" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300401</v>
       </c>
       <c r="B658" s="2">
@@ -24751,7 +24716,7 @@
     </row>
     <row r="659" customHeight="1" spans="1:9">
       <c r="A659" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300402</v>
       </c>
       <c r="B659" s="2">
@@ -24775,7 +24740,7 @@
     </row>
     <row r="660" customHeight="1" spans="1:9">
       <c r="A660" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300403</v>
       </c>
       <c r="B660" s="2">
@@ -24799,7 +24764,7 @@
     </row>
     <row r="661" customHeight="1" spans="1:9">
       <c r="A661" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300404</v>
       </c>
       <c r="B661" s="2">
@@ -24823,7 +24788,7 @@
     </row>
     <row r="662" customHeight="1" spans="1:9">
       <c r="A662" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300405</v>
       </c>
       <c r="B662" s="2">
@@ -24847,7 +24812,7 @@
     </row>
     <row r="663" customHeight="1" spans="1:9">
       <c r="A663" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300406</v>
       </c>
       <c r="B663" s="2">
@@ -24871,7 +24836,7 @@
     </row>
     <row r="664" customHeight="1" spans="1:9">
       <c r="A664" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300407</v>
       </c>
       <c r="B664" s="2">
@@ -24895,7 +24860,7 @@
     </row>
     <row r="665" customHeight="1" spans="1:9">
       <c r="A665" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300408</v>
       </c>
       <c r="B665" s="2">
@@ -24919,7 +24884,7 @@
     </row>
     <row r="666" customHeight="1" spans="1:9">
       <c r="A666" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300501</v>
       </c>
       <c r="B666" s="2">
@@ -24943,7 +24908,7 @@
     </row>
     <row r="667" customHeight="1" spans="1:9">
       <c r="A667" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300502</v>
       </c>
       <c r="B667" s="2">
@@ -24967,7 +24932,7 @@
     </row>
     <row r="668" customHeight="1" spans="1:9">
       <c r="A668" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300503</v>
       </c>
       <c r="B668" s="2">
@@ -24991,7 +24956,7 @@
     </row>
     <row r="669" customHeight="1" spans="1:9">
       <c r="A669" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300504</v>
       </c>
       <c r="B669" s="2">
@@ -25015,7 +24980,7 @@
     </row>
     <row r="670" customHeight="1" spans="1:9">
       <c r="A670" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300505</v>
       </c>
       <c r="B670" s="2">
@@ -25039,7 +25004,7 @@
     </row>
     <row r="671" customHeight="1" spans="1:9">
       <c r="A671" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300506</v>
       </c>
       <c r="B671" s="2">
@@ -25063,7 +25028,7 @@
     </row>
     <row r="672" customHeight="1" spans="1:9">
       <c r="A672" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300507</v>
       </c>
       <c r="B672" s="2">
@@ -25087,7 +25052,7 @@
     </row>
     <row r="673" customHeight="1" spans="1:12">
       <c r="A673" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027300508</v>
       </c>
       <c r="B673" s="2">
@@ -25111,7 +25076,7 @@
     </row>
     <row r="674" customHeight="1" spans="1:12">
       <c r="A674" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027400310</v>
       </c>
       <c r="B674" s="2">
@@ -25141,7 +25106,7 @@
     </row>
     <row r="675" customHeight="1" spans="1:12">
       <c r="A675" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027400410</v>
       </c>
       <c r="B675" s="2">
@@ -25171,7 +25136,7 @@
     </row>
     <row r="676" customHeight="1" spans="1:12">
       <c r="A676" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027400510</v>
       </c>
       <c r="B676" s="2">
@@ -25201,7 +25166,7 @@
     </row>
     <row r="677" customHeight="1" spans="1:12">
       <c r="A677" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027400111</v>
       </c>
       <c r="B677" s="2">
@@ -25231,7 +25196,7 @@
     </row>
     <row r="678" customHeight="1" spans="1:12">
       <c r="A678" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027400112</v>
       </c>
       <c r="B678" s="2">
@@ -25261,7 +25226,7 @@
     </row>
     <row r="679" customHeight="1" spans="1:12">
       <c r="A679" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027400113</v>
       </c>
       <c r="B679" s="2">
@@ -25291,7 +25256,7 @@
     </row>
     <row r="680" customHeight="1" spans="1:12">
       <c r="A680" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1027400114</v>
       </c>
       <c r="B680" s="2">
@@ -25321,7 +25286,7 @@
     </row>
     <row r="681" customHeight="1" spans="1:12">
       <c r="A681" s="2">
-        <f t="shared" ref="A681:A688" si="27">(B681)*10000+C681+F681*100+D681*100000</f>
+        <f t="shared" ref="A681:A688" si="26">(B681)*10000+C681+F681*100+D681*100000</f>
         <v>1037100301</v>
       </c>
       <c r="B681" s="2">
@@ -25345,7 +25310,7 @@
     </row>
     <row r="682" customHeight="1" spans="1:12">
       <c r="A682" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1037100302</v>
       </c>
       <c r="B682" s="2">
@@ -25369,7 +25334,7 @@
     </row>
     <row r="683" customHeight="1" spans="1:12">
       <c r="A683" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1037100303</v>
       </c>
       <c r="B683" s="2">
@@ -25393,7 +25358,7 @@
     </row>
     <row r="684" customHeight="1" spans="1:12">
       <c r="A684" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1037100304</v>
       </c>
       <c r="B684" s="2">
@@ -25417,7 +25382,7 @@
     </row>
     <row r="685" customHeight="1" spans="1:12">
       <c r="A685" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1037100305</v>
       </c>
       <c r="B685" s="2">
@@ -25441,7 +25406,7 @@
     </row>
     <row r="686" customHeight="1" spans="1:12">
       <c r="A686" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1037100306</v>
       </c>
       <c r="B686" s="2">
@@ -25465,7 +25430,7 @@
     </row>
     <row r="687" customHeight="1" spans="1:12">
       <c r="A687" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1037100307</v>
       </c>
       <c r="B687" s="2">
@@ -25489,7 +25454,7 @@
     </row>
     <row r="688" customHeight="1" spans="1:12">
       <c r="A688" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1037400109</v>
       </c>
       <c r="B688" s="2">
@@ -25519,7 +25484,7 @@
     </row>
     <row r="689" customHeight="1" spans="1:9">
       <c r="A689" s="2">
-        <f t="shared" ref="A689:A722" si="28">(B689)*10000+C689+F689*100+D689*100000</f>
+        <f t="shared" ref="A689:A722" si="27">(B689)*10000+C689+F689*100+D689*100000</f>
         <v>1031100207</v>
       </c>
       <c r="B689" s="2">
@@ -25543,7 +25508,7 @@
     </row>
     <row r="690" customHeight="1" spans="1:9">
       <c r="A690" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100208</v>
       </c>
       <c r="B690" s="2">
@@ -25567,7 +25532,7 @@
     </row>
     <row r="691" customHeight="1" spans="1:9">
       <c r="A691" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100209</v>
       </c>
       <c r="B691" s="2">
@@ -25591,7 +25556,7 @@
     </row>
     <row r="692" customHeight="1" spans="1:9">
       <c r="A692" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100210</v>
       </c>
       <c r="B692" s="2">
@@ -25615,7 +25580,7 @@
     </row>
     <row r="693" customHeight="1" spans="1:9">
       <c r="A693" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100301</v>
       </c>
       <c r="B693" s="2">
@@ -25639,7 +25604,7 @@
     </row>
     <row r="694" customHeight="1" spans="1:9">
       <c r="A694" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100302</v>
       </c>
       <c r="B694" s="2">
@@ -25663,7 +25628,7 @@
     </row>
     <row r="695" customHeight="1" spans="1:9">
       <c r="A695" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100303</v>
       </c>
       <c r="B695" s="2">
@@ -25687,7 +25652,7 @@
     </row>
     <row r="696" customHeight="1" spans="1:9">
       <c r="A696" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100304</v>
       </c>
       <c r="B696" s="2">
@@ -25711,7 +25676,7 @@
     </row>
     <row r="697" customHeight="1" spans="1:9">
       <c r="A697" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100305</v>
       </c>
       <c r="B697" s="2">
@@ -25735,7 +25700,7 @@
     </row>
     <row r="698" customHeight="1" spans="1:9">
       <c r="A698" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100306</v>
       </c>
       <c r="B698" s="2">
@@ -25759,7 +25724,7 @@
     </row>
     <row r="699" customHeight="1" spans="1:9">
       <c r="A699" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100307</v>
       </c>
       <c r="B699" s="2">
@@ -25783,7 +25748,7 @@
     </row>
     <row r="700" customHeight="1" spans="1:9">
       <c r="A700" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100308</v>
       </c>
       <c r="B700" s="2">
@@ -25807,7 +25772,7 @@
     </row>
     <row r="701" customHeight="1" spans="1:9">
       <c r="A701" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100309</v>
       </c>
       <c r="B701" s="2">
@@ -25831,7 +25796,7 @@
     </row>
     <row r="702" customHeight="1" spans="1:9">
       <c r="A702" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100310</v>
       </c>
       <c r="B702" s="2">
@@ -25855,7 +25820,7 @@
     </row>
     <row r="703" customHeight="1" spans="1:9">
       <c r="A703" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100401</v>
       </c>
       <c r="B703" s="2">
@@ -25879,7 +25844,7 @@
     </row>
     <row r="704" customHeight="1" spans="1:9">
       <c r="A704" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100402</v>
       </c>
       <c r="B704" s="2">
@@ -25903,7 +25868,7 @@
     </row>
     <row r="705" customHeight="1" spans="1:9">
       <c r="A705" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100403</v>
       </c>
       <c r="B705" s="2">
@@ -25927,7 +25892,7 @@
     </row>
     <row r="706" customHeight="1" spans="1:9">
       <c r="A706" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100404</v>
       </c>
       <c r="B706" s="2">
@@ -25951,7 +25916,7 @@
     </row>
     <row r="707" customHeight="1" spans="1:9">
       <c r="A707" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100405</v>
       </c>
       <c r="B707" s="2">
@@ -25975,7 +25940,7 @@
     </row>
     <row r="708" customHeight="1" spans="1:9">
       <c r="A708" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100406</v>
       </c>
       <c r="B708" s="2">
@@ -25999,7 +25964,7 @@
     </row>
     <row r="709" customHeight="1" spans="1:9">
       <c r="A709" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100407</v>
       </c>
       <c r="B709" s="2">
@@ -26023,7 +25988,7 @@
     </row>
     <row r="710" customHeight="1" spans="1:9">
       <c r="A710" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100408</v>
       </c>
       <c r="B710" s="2">
@@ -26047,7 +26012,7 @@
     </row>
     <row r="711" customHeight="1" spans="1:9">
       <c r="A711" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100409</v>
       </c>
       <c r="B711" s="2">
@@ -26071,7 +26036,7 @@
     </row>
     <row r="712" customHeight="1" spans="1:9">
       <c r="A712" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100410</v>
       </c>
       <c r="B712" s="2">
@@ -26095,7 +26060,7 @@
     </row>
     <row r="713" customHeight="1" spans="1:9">
       <c r="A713" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100501</v>
       </c>
       <c r="B713" s="2">
@@ -26119,7 +26084,7 @@
     </row>
     <row r="714" customHeight="1" spans="1:9">
       <c r="A714" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100502</v>
       </c>
       <c r="B714" s="2">
@@ -26143,7 +26108,7 @@
     </row>
     <row r="715" customHeight="1" spans="1:9">
       <c r="A715" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100503</v>
       </c>
       <c r="B715" s="2">
@@ -26167,7 +26132,7 @@
     </row>
     <row r="716" customHeight="1" spans="1:9">
       <c r="A716" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100504</v>
       </c>
       <c r="B716" s="2">
@@ -26191,7 +26156,7 @@
     </row>
     <row r="717" customHeight="1" spans="1:9">
       <c r="A717" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100505</v>
       </c>
       <c r="B717" s="2">
@@ -26215,7 +26180,7 @@
     </row>
     <row r="718" customHeight="1" spans="1:9">
       <c r="A718" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100506</v>
       </c>
       <c r="B718" s="2">
@@ -26239,7 +26204,7 @@
     </row>
     <row r="719" customHeight="1" spans="1:9">
       <c r="A719" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100507</v>
       </c>
       <c r="B719" s="2">
@@ -26263,7 +26228,7 @@
     </row>
     <row r="720" customHeight="1" spans="1:9">
       <c r="A720" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100508</v>
       </c>
       <c r="B720" s="2">
@@ -26287,7 +26252,7 @@
     </row>
     <row r="721" customHeight="1" spans="1:12">
       <c r="A721" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100509</v>
       </c>
       <c r="B721" s="2">
@@ -26311,7 +26276,7 @@
     </row>
     <row r="722" customHeight="1" spans="1:12">
       <c r="A722" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>1031100510</v>
       </c>
       <c r="B722" s="2">
@@ -26335,7 +26300,7 @@
     </row>
     <row r="723" customHeight="1" spans="1:12">
       <c r="A723" s="2">
-        <f t="shared" ref="A723:A732" si="29">(B723)*10000+C723+F723*100+D723*100000</f>
+        <f t="shared" ref="A723:A732" si="28">(B723)*10000+C723+F723*100+D723*100000</f>
         <v>1031400312</v>
       </c>
       <c r="B723" s="2">
@@ -26362,7 +26327,7 @@
     </row>
     <row r="724" customHeight="1" spans="1:12">
       <c r="A724" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1031400412</v>
       </c>
       <c r="B724" s="2">
@@ -26389,7 +26354,7 @@
     </row>
     <row r="725" customHeight="1" spans="1:12">
       <c r="A725" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1031400512</v>
       </c>
       <c r="B725" s="2">
@@ -26416,7 +26381,7 @@
     </row>
     <row r="726" customHeight="1" spans="1:12">
       <c r="A726" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1031400213</v>
       </c>
       <c r="B726" s="2">
@@ -26443,7 +26408,7 @@
     </row>
     <row r="727" customHeight="1" spans="1:12">
       <c r="A727" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1031400114</v>
       </c>
       <c r="B727" s="2">
@@ -26473,7 +26438,7 @@
     </row>
     <row r="728" customHeight="1" spans="1:12">
       <c r="A728" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1031400115</v>
       </c>
       <c r="B728" s="2">
@@ -26503,7 +26468,7 @@
     </row>
     <row r="729" customHeight="1" spans="1:12">
       <c r="A729" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1031400116</v>
       </c>
       <c r="B729" s="2">
@@ -26533,7 +26498,7 @@
     </row>
     <row r="730" customHeight="1" spans="1:12">
       <c r="A730" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1031400117</v>
       </c>
       <c r="B730" s="2">
@@ -26563,7 +26528,7 @@
     </row>
     <row r="731" customHeight="1" spans="1:12">
       <c r="A731" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1031400118</v>
       </c>
       <c r="B731" s="2">
@@ -26593,7 +26558,7 @@
     </row>
     <row r="732" customHeight="1" spans="1:12">
       <c r="A732" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1031400318</v>
       </c>
       <c r="B732" s="2">
@@ -26623,7 +26588,7 @@
     </row>
     <row r="733" customHeight="1" spans="1:12">
       <c r="A733" s="2">
-        <f t="shared" ref="A733:A767" si="30">(B733)*10000+C733+F733*100+D733*100000</f>
+        <f t="shared" ref="A733:A767" si="29">(B733)*10000+C733+F733*100+D733*100000</f>
         <v>1040100301</v>
       </c>
       <c r="B733" s="2">
@@ -26647,7 +26612,7 @@
     </row>
     <row r="734" customHeight="1" spans="1:12">
       <c r="A734" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100302</v>
       </c>
       <c r="B734" s="2">
@@ -26671,7 +26636,7 @@
     </row>
     <row r="735" customHeight="1" spans="1:12">
       <c r="A735" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100303</v>
       </c>
       <c r="B735" s="2">
@@ -26695,7 +26660,7 @@
     </row>
     <row r="736" customHeight="1" spans="1:12">
       <c r="A736" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100304</v>
       </c>
       <c r="B736" s="2">
@@ -26719,7 +26684,7 @@
     </row>
     <row r="737" customHeight="1" spans="1:9">
       <c r="A737" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100305</v>
       </c>
       <c r="B737" s="2">
@@ -26743,7 +26708,7 @@
     </row>
     <row r="738" customHeight="1" spans="1:9">
       <c r="A738" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100306</v>
       </c>
       <c r="B738" s="2">
@@ -26767,7 +26732,7 @@
     </row>
     <row r="739" customHeight="1" spans="1:9">
       <c r="A739" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100307</v>
       </c>
       <c r="B739" s="2">
@@ -26791,7 +26756,7 @@
     </row>
     <row r="740" customHeight="1" spans="1:9">
       <c r="A740" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100308</v>
       </c>
       <c r="B740" s="2">
@@ -26815,7 +26780,7 @@
     </row>
     <row r="741" customHeight="1" spans="1:9">
       <c r="A741" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100309</v>
       </c>
       <c r="B741" s="2">
@@ -26839,7 +26804,7 @@
     </row>
     <row r="742" customHeight="1" spans="1:9">
       <c r="A742" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100310</v>
       </c>
       <c r="B742" s="2">
@@ -26863,7 +26828,7 @@
     </row>
     <row r="743" customHeight="1" spans="1:9">
       <c r="A743" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100401</v>
       </c>
       <c r="B743" s="2">
@@ -26887,7 +26852,7 @@
     </row>
     <row r="744" customHeight="1" spans="1:9">
       <c r="A744" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100402</v>
       </c>
       <c r="B744" s="2">
@@ -26911,7 +26876,7 @@
     </row>
     <row r="745" customHeight="1" spans="1:9">
       <c r="A745" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100403</v>
       </c>
       <c r="B745" s="2">
@@ -26935,7 +26900,7 @@
     </row>
     <row r="746" customHeight="1" spans="1:9">
       <c r="A746" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100404</v>
       </c>
       <c r="B746" s="2">
@@ -26959,7 +26924,7 @@
     </row>
     <row r="747" customHeight="1" spans="1:9">
       <c r="A747" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100405</v>
       </c>
       <c r="B747" s="2">
@@ -26983,7 +26948,7 @@
     </row>
     <row r="748" customHeight="1" spans="1:9">
       <c r="A748" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100406</v>
       </c>
       <c r="B748" s="2">
@@ -27007,7 +26972,7 @@
     </row>
     <row r="749" customHeight="1" spans="1:9">
       <c r="A749" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100407</v>
       </c>
       <c r="B749" s="2">
@@ -27031,7 +26996,7 @@
     </row>
     <row r="750" customHeight="1" spans="1:9">
       <c r="A750" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100408</v>
       </c>
       <c r="B750" s="2">
@@ -27055,7 +27020,7 @@
     </row>
     <row r="751" customHeight="1" spans="1:9">
       <c r="A751" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100409</v>
       </c>
       <c r="B751" s="2">
@@ -27079,7 +27044,7 @@
     </row>
     <row r="752" customHeight="1" spans="1:9">
       <c r="A752" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100410</v>
       </c>
       <c r="B752" s="2">
@@ -27103,7 +27068,7 @@
     </row>
     <row r="753" customHeight="1" spans="1:12">
       <c r="A753" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100501</v>
       </c>
       <c r="B753" s="2">
@@ -27127,7 +27092,7 @@
     </row>
     <row r="754" customHeight="1" spans="1:12">
       <c r="A754" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100502</v>
       </c>
       <c r="B754" s="2">
@@ -27151,7 +27116,7 @@
     </row>
     <row r="755" customHeight="1" spans="1:12">
       <c r="A755" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100503</v>
       </c>
       <c r="B755" s="2">
@@ -27175,7 +27140,7 @@
     </row>
     <row r="756" customHeight="1" spans="1:12">
       <c r="A756" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100504</v>
       </c>
       <c r="B756" s="2">
@@ -27199,7 +27164,7 @@
     </row>
     <row r="757" customHeight="1" spans="1:12">
       <c r="A757" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100505</v>
       </c>
       <c r="B757" s="2">
@@ -27223,7 +27188,7 @@
     </row>
     <row r="758" customHeight="1" spans="1:12">
       <c r="A758" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100506</v>
       </c>
       <c r="B758" s="2">
@@ -27247,7 +27212,7 @@
     </row>
     <row r="759" customHeight="1" spans="1:12">
       <c r="A759" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100507</v>
       </c>
       <c r="B759" s="2">
@@ -27271,7 +27236,7 @@
     </row>
     <row r="760" customHeight="1" spans="1:12">
       <c r="A760" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100508</v>
       </c>
       <c r="B760" s="2">
@@ -27295,7 +27260,7 @@
     </row>
     <row r="761" customHeight="1" spans="1:12">
       <c r="A761" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100509</v>
       </c>
       <c r="B761" s="2">
@@ -27319,7 +27284,7 @@
     </row>
     <row r="762" customHeight="1" spans="1:12">
       <c r="A762" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040100510</v>
       </c>
       <c r="B762" s="2">
@@ -27343,7 +27308,7 @@
     </row>
     <row r="763" customHeight="1" spans="1:12">
       <c r="A763" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040400312</v>
       </c>
       <c r="B763" s="2">
@@ -27373,7 +27338,7 @@
     </row>
     <row r="764" customHeight="1" spans="1:12">
       <c r="A764" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040400113</v>
       </c>
       <c r="B764" s="2">
@@ -27403,7 +27368,7 @@
     </row>
     <row r="765" customHeight="1" spans="1:12">
       <c r="A765" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040400114</v>
       </c>
       <c r="B765" s="2">
@@ -27433,7 +27398,7 @@
     </row>
     <row r="766" customHeight="1" spans="1:12">
       <c r="A766" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040400115</v>
       </c>
       <c r="B766" s="2">
@@ -27463,7 +27428,7 @@
     </row>
     <row r="767" customHeight="1" spans="1:12">
       <c r="A767" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1040400116</v>
       </c>
       <c r="B767" s="2">
@@ -27493,7 +27458,7 @@
     </row>
     <row r="768" customHeight="1" spans="1:12">
       <c r="A768" s="2">
-        <f t="shared" ref="A768:A799" si="31">(B768)*10000+C768+F768*100+D768*100000</f>
+        <f t="shared" ref="A768:A799" si="30">(B768)*10000+C768+F768*100+D768*100000</f>
         <v>1039100301</v>
       </c>
       <c r="B768" s="2">
@@ -27517,7 +27482,7 @@
     </row>
     <row r="769" customHeight="1" spans="1:9">
       <c r="A769" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100302</v>
       </c>
       <c r="B769" s="2">
@@ -27541,7 +27506,7 @@
     </row>
     <row r="770" customHeight="1" spans="1:9">
       <c r="A770" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100303</v>
       </c>
       <c r="B770" s="2">
@@ -27565,7 +27530,7 @@
     </row>
     <row r="771" customHeight="1" spans="1:9">
       <c r="A771" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100304</v>
       </c>
       <c r="B771" s="2">
@@ -27589,7 +27554,7 @@
     </row>
     <row r="772" customHeight="1" spans="1:9">
       <c r="A772" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100305</v>
       </c>
       <c r="B772" s="2">
@@ -27613,7 +27578,7 @@
     </row>
     <row r="773" customHeight="1" spans="1:9">
       <c r="A773" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100306</v>
       </c>
       <c r="B773" s="2">
@@ -27637,7 +27602,7 @@
     </row>
     <row r="774" customHeight="1" spans="1:9">
       <c r="A774" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100307</v>
       </c>
       <c r="B774" s="2">
@@ -27661,7 +27626,7 @@
     </row>
     <row r="775" customHeight="1" spans="1:9">
       <c r="A775" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100308</v>
       </c>
       <c r="B775" s="2">
@@ -27685,7 +27650,7 @@
     </row>
     <row r="776" customHeight="1" spans="1:9">
       <c r="A776" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100401</v>
       </c>
       <c r="B776" s="2">
@@ -27709,7 +27674,7 @@
     </row>
     <row r="777" customHeight="1" spans="1:9">
       <c r="A777" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100402</v>
       </c>
       <c r="B777" s="2">
@@ -27733,7 +27698,7 @@
     </row>
     <row r="778" customHeight="1" spans="1:9">
       <c r="A778" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100403</v>
       </c>
       <c r="B778" s="2">
@@ -27757,7 +27722,7 @@
     </row>
     <row r="779" customHeight="1" spans="1:9">
       <c r="A779" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100404</v>
       </c>
       <c r="B779" s="2">
@@ -27781,7 +27746,7 @@
     </row>
     <row r="780" customHeight="1" spans="1:9">
       <c r="A780" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100405</v>
       </c>
       <c r="B780" s="2">
@@ -27805,7 +27770,7 @@
     </row>
     <row r="781" customHeight="1" spans="1:9">
       <c r="A781" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100406</v>
       </c>
       <c r="B781" s="2">
@@ -27829,7 +27794,7 @@
     </row>
     <row r="782" customHeight="1" spans="1:9">
       <c r="A782" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100407</v>
       </c>
       <c r="B782" s="2">
@@ -27853,7 +27818,7 @@
     </row>
     <row r="783" customHeight="1" spans="1:9">
       <c r="A783" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100408</v>
       </c>
       <c r="B783" s="2">
@@ -27877,7 +27842,7 @@
     </row>
     <row r="784" customHeight="1" spans="1:9">
       <c r="A784" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100501</v>
       </c>
       <c r="B784" s="2">
@@ -27901,7 +27866,7 @@
     </row>
     <row r="785" customHeight="1" spans="1:12">
       <c r="A785" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100502</v>
       </c>
       <c r="B785" s="2">
@@ -27925,7 +27890,7 @@
     </row>
     <row r="786" customHeight="1" spans="1:12">
       <c r="A786" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100503</v>
       </c>
       <c r="B786" s="2">
@@ -27949,7 +27914,7 @@
     </row>
     <row r="787" customHeight="1" spans="1:12">
       <c r="A787" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100504</v>
       </c>
       <c r="B787" s="2">
@@ -27973,7 +27938,7 @@
     </row>
     <row r="788" customHeight="1" spans="1:12">
       <c r="A788" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100505</v>
       </c>
       <c r="B788" s="2">
@@ -27997,7 +27962,7 @@
     </row>
     <row r="789" customHeight="1" spans="1:12">
       <c r="A789" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100506</v>
       </c>
       <c r="B789" s="2">
@@ -28021,7 +27986,7 @@
     </row>
     <row r="790" customHeight="1" spans="1:12">
       <c r="A790" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100507</v>
       </c>
       <c r="B790" s="2">
@@ -28045,7 +28010,7 @@
     </row>
     <row r="791" customHeight="1" spans="1:12">
       <c r="A791" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039100508</v>
       </c>
       <c r="B791" s="2">
@@ -28069,7 +28034,7 @@
     </row>
     <row r="792" customHeight="1" spans="1:12">
       <c r="A792" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039400310</v>
       </c>
       <c r="B792" s="2">
@@ -28099,7 +28064,7 @@
     </row>
     <row r="793" customHeight="1" spans="1:12">
       <c r="A793" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039400410</v>
       </c>
       <c r="B793" s="2">
@@ -28129,7 +28094,7 @@
     </row>
     <row r="794" customHeight="1" spans="1:12">
       <c r="A794" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039400510</v>
       </c>
       <c r="B794" s="2">
@@ -28159,7 +28124,7 @@
     </row>
     <row r="795" customHeight="1" spans="1:12">
       <c r="A795" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039400111</v>
       </c>
       <c r="B795" s="2">
@@ -28189,7 +28154,7 @@
     </row>
     <row r="796" customHeight="1" spans="1:12">
       <c r="A796" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039400112</v>
       </c>
       <c r="B796" s="2">
@@ -28219,7 +28184,7 @@
     </row>
     <row r="797" customHeight="1" spans="1:12">
       <c r="A797" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039400113</v>
       </c>
       <c r="B797" s="2">
@@ -28249,7 +28214,7 @@
     </row>
     <row r="798" customHeight="1" spans="1:12">
       <c r="A798" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039400114</v>
       </c>
       <c r="B798" s="2">
@@ -28279,7 +28244,7 @@
     </row>
     <row r="799" customHeight="1" spans="1:12">
       <c r="A799" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1039400105</v>
       </c>
       <c r="B799" s="2">
@@ -29565,7 +29530,7 @@
     </row>
     <row r="853" customHeight="1" spans="1:12">
       <c r="A853" s="2">
-        <f t="shared" ref="A853:A897" si="32">(B853)*10000+C853+F853*100+D853*100000</f>
+        <f t="shared" ref="A853:A897" si="31">(B853)*10000+C853+F853*100+D853*100000</f>
         <v>1015300302</v>
       </c>
       <c r="B853" s="2">
@@ -29592,7 +29557,7 @@
     </row>
     <row r="854" customHeight="1" spans="1:12">
       <c r="A854" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300303</v>
       </c>
       <c r="B854" s="2">
@@ -29619,7 +29584,7 @@
     </row>
     <row r="855" customHeight="1" spans="1:12">
       <c r="A855" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300304</v>
       </c>
       <c r="B855" s="2">
@@ -29646,7 +29611,7 @@
     </row>
     <row r="856" customHeight="1" spans="1:12">
       <c r="A856" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300305</v>
       </c>
       <c r="B856" s="2">
@@ -29673,7 +29638,7 @@
     </row>
     <row r="857" customHeight="1" spans="1:12">
       <c r="A857" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300306</v>
       </c>
       <c r="B857" s="2">
@@ -29700,7 +29665,7 @@
     </row>
     <row r="858" customHeight="1" spans="1:12">
       <c r="A858" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300307</v>
       </c>
       <c r="B858" s="2">
@@ -29727,7 +29692,7 @@
     </row>
     <row r="859" customHeight="1" spans="1:12">
       <c r="A859" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300308</v>
       </c>
       <c r="B859" s="2">
@@ -29754,7 +29719,7 @@
     </row>
     <row r="860" customHeight="1" spans="1:12">
       <c r="A860" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300309</v>
       </c>
       <c r="B860" s="2">
@@ -29781,7 +29746,7 @@
     </row>
     <row r="861" customHeight="1" spans="1:12">
       <c r="A861" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300310</v>
       </c>
       <c r="B861" s="2">
@@ -29808,7 +29773,7 @@
     </row>
     <row r="862" customHeight="1" spans="1:12">
       <c r="A862" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300311</v>
       </c>
       <c r="B862" s="2">
@@ -29835,7 +29800,7 @@
     </row>
     <row r="863" customHeight="1" spans="1:12">
       <c r="A863" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300312</v>
       </c>
       <c r="B863" s="2">
@@ -29862,7 +29827,7 @@
     </row>
     <row r="864" customHeight="1" spans="1:12">
       <c r="A864" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300401</v>
       </c>
       <c r="B864" s="2">
@@ -29889,7 +29854,7 @@
     </row>
     <row r="865" customHeight="1" spans="1:10">
       <c r="A865" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300402</v>
       </c>
       <c r="B865" s="2">
@@ -29916,7 +29881,7 @@
     </row>
     <row r="866" customHeight="1" spans="1:10">
       <c r="A866" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300403</v>
       </c>
       <c r="B866" s="2">
@@ -29943,7 +29908,7 @@
     </row>
     <row r="867" customHeight="1" spans="1:10">
       <c r="A867" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300404</v>
       </c>
       <c r="B867" s="2">
@@ -29970,7 +29935,7 @@
     </row>
     <row r="868" customHeight="1" spans="1:10">
       <c r="A868" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300405</v>
       </c>
       <c r="B868" s="2">
@@ -29997,7 +29962,7 @@
     </row>
     <row r="869" customHeight="1" spans="1:10">
       <c r="A869" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300406</v>
       </c>
       <c r="B869" s="2">
@@ -30024,7 +29989,7 @@
     </row>
     <row r="870" customHeight="1" spans="1:10">
       <c r="A870" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300407</v>
       </c>
       <c r="B870" s="2">
@@ -30051,7 +30016,7 @@
     </row>
     <row r="871" customHeight="1" spans="1:10">
       <c r="A871" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300408</v>
       </c>
       <c r="B871" s="2">
@@ -30078,7 +30043,7 @@
     </row>
     <row r="872" customHeight="1" spans="1:10">
       <c r="A872" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300409</v>
       </c>
       <c r="B872" s="2">
@@ -30105,7 +30070,7 @@
     </row>
     <row r="873" customHeight="1" spans="1:10">
       <c r="A873" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300410</v>
       </c>
       <c r="B873" s="2">
@@ -30132,7 +30097,7 @@
     </row>
     <row r="874" customHeight="1" spans="1:10">
       <c r="A874" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300411</v>
       </c>
       <c r="B874" s="2">
@@ -30159,7 +30124,7 @@
     </row>
     <row r="875" customHeight="1" spans="1:10">
       <c r="A875" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300412</v>
       </c>
       <c r="B875" s="2">
@@ -30186,7 +30151,7 @@
     </row>
     <row r="876" customHeight="1" spans="1:10">
       <c r="A876" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300501</v>
       </c>
       <c r="B876" s="2">
@@ -30213,7 +30178,7 @@
     </row>
     <row r="877" customHeight="1" spans="1:10">
       <c r="A877" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300502</v>
       </c>
       <c r="B877" s="2">
@@ -30240,7 +30205,7 @@
     </row>
     <row r="878" customHeight="1" spans="1:10">
       <c r="A878" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300503</v>
       </c>
       <c r="B878" s="2">
@@ -30267,7 +30232,7 @@
     </row>
     <row r="879" customHeight="1" spans="1:10">
       <c r="A879" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300504</v>
       </c>
       <c r="B879" s="2">
@@ -30294,7 +30259,7 @@
     </row>
     <row r="880" customHeight="1" spans="1:10">
       <c r="A880" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300505</v>
       </c>
       <c r="B880" s="2">
@@ -30321,7 +30286,7 @@
     </row>
     <row r="881" customHeight="1" spans="1:12">
       <c r="A881" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300506</v>
       </c>
       <c r="B881" s="2">
@@ -30348,7 +30313,7 @@
     </row>
     <row r="882" customHeight="1" spans="1:12">
       <c r="A882" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300507</v>
       </c>
       <c r="B882" s="2">
@@ -30375,7 +30340,7 @@
     </row>
     <row r="883" customHeight="1" spans="1:12">
       <c r="A883" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300508</v>
       </c>
       <c r="B883" s="2">
@@ -30402,7 +30367,7 @@
     </row>
     <row r="884" customHeight="1" spans="1:12">
       <c r="A884" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300509</v>
       </c>
       <c r="B884" s="2">
@@ -30429,7 +30394,7 @@
     </row>
     <row r="885" customHeight="1" spans="1:12">
       <c r="A885" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300510</v>
       </c>
       <c r="B885" s="2">
@@ -30456,7 +30421,7 @@
     </row>
     <row r="886" customHeight="1" spans="1:12">
       <c r="A886" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300511</v>
       </c>
       <c r="B886" s="2">
@@ -30483,7 +30448,7 @@
     </row>
     <row r="887" customHeight="1" spans="1:12">
       <c r="A887" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300512</v>
       </c>
       <c r="B887" s="2">
@@ -30510,7 +30475,7 @@
     </row>
     <row r="888" customHeight="1" spans="1:12">
       <c r="A888" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015300513</v>
       </c>
       <c r="B888" s="2">
@@ -30537,7 +30502,7 @@
     </row>
     <row r="889" customHeight="1" spans="1:12">
       <c r="A889" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015400314</v>
       </c>
       <c r="B889" s="2">
@@ -30561,7 +30526,7 @@
     </row>
     <row r="890" customHeight="1" spans="1:12">
       <c r="A890" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015400115</v>
       </c>
       <c r="B890" s="2">
@@ -30585,7 +30550,7 @@
     </row>
     <row r="891" customHeight="1" spans="1:12">
       <c r="A891" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015400116</v>
       </c>
       <c r="B891" s="2">
@@ -30615,7 +30580,7 @@
     </row>
     <row r="892" customHeight="1" spans="1:12">
       <c r="A892" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015400117</v>
       </c>
       <c r="B892" s="2">
@@ -30645,7 +30610,7 @@
     </row>
     <row r="893" customHeight="1" spans="1:12">
       <c r="A893" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015400118</v>
       </c>
       <c r="B893" s="2">
@@ -30675,7 +30640,7 @@
     </row>
     <row r="894" customHeight="1" spans="1:12">
       <c r="A894" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015400119</v>
       </c>
       <c r="B894" s="2">
@@ -30705,7 +30670,7 @@
     </row>
     <row r="895" customHeight="1" spans="1:12">
       <c r="A895" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015400120</v>
       </c>
       <c r="B895" s="2">
@@ -30735,7 +30700,7 @@
     </row>
     <row r="896" customHeight="1" spans="1:12">
       <c r="A896" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015400121</v>
       </c>
       <c r="B896" s="2">
@@ -30765,7 +30730,7 @@
     </row>
     <row r="897" customHeight="1" spans="1:9">
       <c r="A897" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1015400122</v>
       </c>
       <c r="B897" s="2">
@@ -42815,7 +42780,7 @@
         <v>16</v>
       </c>
       <c r="D1325" s="55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1325" s="9" t="s">
         <v>185</v>
@@ -42844,7 +42809,7 @@
         <v>17</v>
       </c>
       <c r="D1326" s="55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1326" s="9" t="s">
         <v>186</v>
@@ -42873,7 +42838,7 @@
         <v>18</v>
       </c>
       <c r="D1327" s="55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1327" s="9" t="s">
         <v>187</v>
@@ -54976,7 +54941,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L1675" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L1752" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A105">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
@@ -639,37 +639,37 @@
     <t>转轴上出现符号5时在随机位置上改出1个wild</t>
   </si>
   <si>
-    <t>1_19_31_43_55_66_77_88_99_110_121</t>
+    <t>1_19_31_43_54_65_76_87</t>
   </si>
   <si>
-    <t>2_20_32_44_56_67_78_89_100_111_122</t>
+    <t>2_20_32_44_55_66_77_88</t>
   </si>
   <si>
-    <t>3_21_33_45_57_68_79_90_101_112_123</t>
+    <t>3_21_33_45_56_67_78_89</t>
   </si>
   <si>
-    <t>4_22_34_46_58_69_80_91_102_113_124</t>
+    <t>4_22_34_46_57_68_79_90</t>
   </si>
   <si>
-    <t>5_23_35_47_59_70_81_92_103_114_125</t>
+    <t>5_23_35_47_58_69_80_91</t>
   </si>
   <si>
-    <t>6_24_36_48_60_71_82_93_104_115_126</t>
+    <t>6_24_36_48_59_70_81_92</t>
   </si>
   <si>
-    <t>7_25_37_49_61_72_83_94_105_116_127</t>
+    <t>7_25_37_49_60_71_82_93</t>
   </si>
   <si>
-    <t>8_26_38_50_62_73_84_95_106_117_128</t>
+    <t>8_26_38_50_61_72_83_94</t>
   </si>
   <si>
-    <t>9_27_39_51_63_74_85_96_107_118_129</t>
+    <t>9_27_39_51_62_73_84_95</t>
   </si>
   <si>
-    <t>10_28_40_52_64_75_86_97_108_119_130</t>
+    <t>10_28_40_52_63_74_85_96</t>
   </si>
   <si>
-    <t>11_29_41_53_65_76_87_98_109_120_131</t>
+    <t>11_29_41_53_64_75_86_97</t>
   </si>
   <si>
     <t>13_1_2</t>
@@ -1423,12 +1423,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6605,7 +6605,9 @@
   <sheetFormatPr defaultColWidth="12.1833333333333" defaultRowHeight="18.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.1833333333333" style="8" customWidth="1"/>
-    <col min="2" max="6" width="12.1833333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.1833333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.025" style="2" customWidth="1"/>
+    <col min="4" max="6" width="12.1833333333333" style="2" customWidth="1"/>
     <col min="7" max="9" width="12.1833333333333" style="9" customWidth="1"/>
     <col min="10" max="10" width="12.1833333333333" style="10" customWidth="1"/>
     <col min="11" max="11" width="12.1833333333333" style="2" customWidth="1"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -1424,18 +1424,18 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -29308,6 +29308,9 @@
       <c r="G844" s="9">
         <v>0</v>
       </c>
+      <c r="H844" s="9">
+        <v>30160001</v>
+      </c>
       <c r="I844" s="9">
         <v>0</v>
       </c>
@@ -29334,6 +29337,9 @@
       <c r="G845" s="9">
         <v>0</v>
       </c>
+      <c r="H845" s="9">
+        <v>30160002</v>
+      </c>
       <c r="I845" s="7">
         <v>0</v>
       </c>
@@ -29359,6 +29365,9 @@
       </c>
       <c r="G846" s="9">
         <v>0</v>
+      </c>
+      <c r="H846" s="9">
+        <v>30160003</v>
       </c>
       <c r="I846" s="9">
         <v>0</v>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$1752</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$1803</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -310,7 +310,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="299">
   <si>
     <t>id</t>
   </si>
@@ -639,37 +639,37 @@
     <t>转轴上出现符号5时在随机位置上改出1个wild</t>
   </si>
   <si>
-    <t>1_19_31_43_55_66_77_88_99_110_121</t>
+    <t>1_19_31_43_54_65_76_87</t>
   </si>
   <si>
-    <t>2_20_32_44_56_67_78_89_100_111_122</t>
+    <t>2_20_32_44_55_66_77_88</t>
   </si>
   <si>
-    <t>3_21_33_45_57_68_79_90_101_112_123</t>
+    <t>3_21_33_45_56_67_78_89</t>
   </si>
   <si>
-    <t>4_22_34_46_58_69_80_91_102_113_124</t>
+    <t>4_22_34_46_57_68_79_90</t>
   </si>
   <si>
-    <t>5_23_35_47_59_70_81_92_103_114_125</t>
+    <t>5_23_35_47_58_69_80_91</t>
   </si>
   <si>
-    <t>6_24_36_48_60_71_82_93_104_115_126</t>
+    <t>6_24_36_48_59_70_81_92</t>
   </si>
   <si>
-    <t>7_25_37_49_61_72_83_94_105_116_127</t>
+    <t>7_25_37_49_60_71_82_93</t>
   </si>
   <si>
-    <t>8_26_38_50_62_73_84_95_106_117_128</t>
+    <t>8_26_38_50_61_72_83_94</t>
   </si>
   <si>
-    <t>9_27_39_51_63_74_85_96_107_118_129</t>
+    <t>9_27_39_51_62_73_84_95</t>
   </si>
   <si>
-    <t>10_28_40_52_64_75_86_97_108_119_130</t>
+    <t>10_28_40_52_63_74_85_96</t>
   </si>
   <si>
-    <t>11_29_41_53_65_76_87_98_109_120_131</t>
+    <t>11_29_41_53_64_75_86_97</t>
   </si>
   <si>
     <t>13_1_2</t>
@@ -1156,6 +1156,60 @@
   <si>
     <t>墨镜男孩</t>
   </si>
+  <si>
+    <t>1_18_30_42_53_64_75</t>
+  </si>
+  <si>
+    <t>2_19_31_43_54_65_76</t>
+  </si>
+  <si>
+    <t>3_20_32_44_55_66_77</t>
+  </si>
+  <si>
+    <t>4_21_33_45_56_67_78</t>
+  </si>
+  <si>
+    <t>5_22_34_46_57_68_79</t>
+  </si>
+  <si>
+    <t>6_23_35_47_58_69_80</t>
+  </si>
+  <si>
+    <t>棺材</t>
+  </si>
+  <si>
+    <t>7_24_36_48_59_70_81</t>
+  </si>
+  <si>
+    <t>血杯</t>
+  </si>
+  <si>
+    <t>8_25_37_49_60_71_82</t>
+  </si>
+  <si>
+    <t>药瓶</t>
+  </si>
+  <si>
+    <t>9_26_38_50_61_72_83</t>
+  </si>
+  <si>
+    <t>戒指</t>
+  </si>
+  <si>
+    <t>10_27_39_51_62_73_84</t>
+  </si>
+  <si>
+    <t>魔法书</t>
+  </si>
+  <si>
+    <t>11_28_40_52_63_74_85</t>
+  </si>
+  <si>
+    <t>骷髅头</t>
+  </si>
+  <si>
+    <t>scatter</t>
+  </si>
 </sst>
 </file>
 
@@ -1423,12 +1477,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6601,11 +6655,13 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:N1752"/>
+  <dimension ref="A1:N1803"/>
   <sheetFormatPr defaultColWidth="12.1833333333333" defaultRowHeight="18.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.1833333333333" style="8" customWidth="1"/>
-    <col min="2" max="6" width="12.1833333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.1833333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.025" style="2" customWidth="1"/>
+    <col min="4" max="6" width="12.1833333333333" style="2" customWidth="1"/>
     <col min="7" max="9" width="12.1833333333333" style="9" customWidth="1"/>
     <col min="10" max="10" width="12.1833333333333" style="10" customWidth="1"/>
     <col min="11" max="11" width="12.1833333333333" style="2" customWidth="1"/>
@@ -28956,7 +29012,7 @@
         <v>5</v>
       </c>
       <c r="G829" s="9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I829" s="7">
         <v>0</v>
@@ -29306,6 +29362,9 @@
       <c r="G844" s="9">
         <v>0</v>
       </c>
+      <c r="H844" s="9">
+        <v>30160001</v>
+      </c>
       <c r="I844" s="9">
         <v>0</v>
       </c>
@@ -29332,6 +29391,9 @@
       <c r="G845" s="9">
         <v>0</v>
       </c>
+      <c r="H845" s="9">
+        <v>30160002</v>
+      </c>
       <c r="I845" s="7">
         <v>0</v>
       </c>
@@ -29357,6 +29419,9 @@
       </c>
       <c r="G846" s="9">
         <v>0</v>
+      </c>
+      <c r="H846" s="9">
+        <v>30160003</v>
       </c>
       <c r="I846" s="9">
         <v>0</v>
@@ -52624,7 +52689,7 @@
         <v>3</v>
       </c>
       <c r="G1663" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1664" customHeight="1" spans="1:12">
@@ -52647,7 +52712,7 @@
         <v>3</v>
       </c>
       <c r="G1664" s="9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1665" customHeight="1" spans="1:12">
@@ -52670,7 +52735,7 @@
         <v>3</v>
       </c>
       <c r="G1665" s="9">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1666" customHeight="1" spans="1:12">
@@ -54940,8 +55005,1106 @@
         <v>105</v>
       </c>
     </row>
+    <row r="1753" customHeight="1" spans="1:12">
+      <c r="A1753" s="2">
+        <v>1019300301</v>
+      </c>
+      <c r="B1753" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1753" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1753" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1753" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1753" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1753" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1754" customHeight="1" spans="1:12">
+      <c r="A1754" s="2">
+        <v>1019300302</v>
+      </c>
+      <c r="B1754" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1754" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1754" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1754" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1754" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1754" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1755" customHeight="1" spans="1:12">
+      <c r="A1755" s="2">
+        <v>1019300303</v>
+      </c>
+      <c r="B1755" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1755" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1755" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1755" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1755" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1755" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1756" customHeight="1" spans="1:12">
+      <c r="A1756" s="2">
+        <v>1019300304</v>
+      </c>
+      <c r="B1756" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1756" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1756" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1756" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1756" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1756" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1757" customHeight="1" spans="1:12">
+      <c r="A1757" s="2">
+        <v>1019300305</v>
+      </c>
+      <c r="B1757" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1757" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1757" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1757" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1757" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1757" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1758" customHeight="1" spans="1:12">
+      <c r="A1758" s="2">
+        <v>1019300306</v>
+      </c>
+      <c r="B1758" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1758" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D1758" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1758" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F1758" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1758" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1759" customHeight="1" spans="1:12">
+      <c r="A1759" s="2">
+        <v>1019300307</v>
+      </c>
+      <c r="B1759" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1759" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1759" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1759" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F1759" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1759" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1760" customHeight="1" spans="1:12">
+      <c r="A1760" s="2">
+        <v>1019300308</v>
+      </c>
+      <c r="B1760" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1760" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1760" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1760" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F1760" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1760" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1761" customHeight="1" spans="1:7">
+      <c r="A1761" s="2">
+        <v>1019300309</v>
+      </c>
+      <c r="B1761" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1761" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D1761" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1761" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F1761" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1761" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1762" customHeight="1" spans="1:7">
+      <c r="A1762" s="2">
+        <v>1019300310</v>
+      </c>
+      <c r="B1762" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1762" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1762" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1762" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F1762" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1762" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1763" customHeight="1" spans="1:7">
+      <c r="A1763" s="2">
+        <v>1019300311</v>
+      </c>
+      <c r="B1763" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1763" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1763" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1763" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F1763" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1763" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1764" customHeight="1" spans="1:7">
+      <c r="A1764" s="2">
+        <v>1019300401</v>
+      </c>
+      <c r="B1764" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1764" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1764" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1764" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1764" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1765" customHeight="1" spans="1:7">
+      <c r="A1765" s="2">
+        <v>1019300402</v>
+      </c>
+      <c r="B1765" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1765" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1765" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1765" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1765" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1766" customHeight="1" spans="1:7">
+      <c r="A1766" s="2">
+        <v>1019300403</v>
+      </c>
+      <c r="B1766" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1766" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1766" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1766" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1766" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1767" customHeight="1" spans="1:7">
+      <c r="A1767" s="2">
+        <v>1019300404</v>
+      </c>
+      <c r="B1767" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1767" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1767" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1767" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1767" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1768" customHeight="1" spans="1:7">
+      <c r="A1768" s="2">
+        <v>1019300405</v>
+      </c>
+      <c r="B1768" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1768" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1768" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1768" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1768" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1769" customHeight="1" spans="1:7">
+      <c r="A1769" s="2">
+        <v>1019300406</v>
+      </c>
+      <c r="B1769" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1769" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D1769" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1769" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1769" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1770" customHeight="1" spans="1:7">
+      <c r="A1770" s="2">
+        <v>1019300407</v>
+      </c>
+      <c r="B1770" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1770" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1770" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1770" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1770" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1771" customHeight="1" spans="1:7">
+      <c r="A1771" s="2">
+        <v>1019300408</v>
+      </c>
+      <c r="B1771" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1771" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1771" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1771" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1771" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1772" customHeight="1" spans="1:7">
+      <c r="A1772" s="2">
+        <v>1019300409</v>
+      </c>
+      <c r="B1772" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1772" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D1772" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1772" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1772" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1773" customHeight="1" spans="1:7">
+      <c r="A1773" s="2">
+        <v>1019300410</v>
+      </c>
+      <c r="B1773" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1773" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1773" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1773" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1773" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1774" customHeight="1" spans="1:7">
+      <c r="A1774" s="2">
+        <v>1019300411</v>
+      </c>
+      <c r="B1774" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1774" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1774" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1774" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1774" s="9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1775" customHeight="1" spans="1:7">
+      <c r="A1775" s="2">
+        <v>1019300501</v>
+      </c>
+      <c r="B1775" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1775" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1775" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1775" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1775" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1776" customHeight="1" spans="1:7">
+      <c r="A1776" s="2">
+        <v>1019300502</v>
+      </c>
+      <c r="B1776" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1776" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1776" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1776" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1776" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1777" customHeight="1" spans="1:7">
+      <c r="A1777" s="2">
+        <v>1019300503</v>
+      </c>
+      <c r="B1777" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1777" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1777" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1777" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1777" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1778" customHeight="1" spans="1:7">
+      <c r="A1778" s="2">
+        <v>1019300504</v>
+      </c>
+      <c r="B1778" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1778" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1778" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1778" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1778" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1779" customHeight="1" spans="1:7">
+      <c r="A1779" s="2">
+        <v>1019300505</v>
+      </c>
+      <c r="B1779" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1779" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1779" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1779" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1779" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1780" customHeight="1" spans="1:7">
+      <c r="A1780" s="2">
+        <v>1019300506</v>
+      </c>
+      <c r="B1780" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1780" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D1780" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1780" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1780" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1781" customHeight="1" spans="1:7">
+      <c r="A1781" s="2">
+        <v>1019300507</v>
+      </c>
+      <c r="B1781" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1781" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1781" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1781" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1781" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1782" customHeight="1" spans="1:7">
+      <c r="A1782" s="2">
+        <v>1019300508</v>
+      </c>
+      <c r="B1782" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1782" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1782" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1782" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1782" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1783" customHeight="1" spans="1:7">
+      <c r="A1783" s="2">
+        <v>1019300509</v>
+      </c>
+      <c r="B1783" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1783" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D1783" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1783" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1783" s="9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1784" customHeight="1" spans="1:7">
+      <c r="A1784" s="2">
+        <v>1019300510</v>
+      </c>
+      <c r="B1784" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1784" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1784" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1784" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1784" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1785" customHeight="1" spans="1:7">
+      <c r="A1785" s="2">
+        <v>1019300511</v>
+      </c>
+      <c r="B1785" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1785" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1785" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1785" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1785" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1786" customHeight="1" spans="1:7">
+      <c r="A1786" s="2">
+        <v>1019300601</v>
+      </c>
+      <c r="B1786" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1786" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1786" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1786" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1786" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1787" customHeight="1" spans="1:7">
+      <c r="A1787" s="2">
+        <v>1019300602</v>
+      </c>
+      <c r="B1787" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1787" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1787" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1787" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1787" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1788" customHeight="1" spans="1:7">
+      <c r="A1788" s="2">
+        <v>1019300603</v>
+      </c>
+      <c r="B1788" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1788" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1788" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1788" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1788" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1789" customHeight="1" spans="1:7">
+      <c r="A1789" s="2">
+        <v>1019300604</v>
+      </c>
+      <c r="B1789" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1789" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1789" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1789" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1789" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1790" customHeight="1" spans="1:7">
+      <c r="A1790" s="2">
+        <v>1019300605</v>
+      </c>
+      <c r="B1790" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1790" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1790" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1790" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1790" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1791" customHeight="1" spans="1:7">
+      <c r="A1791" s="2">
+        <v>1019300606</v>
+      </c>
+      <c r="B1791" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1791" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D1791" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1791" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1791" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1792" customHeight="1" spans="1:7">
+      <c r="A1792" s="2">
+        <v>1019300607</v>
+      </c>
+      <c r="B1792" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1792" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1792" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1792" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1792" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1793" customHeight="1" spans="1:12">
+      <c r="A1793" s="2">
+        <v>1019300608</v>
+      </c>
+      <c r="B1793" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1793" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1793" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1793" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1793" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1794" customHeight="1" spans="1:12">
+      <c r="A1794" s="2">
+        <v>1019300609</v>
+      </c>
+      <c r="B1794" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1794" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D1794" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1794" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1794" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1795" customHeight="1" spans="1:12">
+      <c r="A1795" s="2">
+        <v>1019300610</v>
+      </c>
+      <c r="B1795" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1795" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1795" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1795" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1795" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1796" customHeight="1" spans="1:12">
+      <c r="A1796" s="2">
+        <v>1019300611</v>
+      </c>
+      <c r="B1796" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1796" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1796" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1796" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1796" s="9">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1797" customHeight="1" spans="1:12">
+      <c r="A1797" s="2">
+        <v>1019400401</v>
+      </c>
+      <c r="B1797" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1797" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1797" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1797" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F1797" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1797" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1798" customHeight="1" spans="1:12">
+      <c r="A1798" s="2">
+        <v>1019400501</v>
+      </c>
+      <c r="B1798" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1798" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1798" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1798" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F1798" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1798" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1799" customHeight="1" spans="1:12">
+      <c r="A1799" s="2">
+        <v>1019400601</v>
+      </c>
+      <c r="B1799" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1799" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1799" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1799" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F1799" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1799" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1800" customHeight="1" spans="1:12">
+      <c r="A1800" s="2">
+        <v>1019400101</v>
+      </c>
+      <c r="B1800" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1800" s="2">
+        <v>14</v>
+      </c>
+      <c r="D1800" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1800" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1800" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1800" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1800" s="80">
+        <v>101900101</v>
+      </c>
+      <c r="L1800" s="79" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1801" customHeight="1" spans="1:12">
+      <c r="A1801" s="2">
+        <v>1019400102</v>
+      </c>
+      <c r="B1801" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1801" s="2">
+        <v>15</v>
+      </c>
+      <c r="D1801" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1801" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1801" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1801" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1801" s="80">
+        <v>101900102</v>
+      </c>
+      <c r="L1801" s="79" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1802" customHeight="1" spans="1:12">
+      <c r="A1802" s="2">
+        <v>1019400103</v>
+      </c>
+      <c r="B1802" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1802" s="2">
+        <v>16</v>
+      </c>
+      <c r="D1802" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1802" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1802" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1802" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1802" s="80">
+        <v>101900103</v>
+      </c>
+      <c r="L1802" s="79" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1803" customHeight="1" spans="1:12">
+      <c r="A1803" s="2">
+        <v>1019400104</v>
+      </c>
+      <c r="B1803" s="2">
+        <v>101900</v>
+      </c>
+      <c r="C1803" s="2">
+        <v>17</v>
+      </c>
+      <c r="D1803" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1803" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1803" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1803" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1803" s="80">
+        <v>101900104</v>
+      </c>
+      <c r="L1803" s="79" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L1752" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L1803" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A105">
@@ -55049,6 +56212,11 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A948">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1780">
+    <cfRule type="expression" dxfId="1" priority="499">
+      <formula>MOD($B1779,2)=1</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
     <cfRule type="duplicateValues" dxfId="0" priority="167"/>
@@ -55191,7 +56359,7 @@
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B257:B259 B261 B263 B265 B267 B269 B1333:L1660 B1676:L1048576">
+  <conditionalFormatting sqref="B257:B259 B261 B263 B265 B267 B269 B1333:L1660 B1676:L1778 B1779:F1779 H1779:L1779 B1780:F1780 H1780:L1780 B1781:L1048576">
     <cfRule type="expression" dxfId="1" priority="59">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
@@ -310,7 +310,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="299">
   <si>
     <t>id</t>
   </si>
@@ -1221,7 +1221,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1295,6 +1295,13 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1499,7 +1506,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1563,6 +1570,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1943,16 +1956,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1961,37 +1971,37 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2003,96 +2013,99 @@
     <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2337,6 +2350,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2426,6 +2442,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -6655,7 +6676,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:N1803"/>
+  <dimension ref="A1:N2136"/>
   <sheetFormatPr defaultColWidth="12.1833333333333" defaultRowHeight="18.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.1833333333333" style="8" customWidth="1"/>
@@ -16974,7 +16995,7 @@
       <c r="I346" s="9">
         <v>0</v>
       </c>
-      <c r="L346" s="86" t="s">
+      <c r="L346" s="87" t="s">
         <v>70</v>
       </c>
     </row>
@@ -55838,7 +55859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1793" customHeight="1" spans="1:12">
+    <row r="1793" customHeight="1" spans="1:13">
       <c r="A1793" s="2">
         <v>1019300608</v>
       </c>
@@ -55858,7 +55879,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="1794" customHeight="1" spans="1:12">
+    <row r="1794" customHeight="1" spans="1:13">
       <c r="A1794" s="2">
         <v>1019300609</v>
       </c>
@@ -55878,7 +55899,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="1795" customHeight="1" spans="1:12">
+    <row r="1795" customHeight="1" spans="1:13">
       <c r="A1795" s="2">
         <v>1019300610</v>
       </c>
@@ -55898,7 +55919,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="1796" customHeight="1" spans="1:12">
+    <row r="1796" customHeight="1" spans="1:13">
       <c r="A1796" s="2">
         <v>1019300611</v>
       </c>
@@ -55918,7 +55939,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="1797" customHeight="1" spans="1:12">
+    <row r="1797" customHeight="1" spans="1:13">
       <c r="A1797" s="2">
         <v>1019400401</v>
       </c>
@@ -55940,8 +55961,11 @@
       <c r="G1797" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="1798" customHeight="1" spans="1:12">
+      <c r="H1797" s="9">
+        <v>30190001</v>
+      </c>
+    </row>
+    <row r="1798" customHeight="1" spans="1:13">
       <c r="A1798" s="2">
         <v>1019400501</v>
       </c>
@@ -55963,8 +55987,11 @@
       <c r="G1798" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="1799" customHeight="1" spans="1:12">
+      <c r="H1798" s="9">
+        <v>30190002</v>
+      </c>
+    </row>
+    <row r="1799" customHeight="1" spans="1:13">
       <c r="A1799" s="2">
         <v>1019400601</v>
       </c>
@@ -55986,8 +56013,11 @@
       <c r="G1799" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="1800" customHeight="1" spans="1:12">
+      <c r="H1799" s="9">
+        <v>30190003</v>
+      </c>
+    </row>
+    <row r="1800" customHeight="1" spans="1:13">
       <c r="A1800" s="2">
         <v>1019400101</v>
       </c>
@@ -56016,7 +56046,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="1801" customHeight="1" spans="1:12">
+    <row r="1801" customHeight="1" spans="1:13">
       <c r="A1801" s="2">
         <v>1019400102</v>
       </c>
@@ -56045,7 +56075,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="1802" customHeight="1" spans="1:12">
+    <row r="1802" customHeight="1" spans="1:13">
       <c r="A1802" s="2">
         <v>1019400103</v>
       </c>
@@ -56074,7 +56104,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1803" customHeight="1" spans="1:12">
+    <row r="1803" customHeight="1" spans="1:13">
       <c r="A1803" s="2">
         <v>1019400104</v>
       </c>
@@ -56102,326 +56132,7913 @@
       <c r="L1803" s="79" t="s">
         <v>105</v>
       </c>
+    </row>
+    <row r="1804" customHeight="1" spans="1:13">
+      <c r="A1804" s="2">
+        <v>1052700401</v>
+      </c>
+      <c r="B1804" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1804" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1804" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1804" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1804" s="47">
+        <v>4</v>
+      </c>
+      <c r="G1804" s="74">
+        <v>2</v>
+      </c>
+      <c r="H1804" s="9"/>
+      <c r="I1804" s="9"/>
+      <c r="J1804" s="10"/>
+      <c r="K1804" s="2"/>
+      <c r="L1804" s="10"/>
+      <c r="M1804" s="75"/>
+    </row>
+    <row r="1805" customHeight="1" spans="1:13">
+      <c r="A1805" s="2">
+        <v>1052700402</v>
+      </c>
+      <c r="B1805" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1805" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1805" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1805" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1805" s="47">
+        <v>4</v>
+      </c>
+      <c r="G1805" s="74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1806" customHeight="1" spans="1:13">
+      <c r="A1806" s="2">
+        <v>1052700403</v>
+      </c>
+      <c r="B1806" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1806" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1806" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1806" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1806" s="47">
+        <v>4</v>
+      </c>
+      <c r="G1806" s="74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1807" customHeight="1" spans="1:13">
+      <c r="A1807" s="2">
+        <v>1052700404</v>
+      </c>
+      <c r="B1807" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1807" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1807" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1807" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1807" s="47">
+        <v>4</v>
+      </c>
+      <c r="G1807" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1808" customHeight="1" spans="1:13">
+      <c r="A1808" s="2">
+        <v>1052700405</v>
+      </c>
+      <c r="B1808" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1808" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1808" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1808" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1808" s="47">
+        <v>4</v>
+      </c>
+      <c r="G1808" s="74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1809" customHeight="1" spans="1:7">
+      <c r="A1809" s="2">
+        <v>1052700501</v>
+      </c>
+      <c r="B1809" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1809" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1809" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1809" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1809" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1809" s="74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1810" customHeight="1" spans="1:7">
+      <c r="A1810" s="2">
+        <v>1052700502</v>
+      </c>
+      <c r="B1810" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1810" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1810" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1810" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1810" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1810" s="74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1811" customHeight="1" spans="1:7">
+      <c r="A1811" s="2">
+        <v>1052700503</v>
+      </c>
+      <c r="B1811" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1811" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1811" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1811" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1811" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1811" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1812" customHeight="1" spans="1:7">
+      <c r="A1812" s="2">
+        <v>1052700504</v>
+      </c>
+      <c r="B1812" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1812" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1812" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1812" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1812" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1812" s="74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1813" customHeight="1" spans="1:7">
+      <c r="A1813" s="2">
+        <v>1052700505</v>
+      </c>
+      <c r="B1813" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1813" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1813" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1813" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1813" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1813" s="74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1814" customHeight="1" spans="1:7">
+      <c r="A1814" s="2">
+        <v>1052700506</v>
+      </c>
+      <c r="B1814" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1814" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1814" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1814" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1814" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1814" s="74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1815" customHeight="1" spans="1:7">
+      <c r="A1815" s="2">
+        <v>1052700507</v>
+      </c>
+      <c r="B1815" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1815" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1815" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1815" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1815" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1815" s="74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1816" customHeight="1" spans="1:7">
+      <c r="A1816" s="2">
+        <v>1052700508</v>
+      </c>
+      <c r="B1816" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1816" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1816" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1816" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1816" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1816" s="74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1817" customHeight="1" spans="1:7">
+      <c r="A1817" s="2">
+        <v>1052700509</v>
+      </c>
+      <c r="B1817" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1817" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1817" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1817" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1817" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1817" s="74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1818" customHeight="1" spans="1:7">
+      <c r="A1818" s="2">
+        <v>1052700510</v>
+      </c>
+      <c r="B1818" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1818" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1818" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1818" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1818" s="47">
+        <v>5</v>
+      </c>
+      <c r="G1818" s="74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1819" customHeight="1" spans="1:7">
+      <c r="A1819" s="2">
+        <v>1052700601</v>
+      </c>
+      <c r="B1819" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1819" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1819" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1819" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1819" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1819" s="74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1820" customHeight="1" spans="1:7">
+      <c r="A1820" s="2">
+        <v>1052700602</v>
+      </c>
+      <c r="B1820" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1820" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1820" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1820" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1820" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1820" s="74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1821" customHeight="1" spans="1:7">
+      <c r="A1821" s="2">
+        <v>1052700603</v>
+      </c>
+      <c r="B1821" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1821" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1821" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1821" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1821" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1821" s="74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1822" customHeight="1" spans="1:7">
+      <c r="A1822" s="2">
+        <v>1052700604</v>
+      </c>
+      <c r="B1822" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1822" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1822" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1822" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1822" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1822" s="74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1823" customHeight="1" spans="1:7">
+      <c r="A1823" s="2">
+        <v>1052700605</v>
+      </c>
+      <c r="B1823" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1823" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1823" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1823" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1823" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1823" s="74">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1824" customHeight="1" spans="1:7">
+      <c r="A1824" s="2">
+        <v>1052700606</v>
+      </c>
+      <c r="B1824" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1824" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1824" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1824" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1824" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1824" s="74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1825" customHeight="1" spans="1:7">
+      <c r="A1825" s="2">
+        <v>1052700607</v>
+      </c>
+      <c r="B1825" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1825" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1825" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1825" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1825" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1825" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1826" customHeight="1" spans="1:7">
+      <c r="A1826" s="2">
+        <v>1052700608</v>
+      </c>
+      <c r="B1826" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1826" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1826" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1826" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1826" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1826" s="74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1827" customHeight="1" spans="1:7">
+      <c r="A1827" s="2">
+        <v>1052700609</v>
+      </c>
+      <c r="B1827" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1827" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1827" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1827" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1827" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1827" s="74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1828" customHeight="1" spans="1:7">
+      <c r="A1828" s="2">
+        <v>1052700610</v>
+      </c>
+      <c r="B1828" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1828" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1828" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1828" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1828" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1828" s="74">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1829" customHeight="1" spans="1:7">
+      <c r="A1829" s="2">
+        <v>1052700611</v>
+      </c>
+      <c r="B1829" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1829" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1829" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1829" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1829" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1829" s="74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1830" customHeight="1" spans="1:7">
+      <c r="A1830" s="2">
+        <v>1052700612</v>
+      </c>
+      <c r="B1830" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1830" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1830" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1830" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1830" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1830" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1831" customHeight="1" spans="1:7">
+      <c r="A1831" s="2">
+        <v>1052700613</v>
+      </c>
+      <c r="B1831" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1831" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1831" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1831" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1831" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1831" s="74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1832" customHeight="1" spans="1:7">
+      <c r="A1832" s="2">
+        <v>1052700614</v>
+      </c>
+      <c r="B1832" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1832" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1832" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1832" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1832" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1832" s="74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1833" customHeight="1" spans="1:7">
+      <c r="A1833" s="2">
+        <v>1052700615</v>
+      </c>
+      <c r="B1833" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1833" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1833" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1833" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1833" s="47">
+        <v>6</v>
+      </c>
+      <c r="G1833" s="74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1834" customHeight="1" spans="1:7">
+      <c r="A1834" s="2">
+        <v>1052700701</v>
+      </c>
+      <c r="B1834" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1834" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1834" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1834" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1834" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1834" s="74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1835" customHeight="1" spans="1:7">
+      <c r="A1835" s="2">
+        <v>1052700702</v>
+      </c>
+      <c r="B1835" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1835" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1835" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1835" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1835" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1835" s="74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1836" customHeight="1" spans="1:7">
+      <c r="A1836" s="2">
+        <v>1052700703</v>
+      </c>
+      <c r="B1836" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1836" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1836" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1836" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1836" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1836" s="74">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1837" customHeight="1" spans="1:7">
+      <c r="A1837" s="2">
+        <v>1052700704</v>
+      </c>
+      <c r="B1837" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1837" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1837" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1837" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1837" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1837" s="74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1838" customHeight="1" spans="1:7">
+      <c r="A1838" s="2">
+        <v>1052700705</v>
+      </c>
+      <c r="B1838" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1838" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1838" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1838" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1838" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1838" s="74">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1839" customHeight="1" spans="1:7">
+      <c r="A1839" s="2">
+        <v>1052700706</v>
+      </c>
+      <c r="B1839" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1839" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1839" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1839" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1839" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1839" s="74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1840" customHeight="1" spans="1:7">
+      <c r="A1840" s="2">
+        <v>1052700707</v>
+      </c>
+      <c r="B1840" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1840" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1840" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1840" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1840" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1840" s="74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1841" customHeight="1" spans="1:7">
+      <c r="A1841" s="2">
+        <v>1052700708</v>
+      </c>
+      <c r="B1841" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1841" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1841" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1841" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1841" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1841" s="74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1842" customHeight="1" spans="1:7">
+      <c r="A1842" s="2">
+        <v>1052700709</v>
+      </c>
+      <c r="B1842" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1842" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1842" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1842" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1842" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1842" s="74">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1843" customHeight="1" spans="1:7">
+      <c r="A1843" s="2">
+        <v>1052700710</v>
+      </c>
+      <c r="B1843" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1843" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1843" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1843" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1843" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1843" s="74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1844" customHeight="1" spans="1:7">
+      <c r="A1844" s="2">
+        <v>1052700711</v>
+      </c>
+      <c r="B1844" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1844" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1844" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1844" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1844" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1844" s="74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1845" customHeight="1" spans="1:7">
+      <c r="A1845" s="2">
+        <v>1052700712</v>
+      </c>
+      <c r="B1845" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1845" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1845" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1845" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1845" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1845" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1846" customHeight="1" spans="1:7">
+      <c r="A1846" s="2">
+        <v>1052700713</v>
+      </c>
+      <c r="B1846" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1846" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1846" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1846" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1846" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1846" s="74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1847" customHeight="1" spans="1:7">
+      <c r="A1847" s="2">
+        <v>1052700714</v>
+      </c>
+      <c r="B1847" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1847" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1847" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1847" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1847" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1847" s="74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1848" customHeight="1" spans="1:7">
+      <c r="A1848" s="2">
+        <v>1052700715</v>
+      </c>
+      <c r="B1848" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1848" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1848" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1848" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1848" s="47">
+        <v>7</v>
+      </c>
+      <c r="G1848" s="74">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1849" customHeight="1" spans="1:7">
+      <c r="A1849" s="2">
+        <v>1052700801</v>
+      </c>
+      <c r="B1849" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1849" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1849" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1849" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1849" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1849" s="74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1850" customHeight="1" spans="1:7">
+      <c r="A1850" s="2">
+        <v>1052700802</v>
+      </c>
+      <c r="B1850" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1850" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1850" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1850" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1850" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1850" s="74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1851" customHeight="1" spans="1:7">
+      <c r="A1851" s="2">
+        <v>1052700803</v>
+      </c>
+      <c r="B1851" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1851" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1851" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1851" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1851" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1851" s="74">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1852" customHeight="1" spans="1:7">
+      <c r="A1852" s="2">
+        <v>1052700804</v>
+      </c>
+      <c r="B1852" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1852" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1852" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1852" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1852" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1852" s="74">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1853" customHeight="1" spans="1:7">
+      <c r="A1853" s="2">
+        <v>1052700805</v>
+      </c>
+      <c r="B1853" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1853" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1853" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1853" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1853" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1853" s="74">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1854" customHeight="1" spans="1:7">
+      <c r="A1854" s="2">
+        <v>1052700806</v>
+      </c>
+      <c r="B1854" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1854" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1854" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1854" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1854" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1854" s="74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1855" customHeight="1" spans="1:7">
+      <c r="A1855" s="2">
+        <v>1052700807</v>
+      </c>
+      <c r="B1855" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1855" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1855" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1855" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1855" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1855" s="74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1856" customHeight="1" spans="1:7">
+      <c r="A1856" s="2">
+        <v>1052700808</v>
+      </c>
+      <c r="B1856" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1856" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1856" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1856" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1856" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1856" s="74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1857" customHeight="1" spans="1:7">
+      <c r="A1857" s="2">
+        <v>1052700809</v>
+      </c>
+      <c r="B1857" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1857" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1857" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1857" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1857" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1857" s="74">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1858" customHeight="1" spans="1:7">
+      <c r="A1858" s="2">
+        <v>1052700810</v>
+      </c>
+      <c r="B1858" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1858" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1858" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1858" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1858" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1858" s="74">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1859" customHeight="1" spans="1:7">
+      <c r="A1859" s="2">
+        <v>1052700811</v>
+      </c>
+      <c r="B1859" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1859" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1859" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1859" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1859" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1859" s="74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1860" customHeight="1" spans="1:7">
+      <c r="A1860" s="2">
+        <v>1052700812</v>
+      </c>
+      <c r="B1860" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1860" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1860" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1860" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1860" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1860" s="74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1861" customHeight="1" spans="1:7">
+      <c r="A1861" s="2">
+        <v>1052700813</v>
+      </c>
+      <c r="B1861" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1861" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1861" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1861" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1861" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1861" s="74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1862" customHeight="1" spans="1:7">
+      <c r="A1862" s="2">
+        <v>1052700814</v>
+      </c>
+      <c r="B1862" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1862" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1862" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1862" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1862" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1862" s="74">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1863" customHeight="1" spans="1:7">
+      <c r="A1863" s="2">
+        <v>1052700815</v>
+      </c>
+      <c r="B1863" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1863" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1863" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1863" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1863" s="47">
+        <v>8</v>
+      </c>
+      <c r="G1863" s="74">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1864" customHeight="1" spans="1:7">
+      <c r="A1864" s="2">
+        <v>1052700901</v>
+      </c>
+      <c r="B1864" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1864" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1864" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1864" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1864" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1864" s="74">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1865" customHeight="1" spans="1:7">
+      <c r="A1865" s="2">
+        <v>1052700902</v>
+      </c>
+      <c r="B1865" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1865" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1865" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1865" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1865" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1865" s="74">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1866" customHeight="1" spans="1:7">
+      <c r="A1866" s="2">
+        <v>1052700903</v>
+      </c>
+      <c r="B1866" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1866" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1866" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1866" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1866" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1866" s="74">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1867" customHeight="1" spans="1:7">
+      <c r="A1867" s="2">
+        <v>1052700904</v>
+      </c>
+      <c r="B1867" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1867" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1867" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1867" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1867" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1867" s="74">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1868" customHeight="1" spans="1:7">
+      <c r="A1868" s="2">
+        <v>1052700905</v>
+      </c>
+      <c r="B1868" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1868" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1868" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1868" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1868" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1868" s="74">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1869" customHeight="1" spans="1:7">
+      <c r="A1869" s="2">
+        <v>1052700906</v>
+      </c>
+      <c r="B1869" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1869" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1869" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1869" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1869" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1869" s="74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1870" customHeight="1" spans="1:7">
+      <c r="A1870" s="2">
+        <v>1052700907</v>
+      </c>
+      <c r="B1870" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1870" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1870" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1870" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1870" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1870" s="74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1871" customHeight="1" spans="1:7">
+      <c r="A1871" s="2">
+        <v>1052700908</v>
+      </c>
+      <c r="B1871" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1871" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1871" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1871" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1871" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1871" s="74">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1872" customHeight="1" spans="1:7">
+      <c r="A1872" s="2">
+        <v>1052700909</v>
+      </c>
+      <c r="B1872" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1872" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1872" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1872" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1872" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1872" s="74">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1873" customHeight="1" spans="1:7">
+      <c r="A1873" s="2">
+        <v>1052700910</v>
+      </c>
+      <c r="B1873" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1873" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1873" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1873" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1873" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1873" s="74">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1874" customHeight="1" spans="1:7">
+      <c r="A1874" s="2">
+        <v>1052700911</v>
+      </c>
+      <c r="B1874" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1874" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1874" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1874" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1874" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1874" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1875" customHeight="1" spans="1:7">
+      <c r="A1875" s="2">
+        <v>1052700912</v>
+      </c>
+      <c r="B1875" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1875" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1875" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1875" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1875" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1875" s="74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1876" customHeight="1" spans="1:7">
+      <c r="A1876" s="2">
+        <v>1052700913</v>
+      </c>
+      <c r="B1876" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1876" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1876" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1876" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1876" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1876" s="74">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1877" customHeight="1" spans="1:7">
+      <c r="A1877" s="2">
+        <v>1052700914</v>
+      </c>
+      <c r="B1877" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1877" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1877" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1877" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1877" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1877" s="74">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1878" customHeight="1" spans="1:7">
+      <c r="A1878" s="2">
+        <v>1052700915</v>
+      </c>
+      <c r="B1878" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1878" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1878" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1878" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1878" s="47">
+        <v>9</v>
+      </c>
+      <c r="G1878" s="74">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1879" customHeight="1" spans="1:7">
+      <c r="A1879" s="2">
+        <v>1052701001</v>
+      </c>
+      <c r="B1879" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1879" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1879" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1879" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1879" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1879" s="74">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1880" customHeight="1" spans="1:7">
+      <c r="A1880" s="2">
+        <v>1052701002</v>
+      </c>
+      <c r="B1880" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1880" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1880" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1880" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1880" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1880" s="74">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1881" customHeight="1" spans="1:7">
+      <c r="A1881" s="2">
+        <v>1052701003</v>
+      </c>
+      <c r="B1881" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1881" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1881" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1881" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1881" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1881" s="74">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1882" customHeight="1" spans="1:7">
+      <c r="A1882" s="2">
+        <v>1052701004</v>
+      </c>
+      <c r="B1882" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1882" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1882" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1882" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1882" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1882" s="74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1883" customHeight="1" spans="1:7">
+      <c r="A1883" s="2">
+        <v>1052701005</v>
+      </c>
+      <c r="B1883" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1883" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1883" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1883" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1883" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1883" s="74">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1884" customHeight="1" spans="1:7">
+      <c r="A1884" s="2">
+        <v>1052701006</v>
+      </c>
+      <c r="B1884" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1884" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1884" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1884" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1884" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1884" s="74">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1885" customHeight="1" spans="1:7">
+      <c r="A1885" s="2">
+        <v>1052701007</v>
+      </c>
+      <c r="B1885" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1885" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1885" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1885" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1885" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1885" s="74">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1886" customHeight="1" spans="1:7">
+      <c r="A1886" s="2">
+        <v>1052701008</v>
+      </c>
+      <c r="B1886" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1886" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1886" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1886" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1886" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1886" s="74">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1887" customHeight="1" spans="1:7">
+      <c r="A1887" s="2">
+        <v>1052701009</v>
+      </c>
+      <c r="B1887" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1887" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1887" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1887" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1887" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1887" s="74">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1888" customHeight="1" spans="1:7">
+      <c r="A1888" s="2">
+        <v>1052701010</v>
+      </c>
+      <c r="B1888" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1888" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1888" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1888" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1888" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1888" s="74">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1889" customHeight="1" spans="1:7">
+      <c r="A1889" s="2">
+        <v>1052701011</v>
+      </c>
+      <c r="B1889" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1889" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1889" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1889" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1889" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1889" s="74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1890" customHeight="1" spans="1:7">
+      <c r="A1890" s="2">
+        <v>1052701012</v>
+      </c>
+      <c r="B1890" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1890" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1890" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1890" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1890" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1890" s="74">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1891" customHeight="1" spans="1:7">
+      <c r="A1891" s="2">
+        <v>1052701013</v>
+      </c>
+      <c r="B1891" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1891" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1891" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1891" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1891" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1891" s="74">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1892" customHeight="1" spans="1:7">
+      <c r="A1892" s="2">
+        <v>1052701014</v>
+      </c>
+      <c r="B1892" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1892" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1892" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1892" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1892" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1892" s="74">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1893" customHeight="1" spans="1:7">
+      <c r="A1893" s="2">
+        <v>1052701015</v>
+      </c>
+      <c r="B1893" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1893" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1893" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1893" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1893" s="47">
+        <v>10</v>
+      </c>
+      <c r="G1893" s="74">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1894" customHeight="1" spans="1:7">
+      <c r="A1894" s="2">
+        <v>1052701101</v>
+      </c>
+      <c r="B1894" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1894" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1894" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1894" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1894" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1894" s="74">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1895" customHeight="1" spans="1:7">
+      <c r="A1895" s="2">
+        <v>1052701102</v>
+      </c>
+      <c r="B1895" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1895" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1895" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1895" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1895" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1895" s="74">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1896" customHeight="1" spans="1:7">
+      <c r="A1896" s="2">
+        <v>1052701103</v>
+      </c>
+      <c r="B1896" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1896" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1896" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1896" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1896" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1896" s="74">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1897" customHeight="1" spans="1:7">
+      <c r="A1897" s="2">
+        <v>1052701104</v>
+      </c>
+      <c r="B1897" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1897" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1897" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1897" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1897" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1897" s="74">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1898" customHeight="1" spans="1:7">
+      <c r="A1898" s="2">
+        <v>1052701105</v>
+      </c>
+      <c r="B1898" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1898" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1898" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1898" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1898" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1898" s="74">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1899" customHeight="1" spans="1:7">
+      <c r="A1899" s="2">
+        <v>1052701106</v>
+      </c>
+      <c r="B1899" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1899" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1899" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1899" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1899" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1899" s="74">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1900" customHeight="1" spans="1:7">
+      <c r="A1900" s="2">
+        <v>1052701107</v>
+      </c>
+      <c r="B1900" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1900" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1900" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1900" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1900" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1900" s="74">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1901" customHeight="1" spans="1:7">
+      <c r="A1901" s="2">
+        <v>1052701108</v>
+      </c>
+      <c r="B1901" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1901" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1901" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1901" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1901" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1901" s="74">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1902" customHeight="1" spans="1:7">
+      <c r="A1902" s="2">
+        <v>1052701109</v>
+      </c>
+      <c r="B1902" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1902" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1902" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1902" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1902" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1902" s="74">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1903" customHeight="1" spans="1:7">
+      <c r="A1903" s="2">
+        <v>1052701110</v>
+      </c>
+      <c r="B1903" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1903" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1903" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1903" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1903" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1903" s="74">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1904" customHeight="1" spans="1:7">
+      <c r="A1904" s="2">
+        <v>1052701111</v>
+      </c>
+      <c r="B1904" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1904" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1904" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1904" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1904" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1904" s="74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1905" customHeight="1" spans="1:7">
+      <c r="A1905" s="2">
+        <v>1052701112</v>
+      </c>
+      <c r="B1905" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1905" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1905" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1905" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1905" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1905" s="74">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1906" customHeight="1" spans="1:7">
+      <c r="A1906" s="2">
+        <v>1052701113</v>
+      </c>
+      <c r="B1906" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1906" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1906" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1906" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1906" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1906" s="74">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1907" customHeight="1" spans="1:7">
+      <c r="A1907" s="2">
+        <v>1052701114</v>
+      </c>
+      <c r="B1907" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1907" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1907" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1907" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1907" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1907" s="74">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1908" customHeight="1" spans="1:7">
+      <c r="A1908" s="2">
+        <v>1052701115</v>
+      </c>
+      <c r="B1908" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1908" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1908" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1908" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1908" s="47">
+        <v>11</v>
+      </c>
+      <c r="G1908" s="74">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1909" customHeight="1" spans="1:7">
+      <c r="A1909" s="2">
+        <v>1052701201</v>
+      </c>
+      <c r="B1909" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1909" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1909" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1909" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1909" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1909" s="74">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1910" customHeight="1" spans="1:7">
+      <c r="A1910" s="2">
+        <v>1052701202</v>
+      </c>
+      <c r="B1910" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1910" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1910" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1910" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1910" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1910" s="74">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1911" customHeight="1" spans="1:7">
+      <c r="A1911" s="2">
+        <v>1052701203</v>
+      </c>
+      <c r="B1911" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1911" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1911" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1911" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1911" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1911" s="74">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1912" customHeight="1" spans="1:7">
+      <c r="A1912" s="2">
+        <v>1052701204</v>
+      </c>
+      <c r="B1912" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1912" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1912" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1912" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1912" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1912" s="74">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1913" customHeight="1" spans="1:7">
+      <c r="A1913" s="2">
+        <v>1052701205</v>
+      </c>
+      <c r="B1913" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1913" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1913" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1913" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1913" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1913" s="74">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1914" customHeight="1" spans="1:7">
+      <c r="A1914" s="2">
+        <v>1052701206</v>
+      </c>
+      <c r="B1914" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1914" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1914" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1914" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1914" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1914" s="74">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1915" customHeight="1" spans="1:7">
+      <c r="A1915" s="2">
+        <v>1052701207</v>
+      </c>
+      <c r="B1915" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1915" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1915" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1915" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1915" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1915" s="74">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1916" customHeight="1" spans="1:7">
+      <c r="A1916" s="2">
+        <v>1052701208</v>
+      </c>
+      <c r="B1916" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1916" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1916" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1916" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1916" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1916" s="74">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1917" customHeight="1" spans="1:7">
+      <c r="A1917" s="2">
+        <v>1052701209</v>
+      </c>
+      <c r="B1917" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1917" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1917" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1917" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1917" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1917" s="74">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1918" customHeight="1" spans="1:7">
+      <c r="A1918" s="2">
+        <v>1052701210</v>
+      </c>
+      <c r="B1918" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1918" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1918" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1918" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1918" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1918" s="74">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1919" customHeight="1" spans="1:7">
+      <c r="A1919" s="2">
+        <v>1052701211</v>
+      </c>
+      <c r="B1919" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1919" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1919" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1919" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1919" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1919" s="74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1920" customHeight="1" spans="1:7">
+      <c r="A1920" s="2">
+        <v>1052701212</v>
+      </c>
+      <c r="B1920" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1920" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1920" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1920" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1920" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1920" s="74">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1921" customHeight="1" spans="1:7">
+      <c r="A1921" s="2">
+        <v>1052701213</v>
+      </c>
+      <c r="B1921" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1921" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1921" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1921" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1921" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1921" s="74">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1922" customHeight="1" spans="1:7">
+      <c r="A1922" s="2">
+        <v>1052701214</v>
+      </c>
+      <c r="B1922" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1922" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1922" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1922" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1922" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1922" s="74">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1923" customHeight="1" spans="1:7">
+      <c r="A1923" s="2">
+        <v>1052701215</v>
+      </c>
+      <c r="B1923" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1923" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1923" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1923" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1923" s="47">
+        <v>12</v>
+      </c>
+      <c r="G1923" s="74">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1924" customHeight="1" spans="1:7">
+      <c r="A1924" s="2">
+        <v>1052701301</v>
+      </c>
+      <c r="B1924" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1924" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1924" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1924" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1924" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1924" s="74">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1925" customHeight="1" spans="1:7">
+      <c r="A1925" s="2">
+        <v>1052701302</v>
+      </c>
+      <c r="B1925" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1925" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1925" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1925" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1925" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1925" s="74">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1926" customHeight="1" spans="1:7">
+      <c r="A1926" s="2">
+        <v>1052701303</v>
+      </c>
+      <c r="B1926" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1926" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1926" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1926" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1926" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1926" s="74">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1927" customHeight="1" spans="1:7">
+      <c r="A1927" s="2">
+        <v>1052701304</v>
+      </c>
+      <c r="B1927" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1927" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1927" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1927" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1927" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1927" s="74">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1928" customHeight="1" spans="1:7">
+      <c r="A1928" s="2">
+        <v>1052701305</v>
+      </c>
+      <c r="B1928" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1928" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1928" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1928" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1928" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1928" s="74">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="1929" customHeight="1" spans="1:7">
+      <c r="A1929" s="2">
+        <v>1052701306</v>
+      </c>
+      <c r="B1929" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1929" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1929" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1929" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1929" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1929" s="74">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1930" customHeight="1" spans="1:7">
+      <c r="A1930" s="2">
+        <v>1052701307</v>
+      </c>
+      <c r="B1930" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1930" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1930" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1930" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1930" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1930" s="74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1931" customHeight="1" spans="1:7">
+      <c r="A1931" s="2">
+        <v>1052701308</v>
+      </c>
+      <c r="B1931" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1931" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1931" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1931" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1931" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1931" s="74">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1932" customHeight="1" spans="1:7">
+      <c r="A1932" s="2">
+        <v>1052701309</v>
+      </c>
+      <c r="B1932" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1932" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1932" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1932" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1932" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1932" s="74">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1933" customHeight="1" spans="1:7">
+      <c r="A1933" s="2">
+        <v>1052701310</v>
+      </c>
+      <c r="B1933" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1933" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1933" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1933" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1933" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1933" s="74">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1934" customHeight="1" spans="1:7">
+      <c r="A1934" s="2">
+        <v>1052701311</v>
+      </c>
+      <c r="B1934" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1934" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1934" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1934" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1934" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1934" s="74">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1935" customHeight="1" spans="1:7">
+      <c r="A1935" s="2">
+        <v>1052701312</v>
+      </c>
+      <c r="B1935" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1935" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1935" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1935" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1935" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1935" s="74">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1936" customHeight="1" spans="1:7">
+      <c r="A1936" s="2">
+        <v>1052701313</v>
+      </c>
+      <c r="B1936" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1936" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1936" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1936" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1936" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1936" s="74">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1937" customHeight="1" spans="1:7">
+      <c r="A1937" s="2">
+        <v>1052701314</v>
+      </c>
+      <c r="B1937" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1937" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1937" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1937" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1937" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1937" s="74">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1938" customHeight="1" spans="1:7">
+      <c r="A1938" s="2">
+        <v>1052701315</v>
+      </c>
+      <c r="B1938" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1938" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1938" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1938" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1938" s="47">
+        <v>13</v>
+      </c>
+      <c r="G1938" s="74">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1939" customHeight="1" spans="1:7">
+      <c r="A1939" s="2">
+        <v>1052701401</v>
+      </c>
+      <c r="B1939" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1939" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1939" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1939" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1939" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1939" s="74">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1940" customHeight="1" spans="1:7">
+      <c r="A1940" s="2">
+        <v>1052701402</v>
+      </c>
+      <c r="B1940" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1940" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1940" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1940" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1940" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1940" s="74">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1941" customHeight="1" spans="1:7">
+      <c r="A1941" s="2">
+        <v>1052701403</v>
+      </c>
+      <c r="B1941" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1941" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1941" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1941" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1941" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1941" s="74">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1942" customHeight="1" spans="1:7">
+      <c r="A1942" s="2">
+        <v>1052701404</v>
+      </c>
+      <c r="B1942" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1942" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1942" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1942" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1942" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1942" s="74">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="1943" customHeight="1" spans="1:7">
+      <c r="A1943" s="2">
+        <v>1052701405</v>
+      </c>
+      <c r="B1943" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1943" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1943" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1943" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1943" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1943" s="74">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="1944" customHeight="1" spans="1:7">
+      <c r="A1944" s="2">
+        <v>1052701406</v>
+      </c>
+      <c r="B1944" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1944" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1944" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1944" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1944" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1944" s="74">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1945" customHeight="1" spans="1:7">
+      <c r="A1945" s="2">
+        <v>1052701407</v>
+      </c>
+      <c r="B1945" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1945" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1945" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1945" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1945" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1945" s="74">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1946" customHeight="1" spans="1:7">
+      <c r="A1946" s="2">
+        <v>1052701408</v>
+      </c>
+      <c r="B1946" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1946" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1946" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1946" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1946" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1946" s="74">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1947" customHeight="1" spans="1:7">
+      <c r="A1947" s="2">
+        <v>1052701409</v>
+      </c>
+      <c r="B1947" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1947" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1947" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1947" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1947" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1947" s="74">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="1948" customHeight="1" spans="1:7">
+      <c r="A1948" s="2">
+        <v>1052701410</v>
+      </c>
+      <c r="B1948" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1948" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1948" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1948" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1948" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1948" s="74">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="1949" customHeight="1" spans="1:7">
+      <c r="A1949" s="2">
+        <v>1052701411</v>
+      </c>
+      <c r="B1949" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1949" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1949" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1949" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1949" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1949" s="74">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1950" customHeight="1" spans="1:7">
+      <c r="A1950" s="2">
+        <v>1052701412</v>
+      </c>
+      <c r="B1950" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1950" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1950" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1950" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1950" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1950" s="74">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1951" customHeight="1" spans="1:7">
+      <c r="A1951" s="2">
+        <v>1052701413</v>
+      </c>
+      <c r="B1951" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1951" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1951" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1951" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1951" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1951" s="74">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1952" customHeight="1" spans="1:7">
+      <c r="A1952" s="2">
+        <v>1052701414</v>
+      </c>
+      <c r="B1952" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1952" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1952" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1952" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1952" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1952" s="74">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1953" customHeight="1" spans="1:7">
+      <c r="A1953" s="2">
+        <v>1052701415</v>
+      </c>
+      <c r="B1953" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1953" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1953" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1953" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1953" s="47">
+        <v>14</v>
+      </c>
+      <c r="G1953" s="74">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1954" customHeight="1" spans="1:7">
+      <c r="A1954" s="2">
+        <v>1052701501</v>
+      </c>
+      <c r="B1954" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1954" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1954" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1954" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1954" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1954" s="74">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1955" customHeight="1" spans="1:7">
+      <c r="A1955" s="2">
+        <v>1052701502</v>
+      </c>
+      <c r="B1955" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1955" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1955" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1955" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1955" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1955" s="74">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1956" customHeight="1" spans="1:7">
+      <c r="A1956" s="2">
+        <v>1052701503</v>
+      </c>
+      <c r="B1956" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1956" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1956" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1956" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1956" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1956" s="74">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="1957" customHeight="1" spans="1:7">
+      <c r="A1957" s="2">
+        <v>1052701504</v>
+      </c>
+      <c r="B1957" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1957" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1957" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1957" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1957" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1957" s="74">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="1958" customHeight="1" spans="1:7">
+      <c r="A1958" s="2">
+        <v>1052701505</v>
+      </c>
+      <c r="B1958" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1958" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1958" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1958" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1958" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1958" s="74">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1959" customHeight="1" spans="1:7">
+      <c r="A1959" s="2">
+        <v>1052701506</v>
+      </c>
+      <c r="B1959" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1959" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1959" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1959" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1959" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1959" s="74">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1960" customHeight="1" spans="1:7">
+      <c r="A1960" s="2">
+        <v>1052701507</v>
+      </c>
+      <c r="B1960" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1960" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1960" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1960" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1960" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1960" s="74">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1961" customHeight="1" spans="1:7">
+      <c r="A1961" s="2">
+        <v>1052701508</v>
+      </c>
+      <c r="B1961" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1961" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1961" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1961" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1961" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1961" s="74">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="1962" customHeight="1" spans="1:7">
+      <c r="A1962" s="2">
+        <v>1052701509</v>
+      </c>
+      <c r="B1962" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1962" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1962" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1962" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1962" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1962" s="74">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="1963" customHeight="1" spans="1:7">
+      <c r="A1963" s="2">
+        <v>1052701510</v>
+      </c>
+      <c r="B1963" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1963" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1963" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1963" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1963" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1963" s="74">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1964" customHeight="1" spans="1:7">
+      <c r="A1964" s="2">
+        <v>1052701511</v>
+      </c>
+      <c r="B1964" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1964" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1964" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1964" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1964" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1964" s="74">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1965" customHeight="1" spans="1:7">
+      <c r="A1965" s="2">
+        <v>1052701512</v>
+      </c>
+      <c r="B1965" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1965" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1965" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1965" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1965" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1965" s="74">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1966" customHeight="1" spans="1:7">
+      <c r="A1966" s="2">
+        <v>1052701513</v>
+      </c>
+      <c r="B1966" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1966" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1966" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1966" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1966" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1966" s="74">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1967" customHeight="1" spans="1:7">
+      <c r="A1967" s="2">
+        <v>1052701514</v>
+      </c>
+      <c r="B1967" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1967" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1967" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1967" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1967" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1967" s="74">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1968" customHeight="1" spans="1:7">
+      <c r="A1968" s="2">
+        <v>1052701515</v>
+      </c>
+      <c r="B1968" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1968" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1968" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1968" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1968" s="47">
+        <v>15</v>
+      </c>
+      <c r="G1968" s="74">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1969" customHeight="1" spans="1:7">
+      <c r="A1969" s="2">
+        <v>1052701601</v>
+      </c>
+      <c r="B1969" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1969" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1969" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1969" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1969" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1969" s="74">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1970" customHeight="1" spans="1:7">
+      <c r="A1970" s="2">
+        <v>1052701602</v>
+      </c>
+      <c r="B1970" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1970" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1970" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1970" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1970" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1970" s="74">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="1971" customHeight="1" spans="1:7">
+      <c r="A1971" s="2">
+        <v>1052701603</v>
+      </c>
+      <c r="B1971" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1971" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1971" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1971" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1971" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1971" s="74">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="1972" customHeight="1" spans="1:7">
+      <c r="A1972" s="2">
+        <v>1052701604</v>
+      </c>
+      <c r="B1972" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1972" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1972" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1972" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1972" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1972" s="74">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1973" customHeight="1" spans="1:7">
+      <c r="A1973" s="2">
+        <v>1052701605</v>
+      </c>
+      <c r="B1973" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1973" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1973" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1973" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1973" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1973" s="74">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="1974" customHeight="1" spans="1:7">
+      <c r="A1974" s="2">
+        <v>1052701606</v>
+      </c>
+      <c r="B1974" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1974" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1974" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1974" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1974" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1974" s="74">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1975" customHeight="1" spans="1:7">
+      <c r="A1975" s="2">
+        <v>1052701607</v>
+      </c>
+      <c r="B1975" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1975" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1975" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1975" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1975" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1975" s="74">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1976" customHeight="1" spans="1:7">
+      <c r="A1976" s="2">
+        <v>1052701608</v>
+      </c>
+      <c r="B1976" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1976" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1976" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1976" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1976" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1976" s="74">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="1977" customHeight="1" spans="1:7">
+      <c r="A1977" s="2">
+        <v>1052701609</v>
+      </c>
+      <c r="B1977" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1977" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1977" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1977" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1977" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1977" s="74">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1978" customHeight="1" spans="1:7">
+      <c r="A1978" s="2">
+        <v>1052701610</v>
+      </c>
+      <c r="B1978" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1978" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1978" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1978" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1978" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1978" s="74">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="1979" customHeight="1" spans="1:7">
+      <c r="A1979" s="2">
+        <v>1052701611</v>
+      </c>
+      <c r="B1979" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1979" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1979" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1979" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1979" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1979" s="74">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1980" customHeight="1" spans="1:7">
+      <c r="A1980" s="2">
+        <v>1052701612</v>
+      </c>
+      <c r="B1980" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1980" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1980" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1980" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1980" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1980" s="74">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1981" customHeight="1" spans="1:7">
+      <c r="A1981" s="2">
+        <v>1052701613</v>
+      </c>
+      <c r="B1981" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1981" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1981" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1981" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1981" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1981" s="74">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1982" customHeight="1" spans="1:7">
+      <c r="A1982" s="2">
+        <v>1052701614</v>
+      </c>
+      <c r="B1982" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1982" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1982" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1982" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1982" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1982" s="74">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="1983" customHeight="1" spans="1:7">
+      <c r="A1983" s="2">
+        <v>1052701615</v>
+      </c>
+      <c r="B1983" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1983" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1983" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1983" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1983" s="47">
+        <v>16</v>
+      </c>
+      <c r="G1983" s="74">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1984" customHeight="1" spans="1:7">
+      <c r="A1984" s="2">
+        <v>1052701701</v>
+      </c>
+      <c r="B1984" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1984" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1984" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1984" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1984" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1984" s="74">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1985" customHeight="1" spans="1:7">
+      <c r="A1985" s="2">
+        <v>1052701702</v>
+      </c>
+      <c r="B1985" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1985" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1985" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1985" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1985" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1985" s="74">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1986" customHeight="1" spans="1:7">
+      <c r="A1986" s="2">
+        <v>1052701703</v>
+      </c>
+      <c r="B1986" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1986" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1986" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1986" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1986" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1986" s="74">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="1987" customHeight="1" spans="1:7">
+      <c r="A1987" s="2">
+        <v>1052701704</v>
+      </c>
+      <c r="B1987" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1987" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1987" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1987" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1987" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1987" s="74">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="1988" customHeight="1" spans="1:7">
+      <c r="A1988" s="2">
+        <v>1052701705</v>
+      </c>
+      <c r="B1988" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1988" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1988" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1988" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1988" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1988" s="74">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="1989" customHeight="1" spans="1:7">
+      <c r="A1989" s="2">
+        <v>1052701706</v>
+      </c>
+      <c r="B1989" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1989" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1989" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1989" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1989" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1989" s="74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1990" customHeight="1" spans="1:7">
+      <c r="A1990" s="2">
+        <v>1052701707</v>
+      </c>
+      <c r="B1990" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1990" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1990" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1990" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1990" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1990" s="74">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1991" customHeight="1" spans="1:7">
+      <c r="A1991" s="2">
+        <v>1052701708</v>
+      </c>
+      <c r="B1991" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1991" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1991" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1991" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1991" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1991" s="74">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1992" customHeight="1" spans="1:7">
+      <c r="A1992" s="2">
+        <v>1052701709</v>
+      </c>
+      <c r="B1992" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1992" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1992" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1992" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1992" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1992" s="74">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="1993" customHeight="1" spans="1:7">
+      <c r="A1993" s="2">
+        <v>1052701710</v>
+      </c>
+      <c r="B1993" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1993" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1993" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1993" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1993" s="47">
+        <v>17</v>
+      </c>
+      <c r="G1993" s="74">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="1994" customHeight="1" spans="1:7">
+      <c r="A1994" s="2">
+        <v>1052701801</v>
+      </c>
+      <c r="B1994" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1994" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1994" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1994" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1994" s="47">
+        <v>18</v>
+      </c>
+      <c r="G1994" s="74">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1995" customHeight="1" spans="1:7">
+      <c r="A1995" s="2">
+        <v>1052701802</v>
+      </c>
+      <c r="B1995" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1995" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1995" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1995" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1995" s="47">
+        <v>18</v>
+      </c>
+      <c r="G1995" s="74">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="1996" customHeight="1" spans="1:7">
+      <c r="A1996" s="2">
+        <v>1052701803</v>
+      </c>
+      <c r="B1996" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1996" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1996" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1996" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1996" s="47">
+        <v>18</v>
+      </c>
+      <c r="G1996" s="74">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="1997" customHeight="1" spans="1:7">
+      <c r="A1997" s="2">
+        <v>1052701804</v>
+      </c>
+      <c r="B1997" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1997" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1997" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1997" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1997" s="47">
+        <v>18</v>
+      </c>
+      <c r="G1997" s="74">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1998" customHeight="1" spans="1:7">
+      <c r="A1998" s="2">
+        <v>1052701805</v>
+      </c>
+      <c r="B1998" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1998" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1998" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1998" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1998" s="47">
+        <v>18</v>
+      </c>
+      <c r="G1998" s="74">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1999" customHeight="1" spans="1:7">
+      <c r="A1999" s="2">
+        <v>1052701806</v>
+      </c>
+      <c r="B1999" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C1999" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1999" s="55">
+        <v>7</v>
+      </c>
+      <c r="E1999" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1999" s="47">
+        <v>18</v>
+      </c>
+      <c r="G1999" s="74">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2000" customHeight="1" spans="1:7">
+      <c r="A2000" s="2">
+        <v>1052701807</v>
+      </c>
+      <c r="B2000" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2000" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2000" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2000" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2000" s="47">
+        <v>18</v>
+      </c>
+      <c r="G2000" s="74">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2001" customHeight="1" spans="1:7">
+      <c r="A2001" s="2">
+        <v>1052701808</v>
+      </c>
+      <c r="B2001" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2001" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2001" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2001" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2001" s="47">
+        <v>18</v>
+      </c>
+      <c r="G2001" s="74">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2002" customHeight="1" spans="1:7">
+      <c r="A2002" s="2">
+        <v>1052701809</v>
+      </c>
+      <c r="B2002" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2002" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2002" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2002" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2002" s="47">
+        <v>18</v>
+      </c>
+      <c r="G2002" s="74">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2003" customHeight="1" spans="1:7">
+      <c r="A2003" s="2">
+        <v>1052701810</v>
+      </c>
+      <c r="B2003" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2003" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2003" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2003" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2003" s="47">
+        <v>18</v>
+      </c>
+      <c r="G2003" s="74">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="2004" customHeight="1" spans="1:7">
+      <c r="A2004" s="2">
+        <v>1052701901</v>
+      </c>
+      <c r="B2004" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2004" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2004" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2004" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2004" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2004" s="86">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2005" customHeight="1" spans="1:7">
+      <c r="A2005" s="2">
+        <v>1052701902</v>
+      </c>
+      <c r="B2005" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2005" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2005" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2005" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2005" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2005" s="74">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2006" customHeight="1" spans="1:7">
+      <c r="A2006" s="2">
+        <v>1052701903</v>
+      </c>
+      <c r="B2006" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2006" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2006" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2006" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2006" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2006" s="74">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2007" customHeight="1" spans="1:7">
+      <c r="A2007" s="2">
+        <v>1052701904</v>
+      </c>
+      <c r="B2007" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2007" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2007" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2007" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2007" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2007" s="74">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="2008" customHeight="1" spans="1:7">
+      <c r="A2008" s="2">
+        <v>1052701905</v>
+      </c>
+      <c r="B2008" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2008" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2008" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2008" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2008" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2008" s="74">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="2009" customHeight="1" spans="1:7">
+      <c r="A2009" s="2">
+        <v>1052701906</v>
+      </c>
+      <c r="B2009" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2009" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2009" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2009" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2009" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2009" s="74">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2010" customHeight="1" spans="1:7">
+      <c r="A2010" s="2">
+        <v>1052701907</v>
+      </c>
+      <c r="B2010" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2010" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2010" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2010" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2010" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2010" s="74">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2011" customHeight="1" spans="1:7">
+      <c r="A2011" s="2">
+        <v>1052701908</v>
+      </c>
+      <c r="B2011" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2011" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2011" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2011" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2011" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2011" s="74">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2012" customHeight="1" spans="1:7">
+      <c r="A2012" s="2">
+        <v>1052701909</v>
+      </c>
+      <c r="B2012" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2012" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2012" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2012" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2012" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2012" s="74">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="2013" customHeight="1" spans="1:7">
+      <c r="A2013" s="2">
+        <v>1052701910</v>
+      </c>
+      <c r="B2013" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2013" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2013" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2013" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2013" s="47">
+        <v>19</v>
+      </c>
+      <c r="G2013" s="74">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="2014" customHeight="1" spans="1:7">
+      <c r="A2014" s="2">
+        <v>1052702001</v>
+      </c>
+      <c r="B2014" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2014" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2014" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2014" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2014" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2014" s="74">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2015" customHeight="1" spans="1:7">
+      <c r="A2015" s="2">
+        <v>1052702002</v>
+      </c>
+      <c r="B2015" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2015" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2015" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2015" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2015" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2015" s="74">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2016" customHeight="1" spans="1:7">
+      <c r="A2016" s="2">
+        <v>1052702003</v>
+      </c>
+      <c r="B2016" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2016" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2016" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2016" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2016" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2016" s="74">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="2017" customHeight="1" spans="1:7">
+      <c r="A2017" s="2">
+        <v>1052702004</v>
+      </c>
+      <c r="B2017" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2017" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2017" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2017" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2017" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2017" s="74">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="2018" customHeight="1" spans="1:7">
+      <c r="A2018" s="2">
+        <v>1052702005</v>
+      </c>
+      <c r="B2018" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2018" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2018" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2018" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2018" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2018" s="74">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="2019" customHeight="1" spans="1:7">
+      <c r="A2019" s="2">
+        <v>1052702006</v>
+      </c>
+      <c r="B2019" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2019" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2019" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2019" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2019" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2019" s="74">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2020" customHeight="1" spans="1:7">
+      <c r="A2020" s="2">
+        <v>1052702007</v>
+      </c>
+      <c r="B2020" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2020" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2020" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2020" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2020" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2020" s="74">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2021" customHeight="1" spans="1:7">
+      <c r="A2021" s="2">
+        <v>1052702008</v>
+      </c>
+      <c r="B2021" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2021" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2021" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2021" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2021" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2021" s="74">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="2022" customHeight="1" spans="1:7">
+      <c r="A2022" s="2">
+        <v>1052702009</v>
+      </c>
+      <c r="B2022" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2022" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2022" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2022" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2022" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2022" s="74">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="2023" customHeight="1" spans="1:7">
+      <c r="A2023" s="2">
+        <v>1052702010</v>
+      </c>
+      <c r="B2023" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2023" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2023" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2023" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2023" s="47">
+        <v>20</v>
+      </c>
+      <c r="G2023" s="74">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="2024" customHeight="1" spans="1:7">
+      <c r="A2024" s="2">
+        <v>1052702101</v>
+      </c>
+      <c r="B2024" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2024" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2024" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2024" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2024" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2024" s="74">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2025" customHeight="1" spans="1:7">
+      <c r="A2025" s="2">
+        <v>1052702102</v>
+      </c>
+      <c r="B2025" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2025" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2025" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2025" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2025" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2025" s="74">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2026" customHeight="1" spans="1:7">
+      <c r="A2026" s="2">
+        <v>1052702103</v>
+      </c>
+      <c r="B2026" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2026" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2026" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2026" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2026" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2026" s="74">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="2027" customHeight="1" spans="1:7">
+      <c r="A2027" s="2">
+        <v>1052702104</v>
+      </c>
+      <c r="B2027" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2027" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2027" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2027" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2027" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2027" s="74">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="2028" customHeight="1" spans="1:7">
+      <c r="A2028" s="2">
+        <v>1052702105</v>
+      </c>
+      <c r="B2028" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2028" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2028" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2028" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2028" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2028" s="74">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="2029" customHeight="1" spans="1:7">
+      <c r="A2029" s="2">
+        <v>1052702106</v>
+      </c>
+      <c r="B2029" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2029" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2029" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2029" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2029" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2029" s="74">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2030" customHeight="1" spans="1:7">
+      <c r="A2030" s="2">
+        <v>1052702107</v>
+      </c>
+      <c r="B2030" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2030" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2030" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2030" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2030" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2030" s="74">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2031" customHeight="1" spans="1:7">
+      <c r="A2031" s="2">
+        <v>1052702108</v>
+      </c>
+      <c r="B2031" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2031" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2031" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2031" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2031" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2031" s="74">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2032" customHeight="1" spans="1:7">
+      <c r="A2032" s="2">
+        <v>1052702109</v>
+      </c>
+      <c r="B2032" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2032" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2032" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2032" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2032" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2032" s="74">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="2033" customHeight="1" spans="1:7">
+      <c r="A2033" s="2">
+        <v>1052702110</v>
+      </c>
+      <c r="B2033" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2033" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2033" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2033" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2033" s="47">
+        <v>21</v>
+      </c>
+      <c r="G2033" s="74">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="2034" customHeight="1" spans="1:7">
+      <c r="A2034" s="2">
+        <v>1052702201</v>
+      </c>
+      <c r="B2034" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2034" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2034" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2034" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2034" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2034" s="74">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2035" customHeight="1" spans="1:7">
+      <c r="A2035" s="2">
+        <v>1052702202</v>
+      </c>
+      <c r="B2035" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2035" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2035" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2035" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2035" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2035" s="74">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="2036" customHeight="1" spans="1:7">
+      <c r="A2036" s="2">
+        <v>1052702203</v>
+      </c>
+      <c r="B2036" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2036" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2036" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2036" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2036" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2036" s="74">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="2037" customHeight="1" spans="1:7">
+      <c r="A2037" s="2">
+        <v>1052702204</v>
+      </c>
+      <c r="B2037" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2037" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2037" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2037" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2037" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2037" s="74">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="2038" customHeight="1" spans="1:7">
+      <c r="A2038" s="2">
+        <v>1052702205</v>
+      </c>
+      <c r="B2038" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2038" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2038" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2038" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2038" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2038" s="74">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="2039" customHeight="1" spans="1:7">
+      <c r="A2039" s="2">
+        <v>1052702206</v>
+      </c>
+      <c r="B2039" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2039" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2039" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2039" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2039" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2039" s="74">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2040" customHeight="1" spans="1:7">
+      <c r="A2040" s="2">
+        <v>1052702207</v>
+      </c>
+      <c r="B2040" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2040" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2040" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2040" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2040" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2040" s="74">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2041" customHeight="1" spans="1:7">
+      <c r="A2041" s="2">
+        <v>1052702208</v>
+      </c>
+      <c r="B2041" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2041" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2041" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2041" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2041" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2041" s="74">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2042" customHeight="1" spans="1:7">
+      <c r="A2042" s="2">
+        <v>1052702209</v>
+      </c>
+      <c r="B2042" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2042" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2042" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2042" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2042" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2042" s="74">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="2043" customHeight="1" spans="1:7">
+      <c r="A2043" s="2">
+        <v>1052702210</v>
+      </c>
+      <c r="B2043" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2043" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2043" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2043" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2043" s="47">
+        <v>22</v>
+      </c>
+      <c r="G2043" s="74">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="2044" customHeight="1" spans="1:7">
+      <c r="A2044" s="2">
+        <v>1052702301</v>
+      </c>
+      <c r="B2044" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2044" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2044" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2044" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2044" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2044" s="74">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2045" customHeight="1" spans="1:7">
+      <c r="A2045" s="2">
+        <v>1052702302</v>
+      </c>
+      <c r="B2045" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2045" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2045" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2045" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2045" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2045" s="74">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="2046" customHeight="1" spans="1:7">
+      <c r="A2046" s="2">
+        <v>1052702303</v>
+      </c>
+      <c r="B2046" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2046" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2046" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2046" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2046" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2046" s="74">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="2047" customHeight="1" spans="1:7">
+      <c r="A2047" s="2">
+        <v>1052702304</v>
+      </c>
+      <c r="B2047" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2047" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2047" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2047" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2047" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2047" s="74">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="2048" customHeight="1" spans="1:7">
+      <c r="A2048" s="2">
+        <v>1052702305</v>
+      </c>
+      <c r="B2048" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2048" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2048" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2048" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2048" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2048" s="74">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="2049" customHeight="1" spans="1:7">
+      <c r="A2049" s="2">
+        <v>1052702306</v>
+      </c>
+      <c r="B2049" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2049" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2049" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2049" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2049" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2049" s="74">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2050" customHeight="1" spans="1:7">
+      <c r="A2050" s="2">
+        <v>1052702307</v>
+      </c>
+      <c r="B2050" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2050" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2050" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2050" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2050" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2050" s="74">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="2051" customHeight="1" spans="1:7">
+      <c r="A2051" s="2">
+        <v>1052702308</v>
+      </c>
+      <c r="B2051" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2051" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2051" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2051" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2051" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2051" s="74">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="2052" customHeight="1" spans="1:7">
+      <c r="A2052" s="2">
+        <v>1052702309</v>
+      </c>
+      <c r="B2052" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2052" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2052" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2052" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2052" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2052" s="74">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="2053" customHeight="1" spans="1:7">
+      <c r="A2053" s="2">
+        <v>1052702310</v>
+      </c>
+      <c r="B2053" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2053" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2053" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2053" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2053" s="47">
+        <v>23</v>
+      </c>
+      <c r="G2053" s="74">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="2054" customHeight="1" spans="1:7">
+      <c r="A2054" s="2">
+        <v>1052702401</v>
+      </c>
+      <c r="B2054" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2054" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2054" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2054" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2054" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2054" s="74">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2055" customHeight="1" spans="1:7">
+      <c r="A2055" s="2">
+        <v>1052702402</v>
+      </c>
+      <c r="B2055" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2055" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2055" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2055" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2055" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2055" s="74">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="2056" customHeight="1" spans="1:7">
+      <c r="A2056" s="2">
+        <v>1052702403</v>
+      </c>
+      <c r="B2056" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2056" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2056" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2056" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2056" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2056" s="74">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="2057" customHeight="1" spans="1:7">
+      <c r="A2057" s="2">
+        <v>1052702404</v>
+      </c>
+      <c r="B2057" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2057" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2057" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2057" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2057" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2057" s="74">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="2058" customHeight="1" spans="1:7">
+      <c r="A2058" s="2">
+        <v>1052702405</v>
+      </c>
+      <c r="B2058" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2058" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2058" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2058" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2058" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2058" s="74">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="2059" customHeight="1" spans="1:7">
+      <c r="A2059" s="2">
+        <v>1052702406</v>
+      </c>
+      <c r="B2059" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2059" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2059" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2059" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2059" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2059" s="74">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2060" customHeight="1" spans="1:7">
+      <c r="A2060" s="2">
+        <v>1052702407</v>
+      </c>
+      <c r="B2060" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2060" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2060" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2060" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2060" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2060" s="74">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="2061" customHeight="1" spans="1:7">
+      <c r="A2061" s="2">
+        <v>1052702408</v>
+      </c>
+      <c r="B2061" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2061" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2061" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2061" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2061" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2061" s="74">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="2062" customHeight="1" spans="1:7">
+      <c r="A2062" s="2">
+        <v>1052702409</v>
+      </c>
+      <c r="B2062" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2062" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2062" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2062" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2062" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2062" s="74">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="2063" customHeight="1" spans="1:7">
+      <c r="A2063" s="2">
+        <v>1052702410</v>
+      </c>
+      <c r="B2063" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2063" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2063" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2063" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2063" s="47">
+        <v>24</v>
+      </c>
+      <c r="G2063" s="74">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="2064" customHeight="1" spans="1:7">
+      <c r="A2064" s="2">
+        <v>1052702501</v>
+      </c>
+      <c r="B2064" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2064" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2064" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2064" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2064" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2064" s="74">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="2065" customHeight="1" spans="1:7">
+      <c r="A2065" s="2">
+        <v>1052702502</v>
+      </c>
+      <c r="B2065" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2065" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2065" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2065" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2065" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2065" s="74">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="2066" customHeight="1" spans="1:7">
+      <c r="A2066" s="2">
+        <v>1052702503</v>
+      </c>
+      <c r="B2066" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2066" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2066" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2066" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2066" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2066" s="74">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="2067" customHeight="1" spans="1:7">
+      <c r="A2067" s="2">
+        <v>1052702504</v>
+      </c>
+      <c r="B2067" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2067" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2067" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2067" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2067" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2067" s="74">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="2068" customHeight="1" spans="1:7">
+      <c r="A2068" s="2">
+        <v>1052702505</v>
+      </c>
+      <c r="B2068" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2068" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2068" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2068" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2068" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2068" s="74">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="2069" customHeight="1" spans="1:7">
+      <c r="A2069" s="2">
+        <v>1052702506</v>
+      </c>
+      <c r="B2069" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2069" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2069" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2069" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2069" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2069" s="74">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2070" customHeight="1" spans="1:7">
+      <c r="A2070" s="2">
+        <v>1052702507</v>
+      </c>
+      <c r="B2070" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2070" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2070" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2070" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2070" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2070" s="74">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="2071" customHeight="1" spans="1:7">
+      <c r="A2071" s="2">
+        <v>1052702508</v>
+      </c>
+      <c r="B2071" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2071" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2071" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2071" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2071" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2071" s="74">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="2072" customHeight="1" spans="1:7">
+      <c r="A2072" s="2">
+        <v>1052702509</v>
+      </c>
+      <c r="B2072" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2072" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2072" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2072" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2072" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2072" s="74">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="2073" customHeight="1" spans="1:7">
+      <c r="A2073" s="2">
+        <v>1052702510</v>
+      </c>
+      <c r="B2073" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2073" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2073" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2073" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2073" s="47">
+        <v>25</v>
+      </c>
+      <c r="G2073" s="74">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="2074" customHeight="1" spans="1:7">
+      <c r="A2074" s="2">
+        <v>1052702601</v>
+      </c>
+      <c r="B2074" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2074" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2074" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2074" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2074" s="2">
+        <v>26</v>
+      </c>
+      <c r="G2074" s="74">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2075" customHeight="1" spans="1:7">
+      <c r="A2075" s="2">
+        <v>1052702602</v>
+      </c>
+      <c r="B2075" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2075" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2075" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2075" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2075" s="2">
+        <v>26</v>
+      </c>
+      <c r="G2075" s="74">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="2076" customHeight="1" spans="1:7">
+      <c r="A2076" s="2">
+        <v>1052702603</v>
+      </c>
+      <c r="B2076" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2076" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2076" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2076" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2076" s="2">
+        <v>26</v>
+      </c>
+      <c r="G2076" s="74">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="2077" customHeight="1" spans="1:7">
+      <c r="A2077" s="2">
+        <v>1052702604</v>
+      </c>
+      <c r="B2077" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2077" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2077" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2077" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2077" s="2">
+        <v>26</v>
+      </c>
+      <c r="G2077" s="74">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="2078" customHeight="1" spans="1:7">
+      <c r="A2078" s="2">
+        <v>1052702605</v>
+      </c>
+      <c r="B2078" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2078" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2078" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2078" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2078" s="2">
+        <v>26</v>
+      </c>
+      <c r="G2078" s="74">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="2079" customHeight="1" spans="1:7">
+      <c r="A2079" s="2">
+        <v>1052702701</v>
+      </c>
+      <c r="B2079" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2079" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2079" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2079" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2079" s="2">
+        <v>27</v>
+      </c>
+      <c r="G2079" s="74">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2080" customHeight="1" spans="1:7">
+      <c r="A2080" s="2">
+        <v>1052702702</v>
+      </c>
+      <c r="B2080" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2080" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2080" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2080" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2080" s="2">
+        <v>27</v>
+      </c>
+      <c r="G2080" s="74">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="2081" customHeight="1" spans="1:7">
+      <c r="A2081" s="2">
+        <v>1052702703</v>
+      </c>
+      <c r="B2081" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2081" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2081" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2081" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2081" s="2">
+        <v>27</v>
+      </c>
+      <c r="G2081" s="74">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="2082" customHeight="1" spans="1:7">
+      <c r="A2082" s="2">
+        <v>1052702704</v>
+      </c>
+      <c r="B2082" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2082" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2082" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2082" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2082" s="2">
+        <v>27</v>
+      </c>
+      <c r="G2082" s="74">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="2083" customHeight="1" spans="1:7">
+      <c r="A2083" s="2">
+        <v>1052702705</v>
+      </c>
+      <c r="B2083" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2083" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2083" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2083" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2083" s="2">
+        <v>27</v>
+      </c>
+      <c r="G2083" s="74">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="2084" customHeight="1" spans="1:7">
+      <c r="A2084" s="2">
+        <v>1052702801</v>
+      </c>
+      <c r="B2084" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2084" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2084" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2084" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2084" s="2">
+        <v>28</v>
+      </c>
+      <c r="G2084" s="74">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2085" customHeight="1" spans="1:7">
+      <c r="A2085" s="2">
+        <v>1052702802</v>
+      </c>
+      <c r="B2085" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2085" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2085" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2085" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2085" s="2">
+        <v>28</v>
+      </c>
+      <c r="G2085" s="74">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="2086" customHeight="1" spans="1:7">
+      <c r="A2086" s="2">
+        <v>1052702803</v>
+      </c>
+      <c r="B2086" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2086" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2086" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2086" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2086" s="2">
+        <v>28</v>
+      </c>
+      <c r="G2086" s="74">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="2087" customHeight="1" spans="1:7">
+      <c r="A2087" s="2">
+        <v>1052702804</v>
+      </c>
+      <c r="B2087" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2087" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2087" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2087" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2087" s="2">
+        <v>28</v>
+      </c>
+      <c r="G2087" s="74">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="2088" customHeight="1" spans="1:7">
+      <c r="A2088" s="2">
+        <v>1052702805</v>
+      </c>
+      <c r="B2088" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2088" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2088" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2088" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2088" s="2">
+        <v>28</v>
+      </c>
+      <c r="G2088" s="74">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="2089" customHeight="1" spans="1:7">
+      <c r="A2089" s="2">
+        <v>1052702901</v>
+      </c>
+      <c r="B2089" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2089" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2089" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2089" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2089" s="2">
+        <v>29</v>
+      </c>
+      <c r="G2089" s="74">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="2090" customHeight="1" spans="1:7">
+      <c r="A2090" s="2">
+        <v>1052702902</v>
+      </c>
+      <c r="B2090" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2090" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2090" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2090" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2090" s="2">
+        <v>29</v>
+      </c>
+      <c r="G2090" s="74">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="2091" customHeight="1" spans="1:7">
+      <c r="A2091" s="2">
+        <v>1052702903</v>
+      </c>
+      <c r="B2091" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2091" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2091" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2091" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2091" s="2">
+        <v>29</v>
+      </c>
+      <c r="G2091" s="74">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="2092" customHeight="1" spans="1:7">
+      <c r="A2092" s="2">
+        <v>1052702904</v>
+      </c>
+      <c r="B2092" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2092" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2092" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2092" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2092" s="2">
+        <v>29</v>
+      </c>
+      <c r="G2092" s="74">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="2093" customHeight="1" spans="1:7">
+      <c r="A2093" s="2">
+        <v>1052702905</v>
+      </c>
+      <c r="B2093" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2093" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2093" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2093" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2093" s="2">
+        <v>29</v>
+      </c>
+      <c r="G2093" s="74">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="2094" customHeight="1" spans="1:7">
+      <c r="A2094" s="2">
+        <v>1052703001</v>
+      </c>
+      <c r="B2094" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2094" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2094" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2094" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2094" s="2">
+        <v>30</v>
+      </c>
+      <c r="G2094" s="74">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="2095" customHeight="1" spans="1:7">
+      <c r="A2095" s="2">
+        <v>1052703002</v>
+      </c>
+      <c r="B2095" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2095" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2095" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2095" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2095" s="2">
+        <v>30</v>
+      </c>
+      <c r="G2095" s="74">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="2096" customHeight="1" spans="1:7">
+      <c r="A2096" s="2">
+        <v>1052703003</v>
+      </c>
+      <c r="B2096" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2096" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2096" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2096" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2096" s="2">
+        <v>30</v>
+      </c>
+      <c r="G2096" s="74">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="2097" customHeight="1" spans="1:7">
+      <c r="A2097" s="2">
+        <v>1052703004</v>
+      </c>
+      <c r="B2097" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2097" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2097" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2097" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2097" s="2">
+        <v>30</v>
+      </c>
+      <c r="G2097" s="74">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="2098" customHeight="1" spans="1:7">
+      <c r="A2098" s="2">
+        <v>1052703005</v>
+      </c>
+      <c r="B2098" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2098" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2098" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2098" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2098" s="2">
+        <v>30</v>
+      </c>
+      <c r="G2098" s="74">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="2099" customHeight="1" spans="1:7">
+      <c r="A2099" s="2">
+        <v>1052703101</v>
+      </c>
+      <c r="B2099" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2099" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2099" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2099" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2099" s="2">
+        <v>31</v>
+      </c>
+      <c r="G2099" s="74">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="2100" customHeight="1" spans="1:7">
+      <c r="A2100" s="2">
+        <v>1052703102</v>
+      </c>
+      <c r="B2100" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2100" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2100" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2100" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2100" s="2">
+        <v>31</v>
+      </c>
+      <c r="G2100" s="74">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="2101" customHeight="1" spans="1:7">
+      <c r="A2101" s="2">
+        <v>1052703103</v>
+      </c>
+      <c r="B2101" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2101" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2101" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2101" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2101" s="2">
+        <v>31</v>
+      </c>
+      <c r="G2101" s="74">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="2102" customHeight="1" spans="1:7">
+      <c r="A2102" s="2">
+        <v>1052703104</v>
+      </c>
+      <c r="B2102" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2102" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2102" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2102" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2102" s="2">
+        <v>31</v>
+      </c>
+      <c r="G2102" s="74">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2103" customHeight="1" spans="1:7">
+      <c r="A2103" s="2">
+        <v>1052703105</v>
+      </c>
+      <c r="B2103" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2103" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2103" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2103" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2103" s="2">
+        <v>31</v>
+      </c>
+      <c r="G2103" s="74">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="2104" customHeight="1" spans="1:7">
+      <c r="A2104" s="2">
+        <v>1052703201</v>
+      </c>
+      <c r="B2104" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2104" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2104" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2104" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2104" s="2">
+        <v>32</v>
+      </c>
+      <c r="G2104" s="74">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="2105" customHeight="1" spans="1:7">
+      <c r="A2105" s="2">
+        <v>1052703202</v>
+      </c>
+      <c r="B2105" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2105" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2105" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2105" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2105" s="2">
+        <v>32</v>
+      </c>
+      <c r="G2105" s="74">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="2106" customHeight="1" spans="1:7">
+      <c r="A2106" s="2">
+        <v>1052703203</v>
+      </c>
+      <c r="B2106" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2106" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2106" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2106" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2106" s="2">
+        <v>32</v>
+      </c>
+      <c r="G2106" s="74">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="2107" customHeight="1" spans="1:7">
+      <c r="A2107" s="2">
+        <v>1052703204</v>
+      </c>
+      <c r="B2107" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2107" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2107" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2107" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2107" s="2">
+        <v>32</v>
+      </c>
+      <c r="G2107" s="74">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="2108" customHeight="1" spans="1:7">
+      <c r="A2108" s="2">
+        <v>1052703205</v>
+      </c>
+      <c r="B2108" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2108" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2108" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2108" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2108" s="2">
+        <v>32</v>
+      </c>
+      <c r="G2108" s="74">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="2109" customHeight="1" spans="1:7">
+      <c r="A2109" s="2">
+        <v>1052703301</v>
+      </c>
+      <c r="B2109" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2109" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2109" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2109" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2109" s="2">
+        <v>33</v>
+      </c>
+      <c r="G2109" s="74">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="2110" customHeight="1" spans="1:7">
+      <c r="A2110" s="2">
+        <v>1052703302</v>
+      </c>
+      <c r="B2110" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2110" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2110" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2110" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2110" s="2">
+        <v>33</v>
+      </c>
+      <c r="G2110" s="74">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="2111" customHeight="1" spans="1:7">
+      <c r="A2111" s="2">
+        <v>1052703303</v>
+      </c>
+      <c r="B2111" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2111" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2111" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2111" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2111" s="2">
+        <v>33</v>
+      </c>
+      <c r="G2111" s="74">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="2112" customHeight="1" spans="1:7">
+      <c r="A2112" s="2">
+        <v>1052703304</v>
+      </c>
+      <c r="B2112" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2112" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2112" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2112" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2112" s="2">
+        <v>33</v>
+      </c>
+      <c r="G2112" s="74">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="2113" customHeight="1" spans="1:7">
+      <c r="A2113" s="2">
+        <v>1052703305</v>
+      </c>
+      <c r="B2113" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2113" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2113" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2113" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2113" s="2">
+        <v>33</v>
+      </c>
+      <c r="G2113" s="74">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="2114" customHeight="1" spans="1:7">
+      <c r="A2114" s="2">
+        <v>1052703401</v>
+      </c>
+      <c r="B2114" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2114" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2114" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2114" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2114" s="2">
+        <v>34</v>
+      </c>
+      <c r="G2114" s="74">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="2115" customHeight="1" spans="1:7">
+      <c r="A2115" s="2">
+        <v>1052703402</v>
+      </c>
+      <c r="B2115" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2115" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2115" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2115" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2115" s="2">
+        <v>34</v>
+      </c>
+      <c r="G2115" s="74">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="2116" customHeight="1" spans="1:7">
+      <c r="A2116" s="2">
+        <v>1052703403</v>
+      </c>
+      <c r="B2116" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2116" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2116" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2116" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2116" s="2">
+        <v>34</v>
+      </c>
+      <c r="G2116" s="74">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="2117" customHeight="1" spans="1:7">
+      <c r="A2117" s="2">
+        <v>1052703404</v>
+      </c>
+      <c r="B2117" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2117" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2117" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2117" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2117" s="2">
+        <v>34</v>
+      </c>
+      <c r="G2117" s="74">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="2118" customHeight="1" spans="1:7">
+      <c r="A2118" s="2">
+        <v>1052703405</v>
+      </c>
+      <c r="B2118" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2118" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2118" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2118" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2118" s="2">
+        <v>34</v>
+      </c>
+      <c r="G2118" s="74">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="2119" customHeight="1" spans="1:7">
+      <c r="A2119" s="2">
+        <v>1052703501</v>
+      </c>
+      <c r="B2119" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2119" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2119" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2119" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2119" s="2">
+        <v>35</v>
+      </c>
+      <c r="G2119" s="74">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="2120" customHeight="1" spans="1:7">
+      <c r="A2120" s="2">
+        <v>1052703502</v>
+      </c>
+      <c r="B2120" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2120" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2120" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2120" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2120" s="2">
+        <v>35</v>
+      </c>
+      <c r="G2120" s="74">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="2121" customHeight="1" spans="1:7">
+      <c r="A2121" s="2">
+        <v>1052703503</v>
+      </c>
+      <c r="B2121" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2121" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2121" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2121" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2121" s="2">
+        <v>35</v>
+      </c>
+      <c r="G2121" s="74">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="2122" customHeight="1" spans="1:7">
+      <c r="A2122" s="2">
+        <v>1052703504</v>
+      </c>
+      <c r="B2122" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2122" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2122" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2122" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2122" s="2">
+        <v>35</v>
+      </c>
+      <c r="G2122" s="74">
+        <v>3604</v>
+      </c>
+    </row>
+    <row r="2123" customHeight="1" spans="1:7">
+      <c r="A2123" s="2">
+        <v>1052703505</v>
+      </c>
+      <c r="B2123" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2123" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2123" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2123" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2123" s="2">
+        <v>35</v>
+      </c>
+      <c r="G2123" s="74">
+        <v>4505</v>
+      </c>
+    </row>
+    <row r="2124" customHeight="1" spans="1:7">
+      <c r="A2124" s="2">
+        <v>1052703601</v>
+      </c>
+      <c r="B2124" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2124" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2124" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2124" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2124" s="2">
+        <v>36</v>
+      </c>
+      <c r="G2124" s="74">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="2125" customHeight="1" spans="1:7">
+      <c r="A2125" s="2">
+        <v>1052703602</v>
+      </c>
+      <c r="B2125" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2125" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2125" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2125" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2125" s="2">
+        <v>36</v>
+      </c>
+      <c r="G2125" s="74">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="2126" customHeight="1" spans="1:7">
+      <c r="A2126" s="2">
+        <v>1052703603</v>
+      </c>
+      <c r="B2126" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2126" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2126" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2126" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2126" s="2">
+        <v>36</v>
+      </c>
+      <c r="G2126" s="74">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="2127" customHeight="1" spans="1:7">
+      <c r="A2127" s="2">
+        <v>1052703604</v>
+      </c>
+      <c r="B2127" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2127" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2127" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2127" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2127" s="2">
+        <v>36</v>
+      </c>
+      <c r="G2127" s="74">
+        <v>3976</v>
+      </c>
+    </row>
+    <row r="2128" customHeight="1" spans="1:7">
+      <c r="A2128" s="2">
+        <v>1052703605</v>
+      </c>
+      <c r="B2128" s="2">
+        <v>105200</v>
+      </c>
+      <c r="C2128" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2128" s="55">
+        <v>7</v>
+      </c>
+      <c r="E2128" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2128" s="2">
+        <v>36</v>
+      </c>
+      <c r="G2128" s="74">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="2129" customHeight="1" spans="1:12">
+      <c r="A2129" s="2"/>
+      <c r="B2129" s="2"/>
+      <c r="C2129" s="2"/>
+      <c r="D2129" s="55"/>
+      <c r="E2129" s="9"/>
+      <c r="F2129" s="2"/>
+      <c r="G2129" s="74"/>
+    </row>
+    <row r="2130" customHeight="1" spans="1:12">
+      <c r="A2130" s="2"/>
+      <c r="B2130" s="2"/>
+      <c r="C2130" s="2"/>
+      <c r="D2130" s="55"/>
+      <c r="E2130" s="9"/>
+      <c r="F2130" s="2"/>
+      <c r="G2130" s="74"/>
+    </row>
+    <row r="2131" customHeight="1" spans="1:12">
+      <c r="A2131" s="2"/>
+      <c r="B2131" s="2"/>
+      <c r="C2131" s="2"/>
+      <c r="D2131" s="55"/>
+      <c r="E2131" s="9"/>
+      <c r="F2131" s="2"/>
+      <c r="G2131" s="74"/>
+    </row>
+    <row r="2132" customHeight="1" spans="1:12">
+      <c r="A2132" s="2"/>
+      <c r="B2132" s="2"/>
+      <c r="C2132" s="2"/>
+      <c r="D2132" s="2"/>
+      <c r="E2132" s="9"/>
+      <c r="F2132" s="2"/>
+      <c r="G2132" s="74"/>
+      <c r="H2132" s="76"/>
+    </row>
+    <row r="2133" customHeight="1" spans="1:12">
+      <c r="A2133" s="2"/>
+      <c r="B2133" s="2"/>
+      <c r="C2133" s="2"/>
+      <c r="D2133" s="2"/>
+      <c r="E2133" s="9"/>
+      <c r="F2133" s="2"/>
+      <c r="G2133" s="74"/>
+      <c r="H2133"/>
+      <c r="I2133" s="9"/>
+      <c r="J2133" s="10"/>
+      <c r="K2133"/>
+      <c r="L2133" s="70"/>
+    </row>
+    <row r="2134" customHeight="1" spans="1:12">
+      <c r="A2134" s="2"/>
+      <c r="B2134" s="2"/>
+      <c r="C2134" s="2"/>
+      <c r="D2134" s="2"/>
+      <c r="E2134" s="9"/>
+      <c r="F2134" s="2"/>
+      <c r="G2134" s="74"/>
+      <c r="H2134"/>
+      <c r="I2134" s="9"/>
+      <c r="J2134" s="10"/>
+      <c r="K2134"/>
+      <c r="L2134" s="70"/>
+    </row>
+    <row r="2135" customHeight="1" spans="1:12">
+      <c r="A2135" s="2"/>
+      <c r="B2135" s="2"/>
+      <c r="C2135" s="2"/>
+      <c r="D2135" s="2"/>
+      <c r="E2135" s="9"/>
+      <c r="F2135" s="2"/>
+      <c r="G2135" s="74"/>
+      <c r="H2135"/>
+      <c r="I2135" s="9"/>
+      <c r="J2135" s="10"/>
+      <c r="K2135"/>
+      <c r="L2135" s="70"/>
+    </row>
+    <row r="2136" customHeight="1" spans="1:12">
+      <c r="A2136" s="2"/>
+      <c r="B2136" s="2"/>
+      <c r="C2136" s="2"/>
+      <c r="D2136" s="2"/>
+      <c r="E2136" s="9"/>
+      <c r="F2136" s="2"/>
+      <c r="G2136" s="74"/>
+      <c r="H2136"/>
+      <c r="I2136" s="9"/>
+      <c r="J2136" s="10"/>
+      <c r="K2136"/>
+      <c r="L2136" s="72"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L1803" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="0" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="0" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="0" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="0" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="0" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="1" priority="484">
+    <cfRule type="expression" dxfId="1" priority="487">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="1" priority="483">
+    <cfRule type="expression" dxfId="1" priority="486">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L346">
-    <cfRule type="expression" dxfId="1" priority="485">
+    <cfRule type="expression" dxfId="1" priority="488">
       <formula>MOD($B350,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E549">
-    <cfRule type="expression" dxfId="1" priority="35">
+    <cfRule type="expression" dxfId="1" priority="38">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L644">
-    <cfRule type="expression" dxfId="1" priority="34">
+    <cfRule type="expression" dxfId="1" priority="37">
       <formula>MOD($B644,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A942">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A943">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A944">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A945">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A943">
+  <conditionalFormatting sqref="A946">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A944">
+  <conditionalFormatting sqref="A947">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A945">
+  <conditionalFormatting sqref="A948">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A946">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A947">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A948">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G1780">
-    <cfRule type="expression" dxfId="1" priority="499">
+    <cfRule type="expression" dxfId="1" priority="502">
       <formula>MOD($B1779,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="0" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
+    <cfRule type="duplicateValues" dxfId="0" priority="164"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A93:A98">
     <cfRule type="duplicateValues" dxfId="0" priority="161"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A93:A98">
+  <conditionalFormatting sqref="A99:A104">
     <cfRule type="duplicateValues" dxfId="0" priority="158"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="0" priority="155"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A209:A469">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A521:A799">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A800:A851">
-    <cfRule type="duplicateValues" dxfId="0" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A852:A897">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A898:A908">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A909:A919">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A920:A930">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A898:A908">
+  <conditionalFormatting sqref="A931:A941">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A909:A919">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  <conditionalFormatting sqref="A1661:A1675">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A920:A930">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A931:A941">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1661:A1675">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A1804:A2136">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C602:C605">
-    <cfRule type="expression" dxfId="1" priority="494">
+    <cfRule type="expression" dxfId="1" priority="497">
       <formula>MOD($B618,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C606:C611">
-    <cfRule type="expression" dxfId="1" priority="491">
+    <cfRule type="expression" dxfId="1" priority="494">
       <formula>MOD($B623,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="1" priority="58">
+    <cfRule type="expression" dxfId="1" priority="61">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E592:E605">
-    <cfRule type="expression" dxfId="1" priority="36">
+    <cfRule type="expression" dxfId="1" priority="39">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755:G761">
-    <cfRule type="expression" dxfId="1" priority="497">
+    <cfRule type="expression" dxfId="1" priority="500">
       <formula>MOD($B754,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H592:H601">
-    <cfRule type="expression" dxfId="1" priority="37">
+    <cfRule type="expression" dxfId="1" priority="40">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H606:H608">
-    <cfRule type="expression" dxfId="1" priority="487">
+    <cfRule type="expression" dxfId="1" priority="490">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L645:L647">
-    <cfRule type="expression" dxfId="1" priority="33">
+    <cfRule type="expression" dxfId="1" priority="36">
       <formula>MOD($B638,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A949:A1660 A1676:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="480"/>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A949:A1660 A1676:A1803 A2137:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="1" priority="479">
+    <cfRule type="expression" dxfId="1" priority="482">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:G60">
-    <cfRule type="expression" dxfId="1" priority="162">
+    <cfRule type="expression" dxfId="1" priority="165">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J41:J42 L41:L42 B179:L204 B205:G208 B259:D268 F259:L268 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B549:D549 F549:L549 B550:L591 I592:L601 D592:D604 B592:B611 F602:J604 H605:L605 F605:F608 I606:L608 D609:G610 I609:J610 D611:J611 B612:L643 B644:K647 B648:L753 B754:F761 H754:L761 B1329:G1332 I1329:J1332 L1329:L1332">
-    <cfRule type="expression" dxfId="1" priority="478">
+    <cfRule type="expression" dxfId="1" priority="481">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J43:L60">
-    <cfRule type="expression" dxfId="1" priority="164">
+    <cfRule type="expression" dxfId="1" priority="167">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61:L134">
-    <cfRule type="expression" dxfId="1" priority="77">
+    <cfRule type="expression" dxfId="1" priority="80">
       <formula>MOD($B61,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:G178">
-    <cfRule type="expression" dxfId="1" priority="64">
+    <cfRule type="expression" dxfId="1" priority="67">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J171:J172 L171:L172">
-    <cfRule type="expression" dxfId="1" priority="75">
+    <cfRule type="expression" dxfId="1" priority="78">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J173:L178">
-    <cfRule type="expression" dxfId="1" priority="65">
+    <cfRule type="expression" dxfId="1" priority="68">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I205:L256 B210:H256">
-    <cfRule type="expression" dxfId="1" priority="61">
+    <cfRule type="expression" dxfId="1" priority="64">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209">
-    <cfRule type="expression" dxfId="1" priority="62">
+    <cfRule type="expression" dxfId="1" priority="65">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B257:B259 B261 B263 B265 B267 B269 B1333:L1660 B1676:L1778 B1779:F1779 H1779:L1779 B1780:F1780 H1780:L1780 B1781:L1048576">
-    <cfRule type="expression" dxfId="1" priority="59">
+  <conditionalFormatting sqref="B257:B259 B261 B263 B265 B267 B269 B1333:L1660 B1676:L1778 B1779:F1779 H1779:L1779 B1780:F1780 H1780:L1780 B1781:L1803 B2137:L1048576">
+    <cfRule type="expression" dxfId="1" priority="62">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="1" priority="482">
+    <cfRule type="expression" dxfId="1" priority="485">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 F258:L258 D260 I260 D262 I262 D264 I264 D266 I266 D268 I268 I270 I272 I274 I276 I278 I280 I282 I284 I286 I288 I290 I292">
-    <cfRule type="expression" dxfId="1" priority="481">
+    <cfRule type="expression" dxfId="1" priority="484">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B269:L307">
-    <cfRule type="expression" dxfId="1" priority="52">
+    <cfRule type="expression" dxfId="1" priority="55">
       <formula>MOD($B269,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K347:L350">
-    <cfRule type="expression" dxfId="1" priority="50">
+    <cfRule type="expression" dxfId="1" priority="53">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B351:L548">
-    <cfRule type="expression" dxfId="1" priority="43">
+    <cfRule type="expression" dxfId="1" priority="46">
       <formula>MOD($B351,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C592 F592:G592">
-    <cfRule type="expression" dxfId="1" priority="492">
+    <cfRule type="expression" dxfId="1" priority="495">
       <formula>MOD($B605,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C593 F593:G593">
-    <cfRule type="expression" dxfId="1" priority="495">
+    <cfRule type="expression" dxfId="1" priority="498">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C594:C595 F594:G595">
-    <cfRule type="expression" dxfId="1" priority="496">
+    <cfRule type="expression" dxfId="1" priority="499">
       <formula>MOD($B606,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C596:C601 F596:G601">
-    <cfRule type="expression" dxfId="1" priority="493">
+    <cfRule type="expression" dxfId="1" priority="496">
       <formula>MOD($B610,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K609:L611">
-    <cfRule type="expression" dxfId="1" priority="40">
+    <cfRule type="expression" dxfId="1" priority="43">
       <formula>MOD($B602,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762:L1328">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>MOD($B762,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1661:L1675">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>MOD($B1661,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1804:L2132">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>MOD($B1661,2)=1</formula>
+      <formula>MOD($B1804,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2133:G2136 I2133:J2136 L2133:L2136">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>MOD($B2133,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -1423,8 +1423,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1435,7 +1434,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -13100,7 +13100,7 @@
         <v>0</v>
       </c>
       <c r="K205" s="9">
-        <v>10170101</v>
+        <v>101700101</v>
       </c>
       <c r="L205" s="10" t="s">
         <v>65</v>
@@ -13129,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="K206" s="9">
-        <v>10170102</v>
+        <v>101700102</v>
       </c>
       <c r="L206" s="10" t="s">
         <v>66</v>
@@ -13158,7 +13158,7 @@
         <v>0</v>
       </c>
       <c r="K207" s="9">
-        <v>10170103</v>
+        <v>101700103</v>
       </c>
       <c r="L207" s="10" t="s">
         <v>67</v>
@@ -13187,7 +13187,7 @@
         <v>0</v>
       </c>
       <c r="K208" s="9">
-        <v>10170104</v>
+        <v>101700104</v>
       </c>
       <c r="L208" s="10" t="s">
         <v>68</v>
@@ -55192,7 +55192,7 @@
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I205:L256 B210:H256">
+  <conditionalFormatting sqref="I205:L209 B210:L256">
     <cfRule type="expression" dxfId="1" priority="61">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -1423,12 +1423,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -24710,7 +24710,7 @@
         <v>4</v>
       </c>
       <c r="G658" s="9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I658" s="7">
         <v>0</v>
@@ -24734,7 +24734,7 @@
         <v>4</v>
       </c>
       <c r="G659" s="9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I659" s="9">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>4</v>
       </c>
       <c r="G660" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I660" s="7">
         <v>0</v>
@@ -24782,7 +24782,7 @@
         <v>4</v>
       </c>
       <c r="G661" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I661" s="9">
         <v>0</v>
@@ -24806,7 +24806,7 @@
         <v>4</v>
       </c>
       <c r="G662" s="9">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I662" s="7">
         <v>0</v>
@@ -24830,7 +24830,7 @@
         <v>4</v>
       </c>
       <c r="G663" s="9">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I663" s="9">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>4</v>
       </c>
       <c r="G664" s="9">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="I664" s="7">
         <v>0</v>
@@ -24878,7 +24878,7 @@
         <v>4</v>
       </c>
       <c r="G665" s="9">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I665" s="9">
         <v>0</v>
@@ -24902,7 +24902,7 @@
         <v>5</v>
       </c>
       <c r="G666" s="9">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I666" s="7">
         <v>0</v>
@@ -24926,7 +24926,7 @@
         <v>5</v>
       </c>
       <c r="G667" s="9">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I667" s="9">
         <v>0</v>
@@ -24950,7 +24950,7 @@
         <v>5</v>
       </c>
       <c r="G668" s="9">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I668" s="7">
         <v>0</v>
@@ -24974,7 +24974,7 @@
         <v>5</v>
       </c>
       <c r="G669" s="9">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I669" s="9">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>5</v>
       </c>
       <c r="G670" s="9">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="I670" s="7">
         <v>0</v>
@@ -25022,7 +25022,7 @@
         <v>5</v>
       </c>
       <c r="G671" s="9">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="I671" s="9">
         <v>0</v>
@@ -25046,7 +25046,7 @@
         <v>5</v>
       </c>
       <c r="G672" s="9">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="I672" s="7">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>5</v>
       </c>
       <c r="G673" s="9">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="I673" s="9">
         <v>0</v>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -9446,7 +9451,7 @@
         <v>3</v>
       </c>
       <c r="G87" s="34">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H87" s="34"/>
       <c r="I87" s="33">
@@ -9475,7 +9480,7 @@
         <v>3</v>
       </c>
       <c r="G88" s="34">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H88" s="34"/>
       <c r="I88" s="33">
@@ -9504,7 +9509,7 @@
         <v>3</v>
       </c>
       <c r="G89" s="34">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H89" s="34"/>
       <c r="I89" s="33">
@@ -9533,7 +9538,7 @@
         <v>3</v>
       </c>
       <c r="G90" s="34">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H90" s="34"/>
       <c r="I90" s="33">
@@ -9562,7 +9567,7 @@
         <v>3</v>
       </c>
       <c r="G91" s="34">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H91" s="34"/>
       <c r="I91" s="33">
@@ -9591,7 +9596,7 @@
         <v>3</v>
       </c>
       <c r="G92" s="34">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H92" s="34"/>
       <c r="I92" s="33">
@@ -9620,7 +9625,7 @@
         <v>4</v>
       </c>
       <c r="G93" s="34">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H93" s="34"/>
       <c r="I93" s="33">
@@ -9649,7 +9654,7 @@
         <v>4</v>
       </c>
       <c r="G94" s="34">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H94" s="34"/>
       <c r="I94" s="33">
@@ -9678,7 +9683,7 @@
         <v>4</v>
       </c>
       <c r="G95" s="34">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H95" s="34"/>
       <c r="I95" s="33">
@@ -9707,7 +9712,7 @@
         <v>4</v>
       </c>
       <c r="G96" s="34">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H96" s="34"/>
       <c r="I96" s="33">
@@ -9736,7 +9741,7 @@
         <v>4</v>
       </c>
       <c r="G97" s="34">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="H97" s="34"/>
       <c r="I97" s="33">
@@ -9765,7 +9770,7 @@
         <v>4</v>
       </c>
       <c r="G98" s="34">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H98" s="34"/>
       <c r="I98" s="33">
@@ -9794,7 +9799,7 @@
         <v>5</v>
       </c>
       <c r="G99" s="34">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H99" s="34"/>
       <c r="I99" s="33">
@@ -9823,7 +9828,7 @@
         <v>5</v>
       </c>
       <c r="G100" s="34">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H100" s="34"/>
       <c r="I100" s="33">
@@ -9852,7 +9857,7 @@
         <v>5</v>
       </c>
       <c r="G101" s="34">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H101" s="34"/>
       <c r="I101" s="33">
@@ -9881,7 +9886,7 @@
         <v>5</v>
       </c>
       <c r="G102" s="34">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H102" s="34"/>
       <c r="I102" s="33">
@@ -9910,7 +9915,7 @@
         <v>5</v>
       </c>
       <c r="G103" s="34">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="H103" s="34"/>
       <c r="I103" s="33">
@@ -9939,7 +9944,7 @@
         <v>5</v>
       </c>
       <c r="G104" s="34">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="H104" s="34"/>
       <c r="I104" s="33">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -1439,12 +1439,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -24715,7 +24715,7 @@
         <v>4</v>
       </c>
       <c r="G658" s="9">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I658" s="7">
         <v>0</v>
@@ -24739,7 +24739,7 @@
         <v>4</v>
       </c>
       <c r="G659" s="9">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I659" s="9">
         <v>0</v>
@@ -24763,7 +24763,7 @@
         <v>4</v>
       </c>
       <c r="G660" s="9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I660" s="7">
         <v>0</v>
@@ -24787,7 +24787,7 @@
         <v>4</v>
       </c>
       <c r="G661" s="9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I661" s="9">
         <v>0</v>
@@ -24811,7 +24811,7 @@
         <v>4</v>
       </c>
       <c r="G662" s="9">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I662" s="7">
         <v>0</v>
@@ -24835,7 +24835,7 @@
         <v>4</v>
       </c>
       <c r="G663" s="9">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I663" s="9">
         <v>0</v>
@@ -24859,7 +24859,7 @@
         <v>4</v>
       </c>
       <c r="G664" s="9">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="I664" s="7">
         <v>0</v>
@@ -24883,7 +24883,7 @@
         <v>4</v>
       </c>
       <c r="G665" s="9">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I665" s="9">
         <v>0</v>
@@ -24907,7 +24907,7 @@
         <v>5</v>
       </c>
       <c r="G666" s="9">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I666" s="7">
         <v>0</v>
@@ -24931,7 +24931,7 @@
         <v>5</v>
       </c>
       <c r="G667" s="9">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I667" s="9">
         <v>0</v>
@@ -24955,7 +24955,7 @@
         <v>5</v>
       </c>
       <c r="G668" s="9">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="I668" s="7">
         <v>0</v>
@@ -24979,7 +24979,7 @@
         <v>5</v>
       </c>
       <c r="G669" s="9">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="I669" s="9">
         <v>0</v>
@@ -25003,7 +25003,7 @@
         <v>5</v>
       </c>
       <c r="G670" s="9">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="I670" s="7">
         <v>0</v>
@@ -25027,7 +25027,7 @@
         <v>5</v>
       </c>
       <c r="G671" s="9">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="I671" s="9">
         <v>0</v>
@@ -25051,7 +25051,7 @@
         <v>5</v>
       </c>
       <c r="G672" s="9">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="I672" s="7">
         <v>0</v>
@@ -25075,7 +25075,7 @@
         <v>5</v>
       </c>
       <c r="G673" s="9">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="I673" s="9">
         <v>0</v>
